--- a/relatorios/Controle_Comercial_Vigna_-_Julho.xlsx
+++ b/relatorios/Controle_Comercial_Vigna_-_Julho.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2483" uniqueCount="920">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2524" uniqueCount="937">
   <si>
     <t>VISÃO GERAL COMERCIAL</t>
   </si>
@@ -919,6 +919,18 @@
     <t>DF</t>
   </si>
   <si>
+    <t>GRU AIRPORT AEROPORTO INTERNACIONAL DE GUARULHOS SA</t>
+  </si>
+  <si>
+    <t>15.578.569/0001-06</t>
+  </si>
+  <si>
+    <t>Samea Pantoja</t>
+  </si>
+  <si>
+    <t>Pamela e Tayna Bregnoli</t>
+  </si>
+  <si>
     <t>Granjas Sao Jose</t>
   </si>
   <si>
@@ -934,7 +946,13 @@
     <t>CE</t>
   </si>
   <si>
-    <t>TERRA LUZ TRANSPORTES S/A</t>
+    <t>Terra Transportes</t>
+  </si>
+  <si>
+    <t>04.843.115/0001-07</t>
+  </si>
+  <si>
+    <t>Fortaleza</t>
   </si>
   <si>
     <t>AMMAC INDUSTRIA E COMERCIO DE ALIMENTOS LTDA</t>
@@ -973,7 +991,19 @@
     <t>Edilaine</t>
   </si>
   <si>
-    <t>Produmaster Industria De Compostos Plasticos Ltda</t>
+    <t>Produmaster Do Nordeste</t>
+  </si>
+  <si>
+    <t>05.695.884/0001-60</t>
+  </si>
+  <si>
+    <t>Ueslei</t>
+  </si>
+  <si>
+    <t>Camaçari</t>
+  </si>
+  <si>
+    <t>Pamela e João</t>
   </si>
   <si>
     <t>Belluno Pagamentos</t>
@@ -1072,7 +1102,16 @@
     <t>Pamela e Luciana</t>
   </si>
   <si>
-    <t>AGM DISTRIBUIDORA</t>
+    <t>AGM INDUSTRIA COMERCIO E REPRESENTACAO LTDA</t>
+  </si>
+  <si>
+    <t>03.673.826/0001-00</t>
+  </si>
+  <si>
+    <t>Daynara</t>
+  </si>
+  <si>
+    <t>Igor e Paola</t>
   </si>
   <si>
     <t>GLACAI</t>
@@ -1114,7 +1153,16 @@
     <t>Cachoeiro de Itapemirim</t>
   </si>
   <si>
-    <t>TERRAL PARTICIPACOES E EMPREENDIMENTOS LTDA</t>
+    <t>TERRAL INCORPORADORA</t>
+  </si>
+  <si>
+    <t>04.004.733/0001-55</t>
+  </si>
+  <si>
+    <t>Evaldo</t>
+  </si>
+  <si>
+    <t>Aparecida de Goiânia</t>
   </si>
   <si>
     <t>PHV ENGENHARIA LTDA</t>
@@ -1129,6 +1177,12 @@
     <t>Cleber e João</t>
   </si>
   <si>
+    <t>Ricardo Gaia e André Eie</t>
+  </si>
+  <si>
+    <t>Compliance e Jurídico</t>
+  </si>
+  <si>
     <t>Data</t>
   </si>
   <si>
@@ -1718,9 +1772,6 @@
   </si>
   <si>
     <t>(47) 3372-8500 - Procurar RH ou financeiro.  03/06 - atenderam e desligaram 17/06 - atenderam e desligaram 01/07 - jefferson (reaproximação)  não se e</t>
-  </si>
-  <si>
-    <t>TERRAL INCORPORADORA</t>
   </si>
   <si>
     <t>(62) 99266-5588 - evaldo juridico reaproximação (62) 3242-6533 buscar cintia resp RH  01/07 - Evaldo a recepcionista não tem o ramal, pedi pelo financ</t>
@@ -4383,7 +4434,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{E4B32E64-19EF-4DB5-B920-74D84D58D640}</x14:id>
+          <x14:id>{51F781DE-E41E-4423-AE2F-E56344F420D0}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -4396,6 +4447,25 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{51F781DE-E41E-4423-AE2F-E56344F420D0}">
+            <x14:dataBar minLength="0" maxLength="100">
+              <x14:cfvo type="num">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="num">
+                <xm:f>1</xm:f>
+              </x14:cfvo>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>E26:E28</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -9378,13 +9448,36 @@
         <v>238</v>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="36"/>
+    <row r="32" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="36">
+        <v>46203.5</v>
+      </c>
       <c r="B32" t="s">
-        <v>199</v>
+        <v>295</v>
+      </c>
+      <c r="C32" t="s">
+        <v>165</v>
+      </c>
+      <c r="D32" t="s">
+        <v>296</v>
+      </c>
+      <c r="E32" t="s">
+        <v>297</v>
+      </c>
+      <c r="F32" t="s">
+        <v>168</v>
+      </c>
+      <c r="G32" t="s">
+        <v>146</v>
+      </c>
+      <c r="H32" t="s">
+        <v>141</v>
       </c>
       <c r="I32" t="s">
         <v>51</v>
+      </c>
+      <c r="J32" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -9392,25 +9485,25 @@
         <v>46223.5</v>
       </c>
       <c r="B33" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C33" t="s">
         <v>255</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E33" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="F33" t="s">
         <v>168</v>
       </c>
       <c r="G33" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="H33" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="I33" t="s">
         <v>50</v>
@@ -9422,7 +9515,19 @@
     <row r="34" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="36"/>
       <c r="B34" t="s">
-        <v>300</v>
+        <v>304</v>
+      </c>
+      <c r="C34" t="s">
+        <v>183</v>
+      </c>
+      <c r="D34" t="s">
+        <v>305</v>
+      </c>
+      <c r="G34" t="s">
+        <v>306</v>
+      </c>
+      <c r="H34" t="s">
+        <v>303</v>
       </c>
       <c r="I34" t="s">
         <v>49</v>
@@ -9433,31 +9538,31 @@
         <v>46224.5</v>
       </c>
       <c r="B35" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="C35" t="s">
         <v>183</v>
       </c>
       <c r="D35" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="E35" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="F35" t="s">
         <v>139</v>
       </c>
       <c r="G35" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="H35" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="I35" t="s">
         <v>51</v>
       </c>
       <c r="J35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -9465,40 +9570,63 @@
         <v>46241.5</v>
       </c>
       <c r="B36" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="C36" t="s">
         <v>165</v>
       </c>
       <c r="D36" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="E36" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="F36" t="s">
         <v>275</v>
       </c>
       <c r="G36" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="H36" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="I36" t="s">
         <v>49</v>
       </c>
       <c r="J36" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A37" s="36"/>
+      <c r="A37" s="36">
+        <v>46217.5</v>
+      </c>
       <c r="B37" t="s">
-        <v>313</v>
+        <v>319</v>
+      </c>
+      <c r="C37" t="s">
+        <v>183</v>
+      </c>
+      <c r="D37" t="s">
+        <v>320</v>
+      </c>
+      <c r="E37" t="s">
+        <v>321</v>
+      </c>
+      <c r="F37" t="s">
+        <v>275</v>
+      </c>
+      <c r="G37" t="s">
+        <v>322</v>
+      </c>
+      <c r="H37" t="s">
+        <v>149</v>
       </c>
       <c r="I37" t="s">
         <v>50</v>
+      </c>
+      <c r="J37" t="s">
+        <v>323</v>
       </c>
       <c r="K37" t="s">
         <v>151</v>
@@ -9512,16 +9640,16 @@
         <v>46219.5</v>
       </c>
       <c r="B38" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="C38" t="s">
         <v>146</v>
       </c>
       <c r="D38" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="E38" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="F38" t="s">
         <v>243</v>
@@ -9536,7 +9664,7 @@
         <v>197</v>
       </c>
       <c r="J38" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="K38" t="s">
         <v>151</v>
@@ -9545,7 +9673,7 @@
         <v>152</v>
       </c>
       <c r="M38" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -9553,22 +9681,22 @@
         <v>46255.5</v>
       </c>
       <c r="B39" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="C39" t="s">
         <v>183</v>
       </c>
       <c r="D39" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="E39" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="F39" t="s">
         <v>283</v>
       </c>
       <c r="G39" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="H39" t="s">
         <v>97</v>
@@ -9577,7 +9705,7 @@
         <v>49</v>
       </c>
       <c r="J39" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -9585,22 +9713,22 @@
         <v>46226.5</v>
       </c>
       <c r="B40" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="C40" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="D40" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="E40" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="F40" t="s">
         <v>206</v>
       </c>
       <c r="G40" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="H40" t="s">
         <v>141</v>
@@ -9609,7 +9737,7 @@
         <v>50</v>
       </c>
       <c r="J40" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -9617,22 +9745,22 @@
         <v>46232.5</v>
       </c>
       <c r="B41" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="C41" t="s">
         <v>255</v>
       </c>
       <c r="D41" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="E41" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="F41" t="s">
         <v>283</v>
       </c>
       <c r="G41" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="H41" t="s">
         <v>97</v>
@@ -9649,25 +9777,25 @@
         <v>46232.5</v>
       </c>
       <c r="B42" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="C42" t="s">
         <v>233</v>
       </c>
       <c r="D42" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="E42" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="F42" t="s">
         <v>168</v>
       </c>
       <c r="G42" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="H42" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="I42" t="s">
         <v>49</v>
@@ -9681,16 +9809,16 @@
         <v>46238.5</v>
       </c>
       <c r="B43" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="C43" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="D43" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="E43" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="F43" t="s">
         <v>139</v>
@@ -9705,7 +9833,7 @@
         <v>50</v>
       </c>
       <c r="J43" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -9713,13 +9841,13 @@
         <v>46247.5</v>
       </c>
       <c r="B44" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="C44" t="s">
         <v>183</v>
       </c>
       <c r="D44" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="E44" t="s">
         <v>224</v>
@@ -9737,16 +9865,39 @@
         <v>49</v>
       </c>
       <c r="J44" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="45" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="36"/>
+        <v>355</v>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="36">
+        <v>46244.5</v>
+      </c>
       <c r="B45" t="s">
-        <v>346</v>
+        <v>356</v>
+      </c>
+      <c r="C45" t="s">
+        <v>183</v>
+      </c>
+      <c r="D45" t="s">
+        <v>357</v>
+      </c>
+      <c r="E45" t="s">
+        <v>358</v>
+      </c>
+      <c r="F45" t="s">
+        <v>139</v>
+      </c>
+      <c r="G45" t="s">
+        <v>310</v>
+      </c>
+      <c r="H45" t="s">
+        <v>311</v>
       </c>
       <c r="I45" t="s">
         <v>50</v>
+      </c>
+      <c r="J45" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -9754,25 +9905,25 @@
         <v>46239.5</v>
       </c>
       <c r="B46" t="s">
-        <v>347</v>
+        <v>360</v>
       </c>
       <c r="C46" t="s">
         <v>183</v>
       </c>
       <c r="D46" t="s">
-        <v>348</v>
+        <v>361</v>
       </c>
       <c r="E46" t="s">
-        <v>349</v>
+        <v>362</v>
       </c>
       <c r="F46" t="s">
         <v>139</v>
       </c>
       <c r="G46" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="H46" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
       <c r="I46" t="s">
         <v>50</v>
@@ -9786,22 +9937,22 @@
         <v>46247.5</v>
       </c>
       <c r="B47" t="s">
-        <v>352</v>
+        <v>365</v>
       </c>
       <c r="C47" t="s">
         <v>165</v>
       </c>
       <c r="D47" t="s">
-        <v>353</v>
+        <v>366</v>
       </c>
       <c r="E47" t="s">
-        <v>354</v>
+        <v>367</v>
       </c>
       <c r="F47" t="s">
         <v>139</v>
       </c>
       <c r="G47" t="s">
-        <v>355</v>
+        <v>368</v>
       </c>
       <c r="H47" t="s">
         <v>252</v>
@@ -9818,22 +9969,22 @@
         <v>46246.5</v>
       </c>
       <c r="B48" t="s">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="C48" t="s">
         <v>145</v>
       </c>
       <c r="D48" t="s">
-        <v>357</v>
+        <v>370</v>
       </c>
       <c r="E48" t="s">
-        <v>358</v>
+        <v>371</v>
       </c>
       <c r="F48" t="s">
         <v>139</v>
       </c>
       <c r="G48" t="s">
-        <v>359</v>
+        <v>372</v>
       </c>
       <c r="H48" t="s">
         <v>271</v>
@@ -9845,13 +9996,36 @@
         <v>113</v>
       </c>
     </row>
-    <row r="49" ht="15" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" s="36"/>
+    <row r="49" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" s="36">
+        <v>46241.5</v>
+      </c>
       <c r="B49" t="s">
-        <v>360</v>
+        <v>373</v>
+      </c>
+      <c r="C49" t="s">
+        <v>183</v>
+      </c>
+      <c r="D49" t="s">
+        <v>374</v>
+      </c>
+      <c r="E49" t="s">
+        <v>375</v>
+      </c>
+      <c r="F49" t="s">
+        <v>168</v>
+      </c>
+      <c r="G49" t="s">
+        <v>376</v>
+      </c>
+      <c r="H49" t="s">
+        <v>170</v>
       </c>
       <c r="I49" t="s">
         <v>50</v>
+      </c>
+      <c r="J49" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -9859,22 +10033,22 @@
         <v>46248.5</v>
       </c>
       <c r="B50" t="s">
-        <v>361</v>
+        <v>377</v>
       </c>
       <c r="C50" t="s">
         <v>183</v>
       </c>
       <c r="D50" t="s">
-        <v>362</v>
+        <v>378</v>
       </c>
       <c r="E50" t="s">
-        <v>363</v>
+        <v>379</v>
       </c>
       <c r="F50" t="s">
         <v>168</v>
       </c>
       <c r="G50" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="H50" t="s">
         <v>97</v>
@@ -9883,11 +10057,40 @@
         <v>49</v>
       </c>
       <c r="J50" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="51" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51" s="36"/>
+        <v>380</v>
+      </c>
+    </row>
+    <row r="51" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" s="36">
+        <v>46209.5</v>
+      </c>
+      <c r="B51" t="s">
+        <v>295</v>
+      </c>
+      <c r="C51" t="s">
+        <v>165</v>
+      </c>
+      <c r="D51" t="s">
+        <v>296</v>
+      </c>
+      <c r="E51" t="s">
+        <v>381</v>
+      </c>
+      <c r="F51" t="s">
+        <v>382</v>
+      </c>
+      <c r="G51" t="s">
+        <v>146</v>
+      </c>
+      <c r="H51" t="s">
+        <v>141</v>
+      </c>
+      <c r="I51" t="s">
+        <v>51</v>
+      </c>
+      <c r="J51" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="52" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="36"/>
@@ -10721,7 +10924,7 @@
   <sheetData>
     <row r="1" ht="21.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
-        <v>365</v>
+        <v>383</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>36</v>
@@ -10733,10 +10936,10 @@
         <v>89</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>366</v>
+        <v>384</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>367</v>
+        <v>385</v>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10747,16 +10950,16 @@
         <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>368</v>
+        <v>386</v>
       </c>
       <c r="D2" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E2" t="s">
         <v>61</v>
       </c>
       <c r="F2" t="s">
-        <v>370</v>
+        <v>388</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10767,16 +10970,16 @@
         <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>371</v>
+        <v>389</v>
       </c>
       <c r="D3" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E3" t="s">
         <v>60</v>
       </c>
       <c r="F3" t="s">
-        <v>372</v>
+        <v>390</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10787,16 +10990,16 @@
         <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>373</v>
+        <v>391</v>
       </c>
       <c r="D4" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E4" t="s">
         <v>60</v>
       </c>
       <c r="F4" t="s">
-        <v>374</v>
+        <v>392</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10807,16 +11010,16 @@
         <v>50</v>
       </c>
       <c r="C5" t="s">
-        <v>375</v>
+        <v>393</v>
       </c>
       <c r="D5" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E5" t="s">
         <v>64</v>
       </c>
       <c r="F5" t="s">
-        <v>376</v>
+        <v>394</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10827,16 +11030,16 @@
         <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>377</v>
+        <v>395</v>
       </c>
       <c r="D6" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E6" t="s">
         <v>62</v>
       </c>
       <c r="F6" t="s">
-        <v>378</v>
+        <v>396</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10850,13 +11053,13 @@
         <v>267</v>
       </c>
       <c r="D7" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E7" t="s">
         <v>66</v>
       </c>
       <c r="F7" t="s">
-        <v>379</v>
+        <v>397</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10867,16 +11070,16 @@
         <v>50</v>
       </c>
       <c r="C8" t="s">
-        <v>380</v>
+        <v>398</v>
       </c>
       <c r="D8" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E8" t="s">
         <v>61</v>
       </c>
       <c r="F8" t="s">
-        <v>381</v>
+        <v>399</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10887,16 +11090,16 @@
         <v>50</v>
       </c>
       <c r="C9" t="s">
-        <v>382</v>
+        <v>400</v>
       </c>
       <c r="D9" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E9" t="s">
         <v>61</v>
       </c>
       <c r="F9" t="s">
-        <v>383</v>
+        <v>401</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10907,16 +11110,16 @@
         <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>384</v>
+        <v>402</v>
       </c>
       <c r="D10" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E10" t="s">
         <v>60</v>
       </c>
       <c r="F10" t="s">
-        <v>385</v>
+        <v>403</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10927,16 +11130,16 @@
         <v>50</v>
       </c>
       <c r="C11" t="s">
-        <v>384</v>
+        <v>402</v>
       </c>
       <c r="D11" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E11" t="s">
         <v>61</v>
       </c>
       <c r="F11" t="s">
-        <v>386</v>
+        <v>404</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10947,16 +11150,16 @@
         <v>50</v>
       </c>
       <c r="C12" t="s">
-        <v>387</v>
+        <v>405</v>
       </c>
       <c r="D12" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E12" t="s">
         <v>63</v>
       </c>
       <c r="F12" t="s">
-        <v>388</v>
+        <v>406</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10967,16 +11170,16 @@
         <v>50</v>
       </c>
       <c r="C13" t="s">
-        <v>389</v>
+        <v>407</v>
       </c>
       <c r="D13" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E13" t="s">
         <v>61</v>
       </c>
       <c r="F13" t="s">
-        <v>390</v>
+        <v>408</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10987,16 +11190,16 @@
         <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>391</v>
+        <v>409</v>
       </c>
       <c r="D14" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E14" t="s">
         <v>61</v>
       </c>
       <c r="F14" t="s">
-        <v>392</v>
+        <v>410</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11007,16 +11210,16 @@
         <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>393</v>
+        <v>411</v>
       </c>
       <c r="D15" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E15" t="s">
         <v>61</v>
       </c>
       <c r="F15" t="s">
-        <v>394</v>
+        <v>412</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11027,16 +11230,16 @@
         <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>395</v>
+        <v>413</v>
       </c>
       <c r="D16" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E16" t="s">
         <v>61</v>
       </c>
       <c r="F16" t="s">
-        <v>396</v>
+        <v>414</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11047,16 +11250,16 @@
         <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="D17" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E17" t="s">
         <v>61</v>
       </c>
       <c r="F17" t="s">
-        <v>398</v>
+        <v>416</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11067,16 +11270,16 @@
         <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>399</v>
+        <v>417</v>
       </c>
       <c r="D18" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E18" t="s">
         <v>61</v>
       </c>
       <c r="F18" t="s">
-        <v>400</v>
+        <v>418</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11087,16 +11290,16 @@
         <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>401</v>
+        <v>419</v>
       </c>
       <c r="D19" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E19" t="s">
         <v>60</v>
       </c>
       <c r="F19" t="s">
-        <v>402</v>
+        <v>420</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11107,16 +11310,16 @@
         <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>403</v>
+        <v>421</v>
       </c>
       <c r="D20" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E20" t="s">
         <v>64</v>
       </c>
       <c r="F20" t="s">
-        <v>404</v>
+        <v>422</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11130,13 +11333,13 @@
         <v>254</v>
       </c>
       <c r="D21" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E21" t="s">
         <v>66</v>
       </c>
       <c r="F21" t="s">
-        <v>405</v>
+        <v>423</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11147,16 +11350,16 @@
         <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>384</v>
+        <v>402</v>
       </c>
       <c r="D22" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E22" t="s">
         <v>60</v>
       </c>
       <c r="F22" t="s">
-        <v>406</v>
+        <v>424</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11170,13 +11373,13 @@
         <v>254</v>
       </c>
       <c r="D23" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E23" t="s">
         <v>61</v>
       </c>
       <c r="F23" t="s">
-        <v>407</v>
+        <v>425</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11187,16 +11390,16 @@
         <v>50</v>
       </c>
       <c r="C24" t="s">
-        <v>408</v>
+        <v>426</v>
       </c>
       <c r="D24" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E24" t="s">
         <v>62</v>
       </c>
       <c r="F24" t="s">
-        <v>409</v>
+        <v>427</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11207,16 +11410,16 @@
         <v>50</v>
       </c>
       <c r="C25" t="s">
-        <v>371</v>
+        <v>389</v>
       </c>
       <c r="D25" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E25" t="s">
         <v>61</v>
       </c>
       <c r="F25" t="s">
-        <v>410</v>
+        <v>428</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11227,16 +11430,16 @@
         <v>50</v>
       </c>
       <c r="C26" t="s">
-        <v>411</v>
+        <v>429</v>
       </c>
       <c r="D26" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E26" t="s">
         <v>60</v>
       </c>
       <c r="F26" t="s">
-        <v>412</v>
+        <v>430</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11247,16 +11450,16 @@
         <v>50</v>
       </c>
       <c r="C27" t="s">
-        <v>413</v>
+        <v>431</v>
       </c>
       <c r="D27" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E27" t="s">
         <v>64</v>
       </c>
       <c r="F27" t="s">
-        <v>414</v>
+        <v>432</v>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11270,13 +11473,13 @@
         <v>239</v>
       </c>
       <c r="D28" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E28" t="s">
         <v>60</v>
       </c>
       <c r="F28" t="s">
-        <v>415</v>
+        <v>433</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11287,16 +11490,16 @@
         <v>50</v>
       </c>
       <c r="C29" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="D29" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E29" t="s">
         <v>60</v>
       </c>
       <c r="F29" t="s">
-        <v>417</v>
+        <v>435</v>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11307,16 +11510,16 @@
         <v>50</v>
       </c>
       <c r="C30" t="s">
-        <v>416</v>
+        <v>434</v>
       </c>
       <c r="D30" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E30" t="s">
         <v>60</v>
       </c>
       <c r="F30" t="s">
-        <v>418</v>
+        <v>436</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11327,16 +11530,16 @@
         <v>50</v>
       </c>
       <c r="C31" t="s">
-        <v>419</v>
+        <v>437</v>
       </c>
       <c r="D31" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E31" t="s">
         <v>60</v>
       </c>
       <c r="F31" t="s">
-        <v>420</v>
+        <v>438</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11347,16 +11550,16 @@
         <v>50</v>
       </c>
       <c r="C32" t="s">
-        <v>421</v>
+        <v>439</v>
       </c>
       <c r="D32" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E32" t="s">
         <v>60</v>
       </c>
       <c r="F32" t="s">
-        <v>422</v>
+        <v>440</v>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11370,13 +11573,13 @@
         <v>232</v>
       </c>
       <c r="D33" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E33" t="s">
         <v>61</v>
       </c>
       <c r="F33" t="s">
-        <v>423</v>
+        <v>441</v>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11387,16 +11590,16 @@
         <v>50</v>
       </c>
       <c r="C34" t="s">
-        <v>424</v>
+        <v>442</v>
       </c>
       <c r="D34" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E34" t="s">
         <v>60</v>
       </c>
       <c r="F34" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11407,16 +11610,16 @@
         <v>50</v>
       </c>
       <c r="C35" t="s">
-        <v>424</v>
+        <v>442</v>
       </c>
       <c r="D35" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E35" t="s">
         <v>61</v>
       </c>
       <c r="F35" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11427,16 +11630,16 @@
         <v>50</v>
       </c>
       <c r="C36" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="D36" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E36" t="s">
         <v>61</v>
       </c>
       <c r="F36" t="s">
-        <v>428</v>
+        <v>446</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11447,16 +11650,16 @@
         <v>50</v>
       </c>
       <c r="C37" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="D37" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E37" t="s">
         <v>63</v>
       </c>
       <c r="F37" t="s">
-        <v>429</v>
+        <v>447</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11467,16 +11670,16 @@
         <v>50</v>
       </c>
       <c r="C38" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="D38" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E38" t="s">
         <v>61</v>
       </c>
       <c r="F38" t="s">
-        <v>431</v>
+        <v>449</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11487,16 +11690,16 @@
         <v>50</v>
       </c>
       <c r="C39" t="s">
-        <v>432</v>
+        <v>450</v>
       </c>
       <c r="D39" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E39" t="s">
         <v>60</v>
       </c>
       <c r="F39" t="s">
-        <v>433</v>
+        <v>451</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11507,16 +11710,16 @@
         <v>50</v>
       </c>
       <c r="C40" t="s">
-        <v>434</v>
+        <v>452</v>
       </c>
       <c r="D40" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E40" t="s">
         <v>60</v>
       </c>
       <c r="F40" t="s">
-        <v>435</v>
+        <v>453</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11527,16 +11730,16 @@
         <v>50</v>
       </c>
       <c r="C41" t="s">
-        <v>436</v>
+        <v>454</v>
       </c>
       <c r="D41" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E41" t="s">
         <v>61</v>
       </c>
       <c r="F41" t="s">
-        <v>437</v>
+        <v>455</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11547,16 +11750,16 @@
         <v>50</v>
       </c>
       <c r="C42" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="D42" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E42" t="s">
         <v>63</v>
       </c>
       <c r="F42" t="s">
-        <v>439</v>
+        <v>457</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11567,16 +11770,16 @@
         <v>50</v>
       </c>
       <c r="C43" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="D43" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E43" t="s">
         <v>60</v>
       </c>
       <c r="F43" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11587,16 +11790,16 @@
         <v>50</v>
       </c>
       <c r="C44" t="s">
-        <v>441</v>
+        <v>459</v>
       </c>
       <c r="D44" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E44" t="s">
         <v>60</v>
       </c>
       <c r="F44" t="s">
-        <v>442</v>
+        <v>460</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11607,16 +11810,16 @@
         <v>50</v>
       </c>
       <c r="C45" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="D45" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E45" t="s">
         <v>61</v>
       </c>
       <c r="F45" t="s">
-        <v>443</v>
+        <v>461</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11627,16 +11830,16 @@
         <v>50</v>
       </c>
       <c r="C46" t="s">
-        <v>434</v>
+        <v>452</v>
       </c>
       <c r="D46" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E46" t="s">
         <v>60</v>
       </c>
       <c r="F46" t="s">
-        <v>444</v>
+        <v>462</v>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11647,16 +11850,16 @@
         <v>50</v>
       </c>
       <c r="C47" t="s">
-        <v>445</v>
+        <v>463</v>
       </c>
       <c r="D47" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E47" t="s">
         <v>60</v>
       </c>
       <c r="F47" t="s">
-        <v>446</v>
+        <v>464</v>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11667,16 +11870,16 @@
         <v>50</v>
       </c>
       <c r="C48" t="s">
-        <v>447</v>
+        <v>465</v>
       </c>
       <c r="D48" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E48" t="s">
         <v>64</v>
       </c>
       <c r="F48" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11687,16 +11890,16 @@
         <v>50</v>
       </c>
       <c r="C49" t="s">
-        <v>449</v>
+        <v>467</v>
       </c>
       <c r="D49" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E49" t="s">
         <v>61</v>
       </c>
       <c r="F49" t="s">
-        <v>450</v>
+        <v>468</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11707,16 +11910,16 @@
         <v>50</v>
       </c>
       <c r="C50" t="s">
-        <v>451</v>
+        <v>469</v>
       </c>
       <c r="D50" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E50" t="s">
         <v>64</v>
       </c>
       <c r="F50" t="s">
-        <v>452</v>
+        <v>470</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11727,16 +11930,16 @@
         <v>50</v>
       </c>
       <c r="C51" t="s">
-        <v>453</v>
+        <v>471</v>
       </c>
       <c r="D51" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E51" t="s">
         <v>65</v>
       </c>
       <c r="F51" t="s">
-        <v>454</v>
+        <v>472</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11747,16 +11950,16 @@
         <v>50</v>
       </c>
       <c r="C52" t="s">
-        <v>455</v>
+        <v>473</v>
       </c>
       <c r="D52" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E52" t="s">
         <v>61</v>
       </c>
       <c r="F52" t="s">
-        <v>456</v>
+        <v>474</v>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11767,16 +11970,16 @@
         <v>50</v>
       </c>
       <c r="C53" t="s">
-        <v>457</v>
+        <v>475</v>
       </c>
       <c r="D53" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E53" t="s">
         <v>61</v>
       </c>
       <c r="F53" t="s">
-        <v>458</v>
+        <v>476</v>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11787,16 +11990,16 @@
         <v>50</v>
       </c>
       <c r="C54" t="s">
-        <v>459</v>
+        <v>477</v>
       </c>
       <c r="D54" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E54" t="s">
         <v>61</v>
       </c>
       <c r="F54" t="s">
-        <v>460</v>
+        <v>478</v>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11807,16 +12010,16 @@
         <v>50</v>
       </c>
       <c r="C55" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="D55" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E55" t="s">
         <v>60</v>
       </c>
       <c r="F55" t="s">
-        <v>462</v>
+        <v>480</v>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11827,16 +12030,16 @@
         <v>50</v>
       </c>
       <c r="C56" t="s">
-        <v>463</v>
+        <v>481</v>
       </c>
       <c r="D56" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E56" t="s">
         <v>64</v>
       </c>
       <c r="F56" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11847,16 +12050,16 @@
         <v>50</v>
       </c>
       <c r="C57" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="D57" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E57" t="s">
         <v>61</v>
       </c>
       <c r="F57" t="s">
-        <v>465</v>
+        <v>483</v>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11867,16 +12070,16 @@
         <v>50</v>
       </c>
       <c r="C58" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="D58" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E58" t="s">
         <v>61</v>
       </c>
       <c r="F58" t="s">
-        <v>466</v>
+        <v>484</v>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11887,16 +12090,16 @@
         <v>50</v>
       </c>
       <c r="C59" t="s">
-        <v>467</v>
+        <v>485</v>
       </c>
       <c r="D59" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E59" t="s">
         <v>61</v>
       </c>
       <c r="F59" t="s">
-        <v>468</v>
+        <v>486</v>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11907,16 +12110,16 @@
         <v>50</v>
       </c>
       <c r="C60" t="s">
-        <v>469</v>
+        <v>487</v>
       </c>
       <c r="D60" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E60" t="s">
         <v>61</v>
       </c>
       <c r="F60" t="s">
-        <v>470</v>
+        <v>488</v>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11927,16 +12130,16 @@
         <v>50</v>
       </c>
       <c r="C61" t="s">
-        <v>471</v>
+        <v>489</v>
       </c>
       <c r="D61" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E61" t="s">
         <v>60</v>
       </c>
       <c r="F61" t="s">
-        <v>472</v>
+        <v>490</v>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11947,16 +12150,16 @@
         <v>50</v>
       </c>
       <c r="C62" t="s">
-        <v>473</v>
+        <v>491</v>
       </c>
       <c r="D62" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E62" t="s">
         <v>61</v>
       </c>
       <c r="F62" t="s">
-        <v>474</v>
+        <v>492</v>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11967,16 +12170,16 @@
         <v>50</v>
       </c>
       <c r="C63" t="s">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="D63" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E63" t="s">
         <v>61</v>
       </c>
       <c r="F63" t="s">
-        <v>476</v>
+        <v>494</v>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11987,16 +12190,16 @@
         <v>50</v>
       </c>
       <c r="C64" t="s">
-        <v>477</v>
+        <v>495</v>
       </c>
       <c r="D64" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E64" t="s">
         <v>61</v>
       </c>
       <c r="F64" t="s">
-        <v>478</v>
+        <v>496</v>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12007,16 +12210,16 @@
         <v>50</v>
       </c>
       <c r="C65" t="s">
-        <v>479</v>
+        <v>497</v>
       </c>
       <c r="D65" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E65" t="s">
         <v>61</v>
       </c>
       <c r="F65" t="s">
-        <v>480</v>
+        <v>498</v>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12030,13 +12233,13 @@
         <v>279</v>
       </c>
       <c r="D66" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E66" t="s">
         <v>60</v>
       </c>
       <c r="F66" t="s">
-        <v>481</v>
+        <v>499</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12047,16 +12250,16 @@
         <v>50</v>
       </c>
       <c r="C67" t="s">
-        <v>482</v>
+        <v>500</v>
       </c>
       <c r="D67" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E67" t="s">
         <v>61</v>
       </c>
       <c r="F67" t="s">
-        <v>483</v>
+        <v>501</v>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12067,16 +12270,16 @@
         <v>50</v>
       </c>
       <c r="C68" t="s">
-        <v>484</v>
+        <v>502</v>
       </c>
       <c r="D68" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E68" t="s">
         <v>61</v>
       </c>
       <c r="F68" t="s">
-        <v>485</v>
+        <v>503</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12090,13 +12293,13 @@
         <v>279</v>
       </c>
       <c r="D69" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E69" t="s">
         <v>60</v>
       </c>
       <c r="F69" t="s">
-        <v>486</v>
+        <v>504</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12107,16 +12310,16 @@
         <v>50</v>
       </c>
       <c r="C70" t="s">
-        <v>487</v>
+        <v>505</v>
       </c>
       <c r="D70" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E70" t="s">
         <v>61</v>
       </c>
       <c r="F70" t="s">
-        <v>488</v>
+        <v>506</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12127,16 +12330,16 @@
         <v>50</v>
       </c>
       <c r="C71" t="s">
-        <v>489</v>
+        <v>507</v>
       </c>
       <c r="D71" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E71" t="s">
         <v>61</v>
       </c>
       <c r="F71" t="s">
-        <v>490</v>
+        <v>508</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12147,16 +12350,16 @@
         <v>50</v>
       </c>
       <c r="C72" t="s">
-        <v>491</v>
+        <v>509</v>
       </c>
       <c r="D72" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E72" t="s">
         <v>61</v>
       </c>
       <c r="F72" t="s">
-        <v>492</v>
+        <v>510</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12167,16 +12370,16 @@
         <v>50</v>
       </c>
       <c r="C73" t="s">
-        <v>493</v>
+        <v>511</v>
       </c>
       <c r="D73" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E73" t="s">
         <v>60</v>
       </c>
       <c r="F73" t="s">
-        <v>494</v>
+        <v>512</v>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12187,16 +12390,16 @@
         <v>50</v>
       </c>
       <c r="C74" t="s">
-        <v>495</v>
+        <v>513</v>
       </c>
       <c r="D74" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E74" t="s">
         <v>61</v>
       </c>
       <c r="F74" t="s">
-        <v>496</v>
+        <v>514</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12207,16 +12410,16 @@
         <v>50</v>
       </c>
       <c r="C75" t="s">
-        <v>497</v>
+        <v>515</v>
       </c>
       <c r="D75" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E75" t="s">
         <v>61</v>
       </c>
       <c r="F75" t="s">
-        <v>498</v>
+        <v>516</v>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12227,16 +12430,16 @@
         <v>50</v>
       </c>
       <c r="C76" t="s">
-        <v>499</v>
+        <v>517</v>
       </c>
       <c r="D76" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E76" t="s">
         <v>61</v>
       </c>
       <c r="F76" t="s">
-        <v>500</v>
+        <v>518</v>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12247,16 +12450,16 @@
         <v>50</v>
       </c>
       <c r="C77" t="s">
-        <v>501</v>
+        <v>519</v>
       </c>
       <c r="D77" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E77" t="s">
         <v>61</v>
       </c>
       <c r="F77" t="s">
-        <v>502</v>
+        <v>520</v>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12267,16 +12470,16 @@
         <v>50</v>
       </c>
       <c r="C78" t="s">
-        <v>445</v>
+        <v>463</v>
       </c>
       <c r="D78" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E78" t="s">
         <v>61</v>
       </c>
       <c r="F78" t="s">
-        <v>503</v>
+        <v>521</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12287,16 +12490,16 @@
         <v>50</v>
       </c>
       <c r="C79" t="s">
-        <v>504</v>
+        <v>522</v>
       </c>
       <c r="D79" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E79" t="s">
         <v>61</v>
       </c>
       <c r="F79" t="s">
-        <v>505</v>
+        <v>523</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12307,16 +12510,16 @@
         <v>50</v>
       </c>
       <c r="C80" t="s">
-        <v>434</v>
+        <v>452</v>
       </c>
       <c r="D80" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E80" t="s">
         <v>60</v>
       </c>
       <c r="F80" t="s">
-        <v>506</v>
+        <v>524</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12327,16 +12530,16 @@
         <v>50</v>
       </c>
       <c r="C81" t="s">
-        <v>507</v>
+        <v>525</v>
       </c>
       <c r="D81" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E81" t="s">
         <v>60</v>
       </c>
       <c r="F81" t="s">
-        <v>508</v>
+        <v>526</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12347,16 +12550,16 @@
         <v>50</v>
       </c>
       <c r="C82" t="s">
-        <v>509</v>
+        <v>527</v>
       </c>
       <c r="D82" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E82" t="s">
         <v>60</v>
       </c>
       <c r="F82" t="s">
-        <v>510</v>
+        <v>528</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12367,16 +12570,16 @@
         <v>50</v>
       </c>
       <c r="C83" t="s">
-        <v>511</v>
+        <v>529</v>
       </c>
       <c r="D83" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E83" t="s">
         <v>60</v>
       </c>
       <c r="F83" t="s">
-        <v>512</v>
+        <v>530</v>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12387,16 +12590,16 @@
         <v>50</v>
       </c>
       <c r="C84" t="s">
-        <v>513</v>
+        <v>531</v>
       </c>
       <c r="D84" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E84" t="s">
         <v>60</v>
       </c>
       <c r="F84" t="s">
-        <v>514</v>
+        <v>532</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12407,16 +12610,16 @@
         <v>50</v>
       </c>
       <c r="C85" t="s">
-        <v>515</v>
+        <v>533</v>
       </c>
       <c r="D85" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E85" t="s">
         <v>60</v>
       </c>
       <c r="F85" t="s">
-        <v>516</v>
+        <v>534</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12427,16 +12630,16 @@
         <v>50</v>
       </c>
       <c r="C86" t="s">
-        <v>368</v>
+        <v>386</v>
       </c>
       <c r="D86" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E86" t="s">
         <v>61</v>
       </c>
       <c r="F86" t="s">
-        <v>517</v>
+        <v>535</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12447,16 +12650,16 @@
         <v>50</v>
       </c>
       <c r="C87" t="s">
-        <v>518</v>
+        <v>536</v>
       </c>
       <c r="D87" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E87" t="s">
         <v>61</v>
       </c>
       <c r="F87" t="s">
-        <v>519</v>
+        <v>537</v>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12467,16 +12670,16 @@
         <v>50</v>
       </c>
       <c r="C88" t="s">
-        <v>447</v>
+        <v>465</v>
       </c>
       <c r="D88" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E88" t="s">
         <v>61</v>
       </c>
       <c r="F88" t="s">
-        <v>520</v>
+        <v>538</v>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12487,16 +12690,16 @@
         <v>50</v>
       </c>
       <c r="C89" t="s">
-        <v>521</v>
+        <v>539</v>
       </c>
       <c r="D89" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E89" t="s">
         <v>63</v>
       </c>
       <c r="F89" t="s">
-        <v>522</v>
+        <v>540</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12507,16 +12710,16 @@
         <v>50</v>
       </c>
       <c r="C90" t="s">
-        <v>523</v>
+        <v>541</v>
       </c>
       <c r="D90" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E90" t="s">
         <v>60</v>
       </c>
       <c r="F90" t="s">
-        <v>524</v>
+        <v>542</v>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12527,16 +12730,16 @@
         <v>50</v>
       </c>
       <c r="C91" t="s">
-        <v>525</v>
+        <v>543</v>
       </c>
       <c r="D91" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E91" t="s">
         <v>60</v>
       </c>
       <c r="F91" t="s">
-        <v>526</v>
+        <v>544</v>
       </c>
     </row>
     <row r="92" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12547,16 +12750,16 @@
         <v>50</v>
       </c>
       <c r="C92" t="s">
-        <v>527</v>
+        <v>545</v>
       </c>
       <c r="D92" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E92" t="s">
         <v>61</v>
       </c>
       <c r="F92" t="s">
-        <v>528</v>
+        <v>546</v>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12567,16 +12770,16 @@
         <v>50</v>
       </c>
       <c r="C93" t="s">
-        <v>529</v>
+        <v>547</v>
       </c>
       <c r="D93" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E93" t="s">
         <v>61</v>
       </c>
       <c r="F93" t="s">
-        <v>530</v>
+        <v>548</v>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12587,16 +12790,16 @@
         <v>50</v>
       </c>
       <c r="C94" t="s">
-        <v>531</v>
+        <v>549</v>
       </c>
       <c r="D94" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E94" t="s">
         <v>60</v>
       </c>
       <c r="F94" t="s">
-        <v>532</v>
+        <v>550</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12607,16 +12810,16 @@
         <v>50</v>
       </c>
       <c r="C95" t="s">
-        <v>533</v>
+        <v>551</v>
       </c>
       <c r="D95" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E95" t="s">
         <v>60</v>
       </c>
       <c r="F95" t="s">
-        <v>534</v>
+        <v>552</v>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12627,16 +12830,16 @@
         <v>50</v>
       </c>
       <c r="C96" t="s">
-        <v>535</v>
+        <v>553</v>
       </c>
       <c r="D96" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E96" t="s">
         <v>64</v>
       </c>
       <c r="F96" t="s">
-        <v>536</v>
+        <v>554</v>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12647,16 +12850,16 @@
         <v>50</v>
       </c>
       <c r="C97" t="s">
-        <v>513</v>
+        <v>531</v>
       </c>
       <c r="D97" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E97" t="s">
         <v>61</v>
       </c>
       <c r="F97" t="s">
-        <v>537</v>
+        <v>555</v>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12667,16 +12870,16 @@
         <v>50</v>
       </c>
       <c r="C98" t="s">
-        <v>538</v>
+        <v>556</v>
       </c>
       <c r="D98" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E98" t="s">
         <v>60</v>
       </c>
       <c r="F98" t="s">
-        <v>539</v>
+        <v>557</v>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12687,16 +12890,16 @@
         <v>50</v>
       </c>
       <c r="C99" t="s">
-        <v>540</v>
+        <v>558</v>
       </c>
       <c r="D99" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E99" t="s">
         <v>65</v>
       </c>
       <c r="F99" t="s">
-        <v>541</v>
+        <v>559</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12707,16 +12910,16 @@
         <v>50</v>
       </c>
       <c r="C100" t="s">
-        <v>542</v>
+        <v>560</v>
       </c>
       <c r="D100" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E100" t="s">
         <v>64</v>
       </c>
       <c r="F100" t="s">
-        <v>543</v>
+        <v>561</v>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12727,16 +12930,16 @@
         <v>50</v>
       </c>
       <c r="C101" t="s">
-        <v>544</v>
+        <v>562</v>
       </c>
       <c r="D101" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E101" t="s">
         <v>61</v>
       </c>
       <c r="F101" t="s">
-        <v>545</v>
+        <v>563</v>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12747,16 +12950,16 @@
         <v>50</v>
       </c>
       <c r="C102" t="s">
-        <v>546</v>
+        <v>564</v>
       </c>
       <c r="D102" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E102" t="s">
         <v>61</v>
       </c>
       <c r="F102" t="s">
-        <v>547</v>
+        <v>565</v>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12767,16 +12970,16 @@
         <v>50</v>
       </c>
       <c r="C103" t="s">
-        <v>548</v>
+        <v>566</v>
       </c>
       <c r="D103" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E103" t="s">
         <v>62</v>
       </c>
       <c r="F103" t="s">
-        <v>549</v>
+        <v>567</v>
       </c>
     </row>
     <row r="104" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12787,16 +12990,16 @@
         <v>50</v>
       </c>
       <c r="C104" t="s">
-        <v>550</v>
+        <v>568</v>
       </c>
       <c r="D104" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E104" t="s">
         <v>60</v>
       </c>
       <c r="F104" t="s">
-        <v>551</v>
+        <v>569</v>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12807,16 +13010,16 @@
         <v>50</v>
       </c>
       <c r="C105" t="s">
-        <v>552</v>
+        <v>570</v>
       </c>
       <c r="D105" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E105" t="s">
         <v>60</v>
       </c>
       <c r="F105" t="s">
-        <v>553</v>
+        <v>571</v>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12827,16 +13030,16 @@
         <v>50</v>
       </c>
       <c r="C106" t="s">
-        <v>554</v>
+        <v>572</v>
       </c>
       <c r="D106" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E106" t="s">
         <v>63</v>
       </c>
       <c r="F106" t="s">
-        <v>555</v>
+        <v>573</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12847,16 +13050,16 @@
         <v>50</v>
       </c>
       <c r="C107" t="s">
-        <v>556</v>
+        <v>574</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E107" t="s">
         <v>61</v>
       </c>
       <c r="F107" t="s">
-        <v>557</v>
+        <v>575</v>
       </c>
     </row>
     <row r="108" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12867,16 +13070,16 @@
         <v>50</v>
       </c>
       <c r="C108" t="s">
-        <v>558</v>
+        <v>576</v>
       </c>
       <c r="D108" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E108" t="s">
         <v>60</v>
       </c>
       <c r="F108" t="s">
-        <v>559</v>
+        <v>577</v>
       </c>
     </row>
     <row r="109" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12887,16 +13090,16 @@
         <v>50</v>
       </c>
       <c r="C109" t="s">
-        <v>560</v>
+        <v>578</v>
       </c>
       <c r="D109" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E109" t="s">
         <v>60</v>
       </c>
       <c r="F109" t="s">
-        <v>561</v>
+        <v>579</v>
       </c>
     </row>
     <row r="110" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12907,16 +13110,16 @@
         <v>50</v>
       </c>
       <c r="C110" t="s">
-        <v>562</v>
+        <v>373</v>
       </c>
       <c r="D110" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E110" t="s">
         <v>61</v>
       </c>
       <c r="F110" t="s">
-        <v>563</v>
+        <v>580</v>
       </c>
     </row>
     <row r="111" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12927,16 +13130,16 @@
         <v>50</v>
       </c>
       <c r="C111" t="s">
-        <v>564</v>
+        <v>581</v>
       </c>
       <c r="D111" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E111" t="s">
         <v>60</v>
       </c>
       <c r="F111" t="s">
-        <v>565</v>
+        <v>582</v>
       </c>
     </row>
     <row r="112" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12947,16 +13150,16 @@
         <v>50</v>
       </c>
       <c r="C112" t="s">
-        <v>566</v>
+        <v>583</v>
       </c>
       <c r="D112" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E112" t="s">
         <v>60</v>
       </c>
       <c r="F112" t="s">
-        <v>567</v>
+        <v>584</v>
       </c>
     </row>
     <row r="113" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12967,16 +13170,16 @@
         <v>51</v>
       </c>
       <c r="C113" t="s">
-        <v>568</v>
+        <v>585</v>
       </c>
       <c r="D113" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E113" t="s">
         <v>60</v>
       </c>
       <c r="F113" t="s">
-        <v>569</v>
+        <v>586</v>
       </c>
     </row>
     <row r="114" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12987,16 +13190,16 @@
         <v>51</v>
       </c>
       <c r="C114" t="s">
-        <v>568</v>
+        <v>585</v>
       </c>
       <c r="D114" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E114" t="s">
         <v>60</v>
       </c>
       <c r="F114" t="s">
-        <v>570</v>
+        <v>587</v>
       </c>
     </row>
     <row r="115" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13007,16 +13210,16 @@
         <v>51</v>
       </c>
       <c r="C115" t="s">
-        <v>571</v>
+        <v>588</v>
       </c>
       <c r="D115" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E115" t="s">
         <v>60</v>
       </c>
       <c r="F115" t="s">
-        <v>572</v>
+        <v>589</v>
       </c>
     </row>
     <row r="116" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13027,16 +13230,16 @@
         <v>51</v>
       </c>
       <c r="C116" t="s">
-        <v>573</v>
+        <v>590</v>
       </c>
       <c r="D116" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E116" t="s">
         <v>60</v>
       </c>
       <c r="F116" t="s">
-        <v>574</v>
+        <v>591</v>
       </c>
     </row>
     <row r="117" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13050,13 +13253,13 @@
         <v>159</v>
       </c>
       <c r="D117" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E117" t="s">
         <v>60</v>
       </c>
       <c r="F117" t="s">
-        <v>575</v>
+        <v>592</v>
       </c>
     </row>
     <row r="118" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13067,16 +13270,16 @@
         <v>51</v>
       </c>
       <c r="C118" t="s">
-        <v>576</v>
+        <v>593</v>
       </c>
       <c r="D118" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E118" t="s">
         <v>60</v>
       </c>
       <c r="F118" t="s">
-        <v>577</v>
+        <v>594</v>
       </c>
     </row>
     <row r="119" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13087,16 +13290,16 @@
         <v>51</v>
       </c>
       <c r="C119" t="s">
-        <v>578</v>
+        <v>595</v>
       </c>
       <c r="D119" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E119" t="s">
         <v>63</v>
       </c>
       <c r="F119" t="s">
-        <v>579</v>
+        <v>596</v>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13107,16 +13310,16 @@
         <v>51</v>
       </c>
       <c r="C120" t="s">
-        <v>580</v>
+        <v>597</v>
       </c>
       <c r="D120" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E120" t="s">
         <v>63</v>
       </c>
       <c r="F120" t="s">
-        <v>581</v>
+        <v>598</v>
       </c>
     </row>
     <row r="121" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13127,16 +13330,16 @@
         <v>51</v>
       </c>
       <c r="C121" t="s">
-        <v>580</v>
+        <v>597</v>
       </c>
       <c r="D121" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E121" t="s">
         <v>61</v>
       </c>
       <c r="F121" t="s">
-        <v>582</v>
+        <v>599</v>
       </c>
     </row>
     <row r="122" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13147,16 +13350,16 @@
         <v>51</v>
       </c>
       <c r="C122" t="s">
-        <v>583</v>
+        <v>600</v>
       </c>
       <c r="D122" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E122" t="s">
         <v>60</v>
       </c>
       <c r="F122" t="s">
-        <v>584</v>
+        <v>601</v>
       </c>
     </row>
     <row r="123" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13167,16 +13370,16 @@
         <v>51</v>
       </c>
       <c r="C123" t="s">
-        <v>585</v>
+        <v>602</v>
       </c>
       <c r="D123" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E123" t="s">
         <v>60</v>
       </c>
       <c r="F123" t="s">
-        <v>586</v>
+        <v>603</v>
       </c>
     </row>
     <row r="124" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13187,16 +13390,16 @@
         <v>51</v>
       </c>
       <c r="C124" t="s">
-        <v>587</v>
+        <v>604</v>
       </c>
       <c r="D124" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E124" t="s">
         <v>65</v>
       </c>
       <c r="F124" t="s">
-        <v>588</v>
+        <v>605</v>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13210,13 +13413,13 @@
         <v>232</v>
       </c>
       <c r="D125" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E125" t="s">
         <v>64</v>
       </c>
       <c r="F125" t="s">
-        <v>589</v>
+        <v>606</v>
       </c>
     </row>
     <row r="126" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13227,16 +13430,16 @@
         <v>51</v>
       </c>
       <c r="C126" t="s">
-        <v>590</v>
+        <v>607</v>
       </c>
       <c r="D126" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E126" t="s">
         <v>60</v>
       </c>
       <c r="F126" t="s">
-        <v>591</v>
+        <v>608</v>
       </c>
     </row>
     <row r="127" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13247,16 +13450,16 @@
         <v>51</v>
       </c>
       <c r="C127" t="s">
-        <v>592</v>
+        <v>609</v>
       </c>
       <c r="D127" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E127" t="s">
         <v>60</v>
       </c>
       <c r="F127" t="s">
-        <v>593</v>
+        <v>610</v>
       </c>
     </row>
     <row r="128" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13267,16 +13470,16 @@
         <v>51</v>
       </c>
       <c r="C128" t="s">
-        <v>592</v>
+        <v>609</v>
       </c>
       <c r="D128" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E128" t="s">
         <v>64</v>
       </c>
       <c r="F128" t="s">
-        <v>594</v>
+        <v>611</v>
       </c>
     </row>
     <row r="129" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13287,16 +13490,16 @@
         <v>51</v>
       </c>
       <c r="C129" t="s">
-        <v>595</v>
+        <v>612</v>
       </c>
       <c r="D129" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E129" t="s">
         <v>63</v>
       </c>
       <c r="F129" t="s">
-        <v>596</v>
+        <v>613</v>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13307,16 +13510,16 @@
         <v>51</v>
       </c>
       <c r="C130" t="s">
-        <v>597</v>
+        <v>614</v>
       </c>
       <c r="D130" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E130" t="s">
         <v>63</v>
       </c>
       <c r="F130" t="s">
-        <v>598</v>
+        <v>615</v>
       </c>
     </row>
     <row r="131" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13327,16 +13530,16 @@
         <v>51</v>
       </c>
       <c r="C131" t="s">
-        <v>599</v>
+        <v>616</v>
       </c>
       <c r="D131" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E131" t="s">
         <v>60</v>
       </c>
       <c r="F131" t="s">
-        <v>600</v>
+        <v>617</v>
       </c>
     </row>
     <row r="132" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13347,16 +13550,16 @@
         <v>51</v>
       </c>
       <c r="C132" t="s">
-        <v>601</v>
+        <v>618</v>
       </c>
       <c r="D132" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E132" t="s">
         <v>60</v>
       </c>
       <c r="F132" t="s">
-        <v>602</v>
+        <v>619</v>
       </c>
     </row>
     <row r="133" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13367,16 +13570,16 @@
         <v>51</v>
       </c>
       <c r="C133" t="s">
-        <v>603</v>
+        <v>620</v>
       </c>
       <c r="D133" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E133" t="s">
         <v>60</v>
       </c>
       <c r="F133" t="s">
-        <v>604</v>
+        <v>621</v>
       </c>
     </row>
     <row r="134" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13387,16 +13590,16 @@
         <v>51</v>
       </c>
       <c r="C134" t="s">
-        <v>605</v>
+        <v>622</v>
       </c>
       <c r="D134" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E134" t="s">
         <v>62</v>
       </c>
       <c r="F134" t="s">
-        <v>606</v>
+        <v>623</v>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13410,13 +13613,13 @@
         <v>159</v>
       </c>
       <c r="D135" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E135" t="s">
         <v>60</v>
       </c>
       <c r="F135" t="s">
-        <v>607</v>
+        <v>624</v>
       </c>
     </row>
     <row r="136" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13427,16 +13630,16 @@
         <v>51</v>
       </c>
       <c r="C136" t="s">
-        <v>608</v>
+        <v>625</v>
       </c>
       <c r="D136" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E136" t="s">
         <v>60</v>
       </c>
       <c r="F136" t="s">
-        <v>609</v>
+        <v>626</v>
       </c>
     </row>
     <row r="137" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13447,16 +13650,16 @@
         <v>51</v>
       </c>
       <c r="C137" t="s">
-        <v>608</v>
+        <v>625</v>
       </c>
       <c r="D137" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E137" t="s">
         <v>60</v>
       </c>
       <c r="F137" t="s">
-        <v>610</v>
+        <v>627</v>
       </c>
     </row>
     <row r="138" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13467,16 +13670,16 @@
         <v>51</v>
       </c>
       <c r="C138" t="s">
-        <v>611</v>
+        <v>628</v>
       </c>
       <c r="D138" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E138" t="s">
         <v>60</v>
       </c>
       <c r="F138" t="s">
-        <v>612</v>
+        <v>629</v>
       </c>
     </row>
     <row r="139" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13487,16 +13690,16 @@
         <v>51</v>
       </c>
       <c r="C139" t="s">
-        <v>613</v>
+        <v>630</v>
       </c>
       <c r="D139" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E139" t="s">
         <v>60</v>
       </c>
       <c r="F139" t="s">
-        <v>614</v>
+        <v>631</v>
       </c>
     </row>
     <row r="140" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13507,16 +13710,16 @@
         <v>51</v>
       </c>
       <c r="C140" t="s">
-        <v>613</v>
+        <v>630</v>
       </c>
       <c r="D140" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E140" t="s">
         <v>60</v>
       </c>
       <c r="F140" t="s">
-        <v>615</v>
+        <v>632</v>
       </c>
     </row>
     <row r="141" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13527,16 +13730,16 @@
         <v>51</v>
       </c>
       <c r="C141" t="s">
-        <v>613</v>
+        <v>630</v>
       </c>
       <c r="D141" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E141" t="s">
         <v>60</v>
       </c>
       <c r="F141" t="s">
-        <v>616</v>
+        <v>633</v>
       </c>
     </row>
     <row r="142" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13547,16 +13750,16 @@
         <v>51</v>
       </c>
       <c r="C142" t="s">
-        <v>617</v>
+        <v>634</v>
       </c>
       <c r="D142" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E142" t="s">
         <v>60</v>
       </c>
       <c r="F142" t="s">
-        <v>618</v>
+        <v>635</v>
       </c>
     </row>
     <row r="143" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13567,16 +13770,16 @@
         <v>51</v>
       </c>
       <c r="C143" t="s">
-        <v>619</v>
+        <v>636</v>
       </c>
       <c r="D143" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E143" t="s">
         <v>60</v>
       </c>
       <c r="F143" t="s">
-        <v>620</v>
+        <v>637</v>
       </c>
     </row>
     <row r="144" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13587,16 +13790,16 @@
         <v>51</v>
       </c>
       <c r="C144" t="s">
-        <v>621</v>
+        <v>638</v>
       </c>
       <c r="D144" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E144" t="s">
         <v>65</v>
       </c>
       <c r="F144" t="s">
-        <v>622</v>
+        <v>639</v>
       </c>
     </row>
     <row r="145" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13607,16 +13810,16 @@
         <v>51</v>
       </c>
       <c r="C145" t="s">
-        <v>571</v>
+        <v>588</v>
       </c>
       <c r="D145" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E145" t="s">
         <v>60</v>
       </c>
       <c r="F145" t="s">
-        <v>623</v>
+        <v>640</v>
       </c>
     </row>
     <row r="146" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13627,16 +13830,16 @@
         <v>51</v>
       </c>
       <c r="C146" t="s">
-        <v>571</v>
+        <v>588</v>
       </c>
       <c r="D146" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E146" t="s">
         <v>60</v>
       </c>
       <c r="F146" t="s">
-        <v>624</v>
+        <v>641</v>
       </c>
     </row>
     <row r="147" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13647,16 +13850,16 @@
         <v>49</v>
       </c>
       <c r="C147" t="s">
-        <v>625</v>
+        <v>642</v>
       </c>
       <c r="D147" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E147" t="s">
         <v>60</v>
       </c>
       <c r="F147" t="s">
-        <v>626</v>
+        <v>643</v>
       </c>
     </row>
     <row r="148" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13670,13 +13873,13 @@
         <v>182</v>
       </c>
       <c r="D148" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E148" t="s">
         <v>60</v>
       </c>
       <c r="F148" t="s">
-        <v>627</v>
+        <v>644</v>
       </c>
     </row>
     <row r="149" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13687,16 +13890,16 @@
         <v>49</v>
       </c>
       <c r="C149" t="s">
-        <v>628</v>
+        <v>645</v>
       </c>
       <c r="D149" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E149" t="s">
         <v>60</v>
       </c>
       <c r="F149" t="s">
-        <v>629</v>
+        <v>646</v>
       </c>
     </row>
     <row r="150" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13707,16 +13910,16 @@
         <v>49</v>
       </c>
       <c r="C150" t="s">
-        <v>630</v>
+        <v>647</v>
       </c>
       <c r="D150" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E150" t="s">
         <v>60</v>
       </c>
       <c r="F150" t="s">
-        <v>631</v>
+        <v>648</v>
       </c>
     </row>
     <row r="151" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13727,16 +13930,16 @@
         <v>49</v>
       </c>
       <c r="C151" t="s">
-        <v>632</v>
+        <v>649</v>
       </c>
       <c r="D151" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E151" t="s">
         <v>60</v>
       </c>
       <c r="F151" t="s">
-        <v>633</v>
+        <v>650</v>
       </c>
     </row>
     <row r="152" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13747,16 +13950,16 @@
         <v>49</v>
       </c>
       <c r="C152" t="s">
-        <v>634</v>
+        <v>651</v>
       </c>
       <c r="D152" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E152" t="s">
         <v>61</v>
       </c>
       <c r="F152" t="s">
-        <v>635</v>
+        <v>652</v>
       </c>
     </row>
     <row r="153" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13767,16 +13970,16 @@
         <v>49</v>
       </c>
       <c r="C153" t="s">
-        <v>636</v>
+        <v>653</v>
       </c>
       <c r="D153" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E153" t="s">
         <v>60</v>
       </c>
       <c r="F153" t="s">
-        <v>637</v>
+        <v>654</v>
       </c>
     </row>
     <row r="154" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13787,16 +13990,16 @@
         <v>49</v>
       </c>
       <c r="C154" t="s">
-        <v>638</v>
+        <v>655</v>
       </c>
       <c r="D154" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E154" t="s">
         <v>60</v>
       </c>
       <c r="F154" t="s">
-        <v>639</v>
+        <v>656</v>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13807,16 +14010,16 @@
         <v>49</v>
       </c>
       <c r="C155" t="s">
-        <v>638</v>
+        <v>655</v>
       </c>
       <c r="D155" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E155" t="s">
         <v>60</v>
       </c>
       <c r="F155" t="s">
-        <v>640</v>
+        <v>657</v>
       </c>
     </row>
     <row r="156" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13827,16 +14030,16 @@
         <v>49</v>
       </c>
       <c r="C156" t="s">
-        <v>641</v>
+        <v>658</v>
       </c>
       <c r="D156" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E156" t="s">
         <v>63</v>
       </c>
       <c r="F156" t="s">
-        <v>642</v>
+        <v>659</v>
       </c>
     </row>
     <row r="157" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13847,16 +14050,16 @@
         <v>49</v>
       </c>
       <c r="C157" t="s">
-        <v>643</v>
+        <v>660</v>
       </c>
       <c r="D157" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E157" t="s">
         <v>60</v>
       </c>
       <c r="F157" t="s">
-        <v>644</v>
+        <v>661</v>
       </c>
     </row>
     <row r="158" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13870,13 +14073,13 @@
         <v>247</v>
       </c>
       <c r="D158" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E158" t="s">
         <v>60</v>
       </c>
       <c r="F158" t="s">
-        <v>645</v>
+        <v>662</v>
       </c>
     </row>
     <row r="159" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13887,16 +14090,16 @@
         <v>49</v>
       </c>
       <c r="C159" t="s">
-        <v>646</v>
+        <v>663</v>
       </c>
       <c r="D159" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E159" t="s">
         <v>61</v>
       </c>
       <c r="F159" t="s">
-        <v>647</v>
+        <v>664</v>
       </c>
     </row>
     <row r="160" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13907,16 +14110,16 @@
         <v>49</v>
       </c>
       <c r="C160" t="s">
-        <v>648</v>
+        <v>665</v>
       </c>
       <c r="D160" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E160" t="s">
         <v>61</v>
       </c>
       <c r="F160" t="s">
-        <v>649</v>
+        <v>666</v>
       </c>
     </row>
     <row r="161" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13927,16 +14130,16 @@
         <v>49</v>
       </c>
       <c r="C161" t="s">
-        <v>650</v>
+        <v>667</v>
       </c>
       <c r="D161" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E161" t="s">
         <v>64</v>
       </c>
       <c r="F161" t="s">
-        <v>651</v>
+        <v>668</v>
       </c>
     </row>
     <row r="162" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13947,16 +14150,16 @@
         <v>49</v>
       </c>
       <c r="C162" t="s">
-        <v>652</v>
+        <v>669</v>
       </c>
       <c r="D162" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E162" t="s">
         <v>60</v>
       </c>
       <c r="F162" t="s">
-        <v>653</v>
+        <v>670</v>
       </c>
     </row>
     <row r="163" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13967,16 +14170,16 @@
         <v>49</v>
       </c>
       <c r="C163" t="s">
-        <v>654</v>
+        <v>671</v>
       </c>
       <c r="D163" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E163" t="s">
         <v>60</v>
       </c>
       <c r="F163" t="s">
-        <v>655</v>
+        <v>672</v>
       </c>
     </row>
     <row r="164" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13987,16 +14190,16 @@
         <v>49</v>
       </c>
       <c r="C164" t="s">
-        <v>650</v>
+        <v>667</v>
       </c>
       <c r="D164" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E164" t="s">
         <v>60</v>
       </c>
       <c r="F164" t="s">
-        <v>656</v>
+        <v>673</v>
       </c>
     </row>
     <row r="165" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14007,16 +14210,16 @@
         <v>49</v>
       </c>
       <c r="C165" t="s">
-        <v>657</v>
+        <v>674</v>
       </c>
       <c r="D165" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E165" t="s">
         <v>60</v>
       </c>
       <c r="F165" t="s">
-        <v>658</v>
+        <v>675</v>
       </c>
     </row>
     <row r="166" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14030,13 +14233,13 @@
         <v>226</v>
       </c>
       <c r="D166" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E166" t="s">
         <v>60</v>
       </c>
       <c r="F166" t="s">
-        <v>659</v>
+        <v>676</v>
       </c>
     </row>
     <row r="167" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14047,16 +14250,16 @@
         <v>49</v>
       </c>
       <c r="C167" t="s">
-        <v>590</v>
+        <v>607</v>
       </c>
       <c r="D167" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E167" t="s">
         <v>60</v>
       </c>
       <c r="F167" t="s">
-        <v>660</v>
+        <v>677</v>
       </c>
     </row>
     <row r="168" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14067,16 +14270,16 @@
         <v>49</v>
       </c>
       <c r="C168" t="s">
-        <v>590</v>
+        <v>607</v>
       </c>
       <c r="D168" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E168" t="s">
         <v>61</v>
       </c>
       <c r="F168" t="s">
-        <v>661</v>
+        <v>678</v>
       </c>
     </row>
     <row r="169" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14090,13 +14293,13 @@
         <v>247</v>
       </c>
       <c r="D169" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E169" t="s">
         <v>60</v>
       </c>
       <c r="F169" t="s">
-        <v>662</v>
+        <v>679</v>
       </c>
     </row>
     <row r="170" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14107,16 +14310,16 @@
         <v>49</v>
       </c>
       <c r="C170" t="s">
-        <v>663</v>
+        <v>680</v>
       </c>
       <c r="D170" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E170" t="s">
         <v>60</v>
       </c>
       <c r="F170" t="s">
-        <v>664</v>
+        <v>681</v>
       </c>
     </row>
     <row r="171" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14127,16 +14330,16 @@
         <v>49</v>
       </c>
       <c r="C171" t="s">
-        <v>665</v>
+        <v>682</v>
       </c>
       <c r="D171" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E171" t="s">
         <v>60</v>
       </c>
       <c r="F171" t="s">
-        <v>666</v>
+        <v>683</v>
       </c>
     </row>
     <row r="172" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14150,13 +14353,13 @@
         <v>226</v>
       </c>
       <c r="D172" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E172" t="s">
         <v>61</v>
       </c>
       <c r="F172" t="s">
-        <v>667</v>
+        <v>684</v>
       </c>
     </row>
     <row r="173" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14167,16 +14370,16 @@
         <v>49</v>
       </c>
       <c r="C173" t="s">
-        <v>646</v>
+        <v>663</v>
       </c>
       <c r="D173" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E173" t="s">
         <v>60</v>
       </c>
       <c r="F173" t="s">
-        <v>668</v>
+        <v>685</v>
       </c>
     </row>
     <row r="174" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14187,16 +14390,16 @@
         <v>49</v>
       </c>
       <c r="C174" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="D174" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E174" t="s">
         <v>60</v>
       </c>
       <c r="F174" t="s">
-        <v>669</v>
+        <v>686</v>
       </c>
     </row>
     <row r="175" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14207,16 +14410,16 @@
         <v>49</v>
       </c>
       <c r="C175" t="s">
-        <v>670</v>
+        <v>687</v>
       </c>
       <c r="D175" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E175" t="s">
         <v>60</v>
       </c>
       <c r="F175" t="s">
-        <v>671</v>
+        <v>688</v>
       </c>
     </row>
     <row r="176" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14227,16 +14430,16 @@
         <v>49</v>
       </c>
       <c r="C176" t="s">
-        <v>672</v>
+        <v>689</v>
       </c>
       <c r="D176" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E176" t="s">
         <v>60</v>
       </c>
       <c r="F176" t="s">
-        <v>673</v>
+        <v>690</v>
       </c>
     </row>
     <row r="177" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14247,16 +14450,16 @@
         <v>49</v>
       </c>
       <c r="C177" t="s">
-        <v>674</v>
+        <v>691</v>
       </c>
       <c r="D177" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E177" t="s">
         <v>61</v>
       </c>
       <c r="F177" t="s">
-        <v>675</v>
+        <v>692</v>
       </c>
     </row>
     <row r="178" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14267,16 +14470,16 @@
         <v>49</v>
       </c>
       <c r="C178" t="s">
-        <v>676</v>
+        <v>693</v>
       </c>
       <c r="D178" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E178" t="s">
         <v>60</v>
       </c>
       <c r="F178" t="s">
-        <v>677</v>
+        <v>694</v>
       </c>
     </row>
     <row r="179" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14287,16 +14490,16 @@
         <v>49</v>
       </c>
       <c r="C179" t="s">
-        <v>678</v>
+        <v>695</v>
       </c>
       <c r="D179" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E179" t="s">
         <v>61</v>
       </c>
       <c r="F179" t="s">
-        <v>679</v>
+        <v>696</v>
       </c>
     </row>
     <row r="180" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14307,16 +14510,16 @@
         <v>49</v>
       </c>
       <c r="C180" t="s">
-        <v>680</v>
+        <v>697</v>
       </c>
       <c r="D180" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E180" t="s">
         <v>61</v>
       </c>
       <c r="F180" t="s">
-        <v>681</v>
+        <v>698</v>
       </c>
     </row>
     <row r="181" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14330,13 +14533,13 @@
         <v>209</v>
       </c>
       <c r="D181" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E181" t="s">
         <v>60</v>
       </c>
       <c r="F181" t="s">
-        <v>682</v>
+        <v>699</v>
       </c>
     </row>
     <row r="182" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14347,16 +14550,16 @@
         <v>49</v>
       </c>
       <c r="C182" t="s">
-        <v>683</v>
+        <v>700</v>
       </c>
       <c r="D182" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E182" t="s">
         <v>60</v>
       </c>
       <c r="F182" t="s">
-        <v>684</v>
+        <v>701</v>
       </c>
     </row>
     <row r="183" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14367,16 +14570,16 @@
         <v>49</v>
       </c>
       <c r="C183" t="s">
-        <v>685</v>
+        <v>702</v>
       </c>
       <c r="D183" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E183" t="s">
         <v>60</v>
       </c>
       <c r="F183" t="s">
-        <v>686</v>
+        <v>703</v>
       </c>
     </row>
     <row r="184" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14387,16 +14590,16 @@
         <v>49</v>
       </c>
       <c r="C184" t="s">
-        <v>687</v>
+        <v>704</v>
       </c>
       <c r="D184" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E184" t="s">
         <v>60</v>
       </c>
       <c r="F184" t="s">
-        <v>688</v>
+        <v>705</v>
       </c>
     </row>
     <row r="185" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14407,16 +14610,16 @@
         <v>49</v>
       </c>
       <c r="C185" t="s">
-        <v>687</v>
+        <v>704</v>
       </c>
       <c r="D185" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E185" t="s">
         <v>60</v>
       </c>
       <c r="F185" t="s">
-        <v>689</v>
+        <v>706</v>
       </c>
     </row>
     <row r="186" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14430,13 +14633,13 @@
         <v>209</v>
       </c>
       <c r="D186" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E186" t="s">
         <v>60</v>
       </c>
       <c r="F186" t="s">
-        <v>690</v>
+        <v>707</v>
       </c>
     </row>
     <row r="187" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14447,16 +14650,16 @@
         <v>49</v>
       </c>
       <c r="C187" t="s">
-        <v>691</v>
+        <v>708</v>
       </c>
       <c r="D187" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E187" t="s">
         <v>60</v>
       </c>
       <c r="F187" t="s">
-        <v>692</v>
+        <v>709</v>
       </c>
     </row>
     <row r="188" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14467,16 +14670,16 @@
         <v>49</v>
       </c>
       <c r="C188" t="s">
-        <v>693</v>
+        <v>710</v>
       </c>
       <c r="D188" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E188" t="s">
         <v>60</v>
       </c>
       <c r="F188" t="s">
-        <v>694</v>
+        <v>711</v>
       </c>
     </row>
     <row r="189" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14487,16 +14690,16 @@
         <v>49</v>
       </c>
       <c r="C189" t="s">
-        <v>683</v>
+        <v>700</v>
       </c>
       <c r="D189" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E189" t="s">
         <v>60</v>
       </c>
       <c r="F189" t="s">
-        <v>695</v>
+        <v>712</v>
       </c>
     </row>
     <row r="190" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14507,16 +14710,16 @@
         <v>49</v>
       </c>
       <c r="C190" t="s">
-        <v>696</v>
+        <v>713</v>
       </c>
       <c r="D190" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E190" t="s">
         <v>60</v>
       </c>
       <c r="F190" t="s">
-        <v>697</v>
+        <v>714</v>
       </c>
     </row>
     <row r="191" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14527,16 +14730,16 @@
         <v>49</v>
       </c>
       <c r="C191" t="s">
-        <v>698</v>
+        <v>715</v>
       </c>
       <c r="D191" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E191" t="s">
         <v>60</v>
       </c>
       <c r="F191" t="s">
-        <v>699</v>
+        <v>716</v>
       </c>
     </row>
     <row r="192" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14547,16 +14750,16 @@
         <v>49</v>
       </c>
       <c r="C192" t="s">
-        <v>698</v>
+        <v>715</v>
       </c>
       <c r="D192" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E192" t="s">
         <v>60</v>
       </c>
       <c r="F192" t="s">
-        <v>700</v>
+        <v>717</v>
       </c>
     </row>
     <row r="193" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14567,16 +14770,16 @@
         <v>49</v>
       </c>
       <c r="C193" t="s">
-        <v>701</v>
+        <v>718</v>
       </c>
       <c r="D193" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E193" t="s">
         <v>60</v>
       </c>
       <c r="F193" t="s">
-        <v>702</v>
+        <v>719</v>
       </c>
     </row>
     <row r="194" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14587,16 +14790,16 @@
         <v>49</v>
       </c>
       <c r="C194" t="s">
-        <v>703</v>
+        <v>720</v>
       </c>
       <c r="D194" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E194" t="s">
         <v>60</v>
       </c>
       <c r="F194" t="s">
-        <v>704</v>
+        <v>721</v>
       </c>
     </row>
     <row r="195" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14607,16 +14810,16 @@
         <v>49</v>
       </c>
       <c r="C195" t="s">
-        <v>705</v>
+        <v>722</v>
       </c>
       <c r="D195" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E195" t="s">
         <v>60</v>
       </c>
       <c r="F195" t="s">
-        <v>706</v>
+        <v>723</v>
       </c>
     </row>
     <row r="196" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14627,16 +14830,16 @@
         <v>49</v>
       </c>
       <c r="C196" t="s">
-        <v>638</v>
+        <v>655</v>
       </c>
       <c r="D196" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E196" t="s">
         <v>60</v>
       </c>
       <c r="F196" t="s">
-        <v>707</v>
+        <v>724</v>
       </c>
     </row>
     <row r="197" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14647,16 +14850,16 @@
         <v>49</v>
       </c>
       <c r="C197" t="s">
-        <v>708</v>
+        <v>725</v>
       </c>
       <c r="D197" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E197" t="s">
         <v>60</v>
       </c>
       <c r="F197" t="s">
-        <v>709</v>
+        <v>726</v>
       </c>
     </row>
     <row r="198" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14667,16 +14870,16 @@
         <v>49</v>
       </c>
       <c r="C198" t="s">
-        <v>710</v>
+        <v>727</v>
       </c>
       <c r="D198" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E198" t="s">
         <v>60</v>
       </c>
       <c r="F198" t="s">
-        <v>711</v>
+        <v>728</v>
       </c>
     </row>
     <row r="199" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14687,16 +14890,16 @@
         <v>49</v>
       </c>
       <c r="C199" t="s">
-        <v>712</v>
+        <v>729</v>
       </c>
       <c r="D199" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E199" t="s">
         <v>60</v>
       </c>
       <c r="F199" t="s">
-        <v>713</v>
+        <v>730</v>
       </c>
     </row>
     <row r="200" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14707,16 +14910,16 @@
         <v>49</v>
       </c>
       <c r="C200" t="s">
-        <v>714</v>
+        <v>731</v>
       </c>
       <c r="D200" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E200" t="s">
         <v>64</v>
       </c>
       <c r="F200" t="s">
-        <v>715</v>
+        <v>732</v>
       </c>
     </row>
     <row r="201" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14727,16 +14930,16 @@
         <v>49</v>
       </c>
       <c r="C201" t="s">
-        <v>703</v>
+        <v>720</v>
       </c>
       <c r="D201" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E201" t="s">
         <v>60</v>
       </c>
       <c r="F201" t="s">
-        <v>716</v>
+        <v>733</v>
       </c>
     </row>
     <row r="202" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14747,16 +14950,16 @@
         <v>49</v>
       </c>
       <c r="C202" t="s">
-        <v>717</v>
+        <v>734</v>
       </c>
       <c r="D202" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E202" t="s">
         <v>60</v>
       </c>
       <c r="F202" t="s">
-        <v>718</v>
+        <v>735</v>
       </c>
     </row>
     <row r="203" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14767,16 +14970,16 @@
         <v>49</v>
       </c>
       <c r="C203" t="s">
-        <v>719</v>
+        <v>736</v>
       </c>
       <c r="D203" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E203" t="s">
         <v>60</v>
       </c>
       <c r="F203" t="s">
-        <v>720</v>
+        <v>737</v>
       </c>
     </row>
     <row r="204" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14790,13 +14993,13 @@
         <v>182</v>
       </c>
       <c r="D204" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E204" t="s">
         <v>60</v>
       </c>
       <c r="F204" t="s">
-        <v>721</v>
+        <v>738</v>
       </c>
     </row>
     <row r="205" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14807,16 +15010,16 @@
         <v>49</v>
       </c>
       <c r="C205" t="s">
-        <v>722</v>
+        <v>739</v>
       </c>
       <c r="D205" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E205" t="s">
         <v>61</v>
       </c>
       <c r="F205" t="s">
-        <v>723</v>
+        <v>740</v>
       </c>
     </row>
     <row r="206" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14827,16 +15030,16 @@
         <v>49</v>
       </c>
       <c r="C206" t="s">
-        <v>638</v>
+        <v>655</v>
       </c>
       <c r="D206" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E206" t="s">
         <v>61</v>
       </c>
       <c r="F206" t="s">
-        <v>724</v>
+        <v>741</v>
       </c>
     </row>
     <row r="207" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14850,13 +15053,13 @@
         <v>178</v>
       </c>
       <c r="D207" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E207" t="s">
         <v>60</v>
       </c>
       <c r="F207" t="s">
-        <v>725</v>
+        <v>742</v>
       </c>
     </row>
     <row r="208" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14867,16 +15070,16 @@
         <v>49</v>
       </c>
       <c r="C208" t="s">
-        <v>726</v>
+        <v>743</v>
       </c>
       <c r="D208" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E208" t="s">
         <v>60</v>
       </c>
       <c r="F208" t="s">
-        <v>727</v>
+        <v>744</v>
       </c>
     </row>
     <row r="209" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14890,13 +15093,13 @@
         <v>172</v>
       </c>
       <c r="D209" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E209" t="s">
         <v>60</v>
       </c>
       <c r="F209" t="s">
-        <v>728</v>
+        <v>745</v>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14907,16 +15110,16 @@
         <v>49</v>
       </c>
       <c r="C210" t="s">
-        <v>729</v>
+        <v>746</v>
       </c>
       <c r="D210" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E210" t="s">
         <v>64</v>
       </c>
       <c r="F210" t="s">
-        <v>730</v>
+        <v>747</v>
       </c>
     </row>
     <row r="211" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14927,16 +15130,16 @@
         <v>49</v>
       </c>
       <c r="C211" t="s">
-        <v>731</v>
+        <v>748</v>
       </c>
       <c r="D211" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E211" t="s">
         <v>64</v>
       </c>
       <c r="F211" t="s">
-        <v>732</v>
+        <v>749</v>
       </c>
     </row>
     <row r="212" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14947,16 +15150,16 @@
         <v>49</v>
       </c>
       <c r="C212" t="s">
-        <v>733</v>
+        <v>750</v>
       </c>
       <c r="D212" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E212" t="s">
         <v>60</v>
       </c>
       <c r="F212" t="s">
-        <v>734</v>
+        <v>751</v>
       </c>
     </row>
     <row r="213" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14967,16 +15170,16 @@
         <v>49</v>
       </c>
       <c r="C213" t="s">
-        <v>735</v>
+        <v>752</v>
       </c>
       <c r="D213" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E213" t="s">
         <v>60</v>
       </c>
       <c r="F213" t="s">
-        <v>736</v>
+        <v>753</v>
       </c>
     </row>
     <row r="214" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14987,16 +15190,16 @@
         <v>49</v>
       </c>
       <c r="C214" t="s">
-        <v>737</v>
+        <v>754</v>
       </c>
       <c r="D214" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E214" t="s">
         <v>64</v>
       </c>
       <c r="F214" t="s">
-        <v>738</v>
+        <v>755</v>
       </c>
     </row>
     <row r="215" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15010,13 +15213,13 @@
         <v>182</v>
       </c>
       <c r="D215" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E215" t="s">
         <v>60</v>
       </c>
       <c r="F215" t="s">
-        <v>739</v>
+        <v>756</v>
       </c>
     </row>
     <row r="216" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15027,16 +15230,16 @@
         <v>49</v>
       </c>
       <c r="C216" t="s">
-        <v>740</v>
+        <v>757</v>
       </c>
       <c r="D216" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E216" t="s">
         <v>60</v>
       </c>
       <c r="F216" t="s">
-        <v>741</v>
+        <v>758</v>
       </c>
     </row>
     <row r="217" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15047,16 +15250,16 @@
         <v>49</v>
       </c>
       <c r="C217" t="s">
-        <v>742</v>
+        <v>759</v>
       </c>
       <c r="D217" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E217" t="s">
         <v>60</v>
       </c>
       <c r="F217" t="s">
-        <v>743</v>
+        <v>760</v>
       </c>
     </row>
     <row r="218" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15067,16 +15270,16 @@
         <v>49</v>
       </c>
       <c r="C218" t="s">
-        <v>742</v>
+        <v>759</v>
       </c>
       <c r="D218" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E218" t="s">
         <v>61</v>
       </c>
       <c r="F218" t="s">
-        <v>744</v>
+        <v>761</v>
       </c>
     </row>
     <row r="219" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15090,13 +15293,13 @@
         <v>164</v>
       </c>
       <c r="D219" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E219" t="s">
         <v>60</v>
       </c>
       <c r="F219" t="s">
-        <v>745</v>
+        <v>762</v>
       </c>
     </row>
     <row r="220" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15107,16 +15310,16 @@
         <v>49</v>
       </c>
       <c r="C220" t="s">
-        <v>746</v>
+        <v>763</v>
       </c>
       <c r="D220" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E220" t="s">
         <v>60</v>
       </c>
       <c r="F220" t="s">
-        <v>747</v>
+        <v>764</v>
       </c>
     </row>
     <row r="221" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15127,16 +15330,16 @@
         <v>49</v>
       </c>
       <c r="C221" t="s">
-        <v>748</v>
+        <v>765</v>
       </c>
       <c r="D221" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E221" t="s">
         <v>60</v>
       </c>
       <c r="F221" t="s">
-        <v>749</v>
+        <v>766</v>
       </c>
     </row>
     <row r="222" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15147,16 +15350,16 @@
         <v>49</v>
       </c>
       <c r="C222" t="s">
-        <v>750</v>
+        <v>767</v>
       </c>
       <c r="D222" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E222" t="s">
         <v>64</v>
       </c>
       <c r="F222" t="s">
-        <v>751</v>
+        <v>768</v>
       </c>
     </row>
     <row r="223" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15167,16 +15370,16 @@
         <v>49</v>
       </c>
       <c r="C223" t="s">
-        <v>752</v>
+        <v>769</v>
       </c>
       <c r="D223" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E223" t="s">
         <v>64</v>
       </c>
       <c r="F223" t="s">
-        <v>753</v>
+        <v>770</v>
       </c>
     </row>
     <row r="224" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15187,16 +15390,16 @@
         <v>49</v>
       </c>
       <c r="C224" t="s">
-        <v>754</v>
+        <v>771</v>
       </c>
       <c r="D224" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E224" t="s">
         <v>60</v>
       </c>
       <c r="F224" t="s">
-        <v>755</v>
+        <v>772</v>
       </c>
     </row>
     <row r="225" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15207,16 +15410,16 @@
         <v>49</v>
       </c>
       <c r="C225" t="s">
-        <v>756</v>
+        <v>773</v>
       </c>
       <c r="D225" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E225" t="s">
         <v>60</v>
       </c>
       <c r="F225" t="s">
-        <v>757</v>
+        <v>774</v>
       </c>
     </row>
     <row r="226" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15227,16 +15430,16 @@
         <v>49</v>
       </c>
       <c r="C226" t="s">
-        <v>758</v>
+        <v>775</v>
       </c>
       <c r="D226" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E226" t="s">
         <v>60</v>
       </c>
       <c r="F226" t="s">
-        <v>759</v>
+        <v>776</v>
       </c>
     </row>
     <row r="227" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15247,16 +15450,16 @@
         <v>49</v>
       </c>
       <c r="C227" t="s">
-        <v>760</v>
+        <v>777</v>
       </c>
       <c r="D227" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E227" t="s">
         <v>63</v>
       </c>
       <c r="F227" t="s">
-        <v>761</v>
+        <v>778</v>
       </c>
     </row>
     <row r="228" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15267,16 +15470,16 @@
         <v>49</v>
       </c>
       <c r="C228" t="s">
-        <v>762</v>
+        <v>779</v>
       </c>
       <c r="D228" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E228" t="s">
         <v>61</v>
       </c>
       <c r="F228" t="s">
-        <v>763</v>
+        <v>780</v>
       </c>
     </row>
     <row r="229" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15287,16 +15490,16 @@
         <v>49</v>
       </c>
       <c r="C229" t="s">
-        <v>764</v>
+        <v>781</v>
       </c>
       <c r="D229" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E229" t="s">
         <v>60</v>
       </c>
       <c r="F229" t="s">
-        <v>765</v>
+        <v>782</v>
       </c>
     </row>
     <row r="230" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15307,16 +15510,16 @@
         <v>49</v>
       </c>
       <c r="C230" t="s">
-        <v>766</v>
+        <v>783</v>
       </c>
       <c r="D230" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E230" t="s">
         <v>64</v>
       </c>
       <c r="F230" t="s">
-        <v>767</v>
+        <v>784</v>
       </c>
     </row>
     <row r="231" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15327,16 +15530,16 @@
         <v>49</v>
       </c>
       <c r="C231" t="s">
-        <v>768</v>
+        <v>785</v>
       </c>
       <c r="D231" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E231" t="s">
         <v>60</v>
       </c>
       <c r="F231" t="s">
-        <v>769</v>
+        <v>786</v>
       </c>
     </row>
     <row r="232" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15350,13 +15553,13 @@
         <v>144</v>
       </c>
       <c r="D232" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E232" t="s">
         <v>60</v>
       </c>
       <c r="F232" t="s">
-        <v>770</v>
+        <v>787</v>
       </c>
     </row>
     <row r="233" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15367,16 +15570,16 @@
         <v>49</v>
       </c>
       <c r="C233" t="s">
-        <v>674</v>
+        <v>691</v>
       </c>
       <c r="D233" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E233" t="s">
         <v>60</v>
       </c>
       <c r="F233" t="s">
-        <v>771</v>
+        <v>788</v>
       </c>
     </row>
     <row r="234" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15387,16 +15590,16 @@
         <v>49</v>
       </c>
       <c r="C234" t="s">
-        <v>772</v>
+        <v>789</v>
       </c>
       <c r="D234" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E234" t="s">
         <v>60</v>
       </c>
       <c r="F234" t="s">
-        <v>773</v>
+        <v>790</v>
       </c>
     </row>
     <row r="235" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15407,16 +15610,16 @@
         <v>49</v>
       </c>
       <c r="C235" t="s">
-        <v>774</v>
+        <v>791</v>
       </c>
       <c r="D235" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E235" t="s">
         <v>60</v>
       </c>
       <c r="F235" t="s">
-        <v>775</v>
+        <v>792</v>
       </c>
     </row>
     <row r="236" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15427,16 +15630,16 @@
         <v>49</v>
       </c>
       <c r="C236" t="s">
-        <v>776</v>
+        <v>793</v>
       </c>
       <c r="D236" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E236" t="s">
         <v>60</v>
       </c>
       <c r="F236" t="s">
-        <v>777</v>
+        <v>794</v>
       </c>
     </row>
     <row r="237" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15447,16 +15650,16 @@
         <v>49</v>
       </c>
       <c r="C237" t="s">
-        <v>778</v>
+        <v>795</v>
       </c>
       <c r="D237" s="37" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E237" t="s">
         <v>60</v>
       </c>
       <c r="F237" t="s">
-        <v>779</v>
+        <v>796</v>
       </c>
     </row>
     <row r="238" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15470,13 +15673,13 @@
         <v>135</v>
       </c>
       <c r="D238" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="E238" t="s">
         <v>60</v>
       </c>
       <c r="F238" t="s">
-        <v>780</v>
+        <v>797</v>
       </c>
     </row>
     <row r="239" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -16029,7 +16232,7 @@
     </row>
     <row r="2" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>781</v>
+        <v>798</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -16040,19 +16243,19 @@
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>782</v>
+        <v>799</v>
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="9" t="s">
-        <v>783</v>
+        <v>800</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9" t="s">
-        <v>784</v>
+        <v>801</v>
       </c>
       <c r="F4" s="9"/>
       <c r="G4" s="9" t="s">
-        <v>785</v>
+        <v>802</v>
       </c>
       <c r="H4" s="9"/>
     </row>
@@ -16080,7 +16283,7 @@
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>786</v>
+        <v>803</v>
       </c>
       <c r="B7" s="9"/>
     </row>
@@ -16093,7 +16296,7 @@
     </row>
     <row r="11" ht="21.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>787</v>
+        <v>804</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>125</v>
@@ -16105,16 +16308,16 @@
         <v>133</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>788</v>
+        <v>805</v>
       </c>
       <c r="F11" s="13" t="s">
         <v>89</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>789</v>
+        <v>806</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>367</v>
+        <v>385</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -16122,19 +16325,19 @@
         <v>46210</v>
       </c>
       <c r="B12" t="s">
-        <v>790</v>
+        <v>807</v>
       </c>
       <c r="C12" t="s">
         <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>791</v>
+        <v>808</v>
       </c>
       <c r="E12" s="39">
         <v>10000</v>
       </c>
       <c r="F12" t="s">
-        <v>792</v>
+        <v>809</v>
       </c>
       <c r="G12" s="36"/>
     </row>
@@ -16143,19 +16346,19 @@
         <v>46210</v>
       </c>
       <c r="B13" t="s">
-        <v>793</v>
+        <v>810</v>
       </c>
       <c r="C13" t="s">
         <v>51</v>
       </c>
       <c r="D13" t="s">
-        <v>794</v>
+        <v>811</v>
       </c>
       <c r="E13" s="39">
         <v>1500</v>
       </c>
       <c r="F13" t="s">
-        <v>795</v>
+        <v>812</v>
       </c>
       <c r="G13" s="36">
         <v>46210</v>
@@ -16172,13 +16375,13 @@
         <v>51</v>
       </c>
       <c r="D14" t="s">
-        <v>796</v>
+        <v>813</v>
       </c>
       <c r="E14" s="39">
         <v>3500</v>
       </c>
       <c r="F14" t="s">
-        <v>797</v>
+        <v>814</v>
       </c>
       <c r="G14" s="36"/>
     </row>
@@ -16187,19 +16390,19 @@
         <v>46204</v>
       </c>
       <c r="B15" t="s">
-        <v>798</v>
+        <v>815</v>
       </c>
       <c r="C15" t="s">
         <v>51</v>
       </c>
       <c r="D15" t="s">
-        <v>799</v>
+        <v>816</v>
       </c>
       <c r="E15" s="39">
         <v>590</v>
       </c>
       <c r="F15" t="s">
-        <v>795</v>
+        <v>812</v>
       </c>
       <c r="G15" s="36">
         <v>46210</v>
@@ -16216,13 +16419,13 @@
         <v>51</v>
       </c>
       <c r="D16" t="s">
-        <v>800</v>
+        <v>817</v>
       </c>
       <c r="E16" s="39">
         <v>14000</v>
       </c>
       <c r="F16" t="s">
-        <v>792</v>
+        <v>809</v>
       </c>
       <c r="G16" s="36"/>
     </row>
@@ -16231,25 +16434,25 @@
         <v>46205</v>
       </c>
       <c r="B17" t="s">
-        <v>801</v>
+        <v>818</v>
       </c>
       <c r="C17" t="s">
         <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>802</v>
+        <v>819</v>
       </c>
       <c r="E17" s="39">
         <v>4200</v>
       </c>
       <c r="F17" t="s">
-        <v>803</v>
+        <v>820</v>
       </c>
       <c r="G17" s="36">
         <v>46210</v>
       </c>
       <c r="H17" t="s">
-        <v>804</v>
+        <v>821</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -16257,25 +16460,25 @@
         <v>46205</v>
       </c>
       <c r="B18" t="s">
-        <v>801</v>
+        <v>818</v>
       </c>
       <c r="C18" t="s">
         <v>51</v>
       </c>
       <c r="D18" t="s">
-        <v>802</v>
+        <v>819</v>
       </c>
       <c r="E18" s="39">
         <v>4200</v>
       </c>
       <c r="F18" t="s">
-        <v>803</v>
+        <v>820</v>
       </c>
       <c r="G18" s="36">
         <v>46210</v>
       </c>
       <c r="H18" t="s">
-        <v>805</v>
+        <v>822</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -16283,17 +16486,17 @@
         <v>46205</v>
       </c>
       <c r="B19" t="s">
-        <v>806</v>
+        <v>823</v>
       </c>
       <c r="C19" t="s">
         <v>50</v>
       </c>
       <c r="D19" t="s">
-        <v>807</v>
+        <v>824</v>
       </c>
       <c r="E19" s="39"/>
       <c r="F19" t="s">
-        <v>797</v>
+        <v>814</v>
       </c>
       <c r="G19" s="36"/>
     </row>
@@ -16308,13 +16511,13 @@
         <v>51</v>
       </c>
       <c r="D20" t="s">
-        <v>796</v>
+        <v>813</v>
       </c>
       <c r="E20" s="39">
         <v>5500</v>
       </c>
       <c r="F20" t="s">
-        <v>797</v>
+        <v>814</v>
       </c>
       <c r="G20" s="36"/>
     </row>
@@ -16329,13 +16532,13 @@
         <v>49</v>
       </c>
       <c r="D21" t="s">
-        <v>808</v>
+        <v>825</v>
       </c>
       <c r="E21" s="39">
         <v>850</v>
       </c>
       <c r="F21" t="s">
-        <v>797</v>
+        <v>814</v>
       </c>
       <c r="G21" s="36"/>
     </row>
@@ -16344,19 +16547,19 @@
         <v>46209</v>
       </c>
       <c r="B22" t="s">
-        <v>778</v>
+        <v>795</v>
       </c>
       <c r="C22" t="s">
         <v>49</v>
       </c>
       <c r="D22" t="s">
-        <v>808</v>
+        <v>825</v>
       </c>
       <c r="E22" s="39">
         <v>2700</v>
       </c>
       <c r="F22" t="s">
-        <v>797</v>
+        <v>814</v>
       </c>
       <c r="G22" s="36"/>
     </row>
@@ -17382,7 +17585,7 @@
         <v>46054</v>
       </c>
       <c r="C2" t="s">
-        <v>809</v>
+        <v>826</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -17415,7 +17618,7 @@
         <v>45931</v>
       </c>
       <c r="C5" t="s">
-        <v>809</v>
+        <v>826</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -17486,7 +17689,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>810</v>
+        <v>827</v>
       </c>
       <c r="B12" s="41"/>
       <c r="C12" t="s">
@@ -17495,7 +17698,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>811</v>
+        <v>828</v>
       </c>
       <c r="B13" s="41"/>
       <c r="C13" t="s">
@@ -17504,7 +17707,7 @@
     </row>
     <row r="15" ht="32.85" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="35" t="s">
-        <v>812</v>
+        <v>829</v>
       </c>
       <c r="B15" s="35"/>
       <c r="C15" s="35"/>
@@ -17541,25 +17744,25 @@
         <v>89</v>
       </c>
       <c r="E1" t="s">
-        <v>813</v>
+        <v>830</v>
       </c>
       <c r="G1" t="s">
-        <v>814</v>
+        <v>831</v>
       </c>
       <c r="I1" t="s">
-        <v>815</v>
+        <v>832</v>
       </c>
       <c r="K1" t="s">
-        <v>816</v>
+        <v>833</v>
       </c>
       <c r="M1" t="s">
-        <v>817</v>
+        <v>834</v>
       </c>
       <c r="O1" t="s">
-        <v>818</v>
+        <v>835</v>
       </c>
       <c r="Q1" t="s">
-        <v>819</v>
+        <v>836</v>
       </c>
       <c r="S1" t="s">
         <v>83</v>
@@ -17576,25 +17779,25 @@
         <v>152</v>
       </c>
       <c r="G2" t="s">
-        <v>797</v>
+        <v>814</v>
       </c>
       <c r="I2" t="s">
-        <v>820</v>
+        <v>837</v>
       </c>
       <c r="K2" t="s">
         <v>255</v>
       </c>
       <c r="M2" t="s">
-        <v>802</v>
+        <v>819</v>
       </c>
       <c r="O2" t="s">
-        <v>369</v>
+        <v>387</v>
       </c>
       <c r="Q2" t="s">
         <v>60</v>
       </c>
       <c r="S2" t="s">
-        <v>821</v>
+        <v>838</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -17608,25 +17811,25 @@
         <v>278</v>
       </c>
       <c r="G3" t="s">
-        <v>792</v>
+        <v>809</v>
       </c>
       <c r="I3" t="s">
-        <v>822</v>
+        <v>839</v>
       </c>
       <c r="K3" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="M3" t="s">
-        <v>823</v>
+        <v>840</v>
       </c>
       <c r="O3" t="s">
-        <v>824</v>
+        <v>841</v>
       </c>
       <c r="Q3" t="s">
         <v>61</v>
       </c>
       <c r="S3" t="s">
-        <v>825</v>
+        <v>842</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -17634,25 +17837,25 @@
         <v>46</v>
       </c>
       <c r="C4" t="s">
-        <v>826</v>
+        <v>843</v>
       </c>
       <c r="G4" t="s">
-        <v>795</v>
+        <v>812</v>
       </c>
       <c r="I4" t="s">
         <v>3</v>
       </c>
       <c r="K4" t="s">
-        <v>827</v>
+        <v>844</v>
       </c>
       <c r="M4" t="s">
-        <v>828</v>
+        <v>845</v>
       </c>
       <c r="Q4" t="s">
         <v>62</v>
       </c>
       <c r="S4" t="s">
-        <v>829</v>
+        <v>846</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -17663,19 +17866,19 @@
         <v>198</v>
       </c>
       <c r="G5" t="s">
-        <v>803</v>
+        <v>820</v>
       </c>
       <c r="K5" t="s">
-        <v>830</v>
+        <v>847</v>
       </c>
       <c r="M5" t="s">
-        <v>831</v>
+        <v>848</v>
       </c>
       <c r="Q5" t="s">
         <v>63</v>
       </c>
       <c r="S5" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -17683,10 +17886,10 @@
         <v>48</v>
       </c>
       <c r="K6" t="s">
-        <v>832</v>
+        <v>849</v>
       </c>
       <c r="M6" t="s">
-        <v>833</v>
+        <v>850</v>
       </c>
       <c r="Q6" t="s">
         <v>64</v>
@@ -17703,13 +17906,13 @@
         <v>286</v>
       </c>
       <c r="M7" t="s">
-        <v>834</v>
+        <v>851</v>
       </c>
       <c r="Q7" t="s">
         <v>65</v>
       </c>
       <c r="S7" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -17720,7 +17923,7 @@
         <v>136</v>
       </c>
       <c r="M8" t="s">
-        <v>835</v>
+        <v>852</v>
       </c>
       <c r="Q8" t="s">
         <v>66</v>
@@ -17734,10 +17937,10 @@
         <v>51</v>
       </c>
       <c r="K9" t="s">
-        <v>836</v>
+        <v>853</v>
       </c>
       <c r="M9" t="s">
-        <v>837</v>
+        <v>854</v>
       </c>
       <c r="Q9" t="s">
         <v>67</v>
@@ -17754,7 +17957,7 @@
         <v>203</v>
       </c>
       <c r="M10" t="s">
-        <v>838</v>
+        <v>855</v>
       </c>
       <c r="S10" t="s">
         <v>170</v>
@@ -17768,10 +17971,10 @@
         <v>222</v>
       </c>
       <c r="M11" t="s">
-        <v>839</v>
+        <v>856</v>
       </c>
       <c r="S11" t="s">
-        <v>840</v>
+        <v>857</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -17779,10 +17982,10 @@
         <v>54</v>
       </c>
       <c r="K12" t="s">
-        <v>841</v>
+        <v>858</v>
       </c>
       <c r="M12" t="s">
-        <v>794</v>
+        <v>811</v>
       </c>
       <c r="S12" t="s">
         <v>252</v>
@@ -17793,10 +17996,10 @@
         <v>55</v>
       </c>
       <c r="K13" t="s">
-        <v>842</v>
+        <v>859</v>
       </c>
       <c r="M13" t="s">
-        <v>843</v>
+        <v>860</v>
       </c>
       <c r="S13" t="s">
         <v>266</v>
@@ -17804,13 +18007,13 @@
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>844</v>
+        <v>861</v>
       </c>
       <c r="K14" t="s">
-        <v>845</v>
+        <v>862</v>
       </c>
       <c r="M14" t="s">
-        <v>846</v>
+        <v>863</v>
       </c>
       <c r="S14" t="s">
         <v>97</v>
@@ -17818,41 +18021,41 @@
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>847</v>
+        <v>864</v>
       </c>
       <c r="K15" t="s">
-        <v>848</v>
+        <v>865</v>
       </c>
       <c r="M15" t="s">
-        <v>849</v>
+        <v>866</v>
       </c>
       <c r="S15" t="s">
-        <v>850</v>
+        <v>867</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>851</v>
+        <v>868</v>
       </c>
       <c r="K16" t="s">
-        <v>852</v>
+        <v>869</v>
       </c>
       <c r="M16" t="s">
-        <v>853</v>
+        <v>870</v>
       </c>
       <c r="S16" t="s">
-        <v>351</v>
+        <v>364</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>854</v>
+        <v>871</v>
       </c>
       <c r="K17" t="s">
-        <v>855</v>
+        <v>872</v>
       </c>
       <c r="M17" t="s">
-        <v>808</v>
+        <v>825</v>
       </c>
       <c r="S17" t="s">
         <v>92</v>
@@ -17860,27 +18063,27 @@
     </row>
     <row r="18" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>856</v>
+        <v>873</v>
       </c>
       <c r="K18" t="s">
-        <v>857</v>
+        <v>874</v>
       </c>
       <c r="M18" t="s">
-        <v>799</v>
+        <v>816</v>
       </c>
       <c r="S18" t="s">
-        <v>858</v>
+        <v>875</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
       <c r="K19" t="s">
-        <v>859</v>
+        <v>876</v>
       </c>
       <c r="M19" t="s">
-        <v>860</v>
+        <v>877</v>
       </c>
       <c r="S19" t="s">
-        <v>861</v>
+        <v>878</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
@@ -17888,10 +18091,10 @@
         <v>233</v>
       </c>
       <c r="M20" t="s">
-        <v>862</v>
+        <v>879</v>
       </c>
       <c r="S20" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
@@ -17899,7 +18102,7 @@
         <v>183</v>
       </c>
       <c r="M21" t="s">
-        <v>863</v>
+        <v>880</v>
       </c>
       <c r="S21" t="s">
         <v>237</v>
@@ -17907,10 +18110,10 @@
     </row>
     <row r="22" ht="15" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
       <c r="K22" t="s">
-        <v>864</v>
+        <v>881</v>
       </c>
       <c r="M22" t="s">
-        <v>865</v>
+        <v>882</v>
       </c>
       <c r="S22" t="s">
         <v>99</v>
@@ -17921,29 +18124,29 @@
         <v>173</v>
       </c>
       <c r="M23" t="s">
-        <v>866</v>
+        <v>883</v>
       </c>
       <c r="S23" t="s">
-        <v>867</v>
+        <v>884</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
       <c r="K24" t="s">
-        <v>868</v>
+        <v>885</v>
       </c>
       <c r="M24" t="s">
-        <v>869</v>
+        <v>886</v>
       </c>
       <c r="S24" t="s">
-        <v>870</v>
+        <v>887</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
       <c r="K25" t="s">
-        <v>871</v>
+        <v>888</v>
       </c>
       <c r="M25" t="s">
-        <v>872</v>
+        <v>889</v>
       </c>
       <c r="S25" t="s">
         <v>157</v>
@@ -17951,10 +18154,10 @@
     </row>
     <row r="26" ht="15" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
       <c r="K26" t="s">
-        <v>873</v>
+        <v>890</v>
       </c>
       <c r="M26" t="s">
-        <v>874</v>
+        <v>891</v>
       </c>
       <c r="S26" t="s">
         <v>141</v>
@@ -17962,24 +18165,24 @@
     </row>
     <row r="27" ht="15" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
       <c r="K27" t="s">
-        <v>875</v>
+        <v>892</v>
       </c>
       <c r="M27" t="s">
-        <v>876</v>
+        <v>893</v>
       </c>
       <c r="S27" t="s">
-        <v>877</v>
+        <v>894</v>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
       <c r="K28" t="s">
-        <v>878</v>
+        <v>895</v>
       </c>
       <c r="M28" t="s">
-        <v>879</v>
+        <v>896</v>
       </c>
       <c r="S28" t="s">
-        <v>880</v>
+        <v>897</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" spans="11:13" x14ac:dyDescent="0.25">
@@ -17987,15 +18190,15 @@
         <v>240</v>
       </c>
       <c r="M29" t="s">
-        <v>881</v>
+        <v>898</v>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" spans="11:13" x14ac:dyDescent="0.25">
       <c r="K30" t="s">
-        <v>882</v>
+        <v>899</v>
       </c>
       <c r="M30" t="s">
-        <v>883</v>
+        <v>900</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" spans="11:13" x14ac:dyDescent="0.25">
@@ -18003,23 +18206,23 @@
         <v>280</v>
       </c>
       <c r="M31" t="s">
-        <v>884</v>
+        <v>901</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" spans="11:13" x14ac:dyDescent="0.25">
       <c r="K32" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="M32" t="s">
-        <v>885</v>
+        <v>902</v>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" spans="11:13" x14ac:dyDescent="0.25">
       <c r="K33" t="s">
-        <v>886</v>
+        <v>903</v>
       </c>
       <c r="M33" t="s">
-        <v>887</v>
+        <v>904</v>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" spans="11:13" x14ac:dyDescent="0.25">
@@ -18027,185 +18230,185 @@
         <v>165</v>
       </c>
       <c r="M34" t="s">
-        <v>888</v>
+        <v>905</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" spans="11:13" x14ac:dyDescent="0.25">
       <c r="K35" t="s">
-        <v>889</v>
+        <v>906</v>
       </c>
       <c r="M35" t="s">
-        <v>796</v>
+        <v>813</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M36" t="s">
-        <v>890</v>
+        <v>907</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M37" t="s">
-        <v>891</v>
+        <v>908</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M38" t="s">
-        <v>892</v>
+        <v>909</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M39" t="s">
-        <v>893</v>
+        <v>910</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M40" t="s">
-        <v>894</v>
+        <v>911</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M41" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M42" t="s">
-        <v>896</v>
+        <v>913</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M43" t="s">
-        <v>897</v>
+        <v>914</v>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M44" t="s">
-        <v>807</v>
+        <v>824</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M45" t="s">
-        <v>791</v>
+        <v>808</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M46" t="s">
-        <v>898</v>
+        <v>915</v>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M47" t="s">
-        <v>899</v>
+        <v>916</v>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M48" t="s">
-        <v>900</v>
+        <v>917</v>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M49" t="s">
-        <v>901</v>
+        <v>918</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M50" t="s">
-        <v>902</v>
+        <v>919</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M51" t="s">
-        <v>903</v>
+        <v>920</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M52" t="s">
-        <v>800</v>
+        <v>817</v>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M53" t="s">
-        <v>904</v>
+        <v>921</v>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M54" t="s">
-        <v>905</v>
+        <v>922</v>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M55" t="s">
-        <v>906</v>
+        <v>923</v>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M56" t="s">
-        <v>907</v>
+        <v>924</v>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M57" t="s">
-        <v>908</v>
+        <v>925</v>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M58" t="s">
-        <v>909</v>
+        <v>926</v>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M59" t="s">
-        <v>910</v>
+        <v>927</v>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M60" t="s">
-        <v>911</v>
+        <v>928</v>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M61" t="s">
-        <v>912</v>
+        <v>929</v>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M62" t="s">
-        <v>913</v>
+        <v>930</v>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M63" t="s">
-        <v>914</v>
+        <v>931</v>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M64" t="s">
-        <v>915</v>
+        <v>932</v>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M65" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M66" t="s">
-        <v>916</v>
+        <v>933</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M67" t="s">
-        <v>917</v>
+        <v>934</v>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M68" t="s">
-        <v>918</v>
+        <v>935</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M69" t="s">
-        <v>919</v>
+        <v>936</v>
       </c>
     </row>
   </sheetData>

--- a/relatorios/Controle_Comercial_Vigna_-_Julho.xlsx
+++ b/relatorios/Controle_Comercial_Vigna_-_Julho.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2524" uniqueCount="937">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3019" uniqueCount="1181">
   <si>
     <t>VISÃO GERAL COMERCIAL</t>
   </si>
@@ -1183,6 +1183,780 @@
     <t>Compliance e Jurídico</t>
   </si>
   <si>
+    <t>LUA NOVA IND E COMERCIO DE PRODUTOS ALIMENTICIOS LTDA - PANCO</t>
+  </si>
+  <si>
+    <t>Comércio Atacadista</t>
+  </si>
+  <si>
+    <t>62.461.140/0005-48</t>
+  </si>
+  <si>
+    <t>Adriana</t>
+  </si>
+  <si>
+    <t>DR ONLINE 24HRS/ GRUPO FAPES</t>
+  </si>
+  <si>
+    <t>46.738.901/0001-86</t>
+  </si>
+  <si>
+    <t>Ayton</t>
+  </si>
+  <si>
+    <t>Bianca Mota</t>
+  </si>
+  <si>
+    <t>DO MESTRE , FORT SOLUTIONS &amp; BRAVIA</t>
+  </si>
+  <si>
+    <t>Distribuidor</t>
+  </si>
+  <si>
+    <t>04.100.718/0001-00</t>
+  </si>
+  <si>
+    <t>responsável jurídico</t>
+  </si>
+  <si>
+    <t>Nazaré da Mata</t>
+  </si>
+  <si>
+    <t>PE</t>
+  </si>
+  <si>
+    <t>João e Cleber</t>
+  </si>
+  <si>
+    <t>SEQUOIA ALIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>35.759.786/0001-00</t>
+  </si>
+  <si>
+    <t>Dr. Bernardo</t>
+  </si>
+  <si>
+    <t>contábil fiscal jurídico</t>
+  </si>
+  <si>
+    <t>Magé</t>
+  </si>
+  <si>
+    <t>Edilaine e Pamela</t>
+  </si>
+  <si>
+    <t>GOIAS ALIMENTOS S/A</t>
+  </si>
+  <si>
+    <t>05.207.895/0001-53</t>
+  </si>
+  <si>
+    <t>Sofia</t>
+  </si>
+  <si>
+    <t>responsável pelo RH</t>
+  </si>
+  <si>
+    <t>Goianésia</t>
+  </si>
+  <si>
+    <t>Igor e Ana beatriz</t>
+  </si>
+  <si>
+    <t>PLANATC TECNOLOGIA</t>
+  </si>
+  <si>
+    <t>00.566.906/0001-78</t>
+  </si>
+  <si>
+    <t>resp fiscal</t>
+  </si>
+  <si>
+    <t>TERRA DE CULTIVO/GRUPO PENHA</t>
+  </si>
+  <si>
+    <t>06.105.854/0001-19</t>
+  </si>
+  <si>
+    <t>Sr. Lucas Mendes</t>
+  </si>
+  <si>
+    <t>Contabilidade, Fiscal e tributário</t>
+  </si>
+  <si>
+    <t>Machado</t>
+  </si>
+  <si>
+    <t>Paola e Rafael matarozzo</t>
+  </si>
+  <si>
+    <t>TECNOLOGIA BANCARIA S.A.</t>
+  </si>
+  <si>
+    <t>Bancos</t>
+  </si>
+  <si>
+    <t>51.427.102/0001-29</t>
+  </si>
+  <si>
+    <t>Sra. Keli Roberta Franco</t>
+  </si>
+  <si>
+    <t>Coordenadora Academia Corporativa</t>
+  </si>
+  <si>
+    <t>Dra. Tayna Bregnoli e Evelim</t>
+  </si>
+  <si>
+    <t>SOMAR INDUSTRIAL DE EMBALAGENS LTDA</t>
+  </si>
+  <si>
+    <t>95.758.330/0001-57</t>
+  </si>
+  <si>
+    <t>Vera</t>
+  </si>
+  <si>
+    <t>resp RH</t>
+  </si>
+  <si>
+    <t>Caçador</t>
+  </si>
+  <si>
+    <t>REFRICRIL DISTRIBUIDORA DE AR CONDICIONADO E PECAS LTDA</t>
+  </si>
+  <si>
+    <t>01.919.309/0001-42</t>
+  </si>
+  <si>
+    <t>Samuel Miguel</t>
+  </si>
+  <si>
+    <t>responsável pelo Adm</t>
+  </si>
+  <si>
+    <t>Içara</t>
+  </si>
+  <si>
+    <t>SOLPLAN</t>
+  </si>
+  <si>
+    <t>38.708.198/0001-35</t>
+  </si>
+  <si>
+    <t>Valderez</t>
+  </si>
+  <si>
+    <t>sócia</t>
+  </si>
+  <si>
+    <t>Igor &amp; Paola</t>
+  </si>
+  <si>
+    <t>GRUPO GUITTA CORRETORA DE CAMBIO</t>
+  </si>
+  <si>
+    <t>24.074.692/0001-80</t>
+  </si>
+  <si>
+    <t>Sr. Nicolas</t>
+  </si>
+  <si>
+    <t>Gerente Jurídico e Compliance</t>
+  </si>
+  <si>
+    <t>Igor Vasconcelos, Paola e Andrezza</t>
+  </si>
+  <si>
+    <t>SA RIBAS ENGENHARIA  (indicação Jorge)</t>
+  </si>
+  <si>
+    <t>27.514.154/0001-58</t>
+  </si>
+  <si>
+    <t>Gisely</t>
+  </si>
+  <si>
+    <t>Proprietária</t>
+  </si>
+  <si>
+    <t>Itajaí</t>
+  </si>
+  <si>
+    <t>HT CONSTRUCAO CIVIL LTDA</t>
+  </si>
+  <si>
+    <t>13.178.498/0001-29</t>
+  </si>
+  <si>
+    <t>Jakeline</t>
+  </si>
+  <si>
+    <t>Paola &amp; Igor</t>
+  </si>
+  <si>
+    <t>BRASAL PARTICIPACOES S/A</t>
+  </si>
+  <si>
+    <t>36.756.997/0001-51</t>
+  </si>
+  <si>
+    <t>Dra. Monica Passos</t>
+  </si>
+  <si>
+    <t>Jurídico tributário</t>
+  </si>
+  <si>
+    <t>Igor Vasconcelos e Rafael</t>
+  </si>
+  <si>
+    <t>ENGELUX CONSTRUTORA LTDA</t>
+  </si>
+  <si>
+    <t>44.023.760/0001-90</t>
+  </si>
+  <si>
+    <t>Tatiane Rodrigues</t>
+  </si>
+  <si>
+    <t>Área de cobrança</t>
+  </si>
+  <si>
+    <t>Raissa Montoro e Flavia Almeida Bezzi</t>
+  </si>
+  <si>
+    <t>STEELROOL INDUSTRIA METALURGICA</t>
+  </si>
+  <si>
+    <t>09.515.037/0001-27</t>
+  </si>
+  <si>
+    <t>Sra. Caroline Zanatta</t>
+  </si>
+  <si>
+    <t>Diretora Administrativa</t>
+  </si>
+  <si>
+    <t>Criciúma</t>
+  </si>
+  <si>
+    <t>ALCA ALIMENTOS S/A</t>
+  </si>
+  <si>
+    <t>20.785.999/0001-39</t>
+  </si>
+  <si>
+    <t>Sra. Maria Angélica</t>
+  </si>
+  <si>
+    <t>responsável pelo jurídico</t>
+  </si>
+  <si>
+    <t>Joinville</t>
+  </si>
+  <si>
+    <t>VERITAS APEX LTDA</t>
+  </si>
+  <si>
+    <t>60.362.024/0001-12</t>
+  </si>
+  <si>
+    <t>Marcelo</t>
+  </si>
+  <si>
+    <t>sócio</t>
+  </si>
+  <si>
+    <t>Raissa Dantas e Flavia</t>
+  </si>
+  <si>
+    <t>Mineracao Boa Vista</t>
+  </si>
+  <si>
+    <t>05.621.860/0001-66</t>
+  </si>
+  <si>
+    <t>Francisco</t>
+  </si>
+  <si>
+    <t>contador</t>
+  </si>
+  <si>
+    <t>Casserengue</t>
+  </si>
+  <si>
+    <t>Cleber &amp; Luciana</t>
+  </si>
+  <si>
+    <t>HYBRIDA PRODUTOS HOSPITALARES LTDA</t>
+  </si>
+  <si>
+    <t>12.544.921/0001-02</t>
+  </si>
+  <si>
+    <t>responsável pelo financeiro</t>
+  </si>
+  <si>
+    <t>Belém</t>
+  </si>
+  <si>
+    <t>PA</t>
+  </si>
+  <si>
+    <t>Cleber Scarparo e João Victor</t>
+  </si>
+  <si>
+    <t>BRASIL VIDA TAXI AEREO</t>
+  </si>
+  <si>
+    <t>06.234.656/0001-55</t>
+  </si>
+  <si>
+    <t>Marcos</t>
+  </si>
+  <si>
+    <t>resp contábil</t>
+  </si>
+  <si>
+    <t>FCC - INDUSTRIA E COMERCIO LTDA.</t>
+  </si>
+  <si>
+    <t>03.281.950/0001-20</t>
+  </si>
+  <si>
+    <t>Rafael</t>
+  </si>
+  <si>
+    <t>Conceição do Jacuípe</t>
+  </si>
+  <si>
+    <t>Aritusa</t>
+  </si>
+  <si>
+    <t>responsável financeira e uma das diretoras</t>
+  </si>
+  <si>
+    <t>YOUSE SEGURADORA S.A.</t>
+  </si>
+  <si>
+    <t>Seguradoras</t>
+  </si>
+  <si>
+    <t>24.856.160/0001-03</t>
+  </si>
+  <si>
+    <t>Kelly</t>
+  </si>
+  <si>
+    <t>resp jurídica</t>
+  </si>
+  <si>
+    <t>Pamela &amp; Flavia</t>
+  </si>
+  <si>
+    <t>REAL BRASIL TURISMO</t>
+  </si>
+  <si>
+    <t>40.160.558/0001-59</t>
+  </si>
+  <si>
+    <t>Simone</t>
+  </si>
+  <si>
+    <t>Salinor - Salinas Do Nordeste S.a.</t>
+  </si>
+  <si>
+    <t>03.994.427/0001-40</t>
+  </si>
+  <si>
+    <t>Wanderson</t>
+  </si>
+  <si>
+    <t>Gerente de Gente &amp; RH</t>
+  </si>
+  <si>
+    <t>Igor Gabriel Vasconcelos</t>
+  </si>
+  <si>
+    <t>VIACAO MIRACATIBA LTDA</t>
+  </si>
+  <si>
+    <t>01.962.300/0001-14</t>
+  </si>
+  <si>
+    <t>Ana Carolina</t>
+  </si>
+  <si>
+    <t>responsável pelo Jurídico</t>
+  </si>
+  <si>
+    <t>Itapecerica da Serra</t>
+  </si>
+  <si>
+    <t>BIOMIG MATERIAL MEDICO HOSPITALAR LTDA</t>
+  </si>
+  <si>
+    <t>22.355.622/0001-75</t>
+  </si>
+  <si>
+    <t>Sra. Daianne</t>
+  </si>
+  <si>
+    <t>responsável pelo Financeiro</t>
+  </si>
+  <si>
+    <t>Cleber e Mayara</t>
+  </si>
+  <si>
+    <t>MINERADORA TAPAJOS</t>
+  </si>
+  <si>
+    <t>34.237.001/0001-76</t>
+  </si>
+  <si>
+    <t>Sr. Daniel</t>
+  </si>
+  <si>
+    <t>CEO</t>
+  </si>
+  <si>
+    <t>Aveiro</t>
+  </si>
+  <si>
+    <t>Cleber e João Victor</t>
+  </si>
+  <si>
+    <t>MASTER COMERCIO</t>
+  </si>
+  <si>
+    <t>12.397.068/0001-35</t>
+  </si>
+  <si>
+    <t>Sr. Marco</t>
+  </si>
+  <si>
+    <t>Cleber &amp; João</t>
+  </si>
+  <si>
+    <t>COPERPHOS INDUSTRIA COMERCIO E REPRESENTACOES LTDA</t>
+  </si>
+  <si>
+    <t>37.449.410/0001-24</t>
+  </si>
+  <si>
+    <t>Claides</t>
+  </si>
+  <si>
+    <t>resp financeira</t>
+  </si>
+  <si>
+    <t>Rondonópolis</t>
+  </si>
+  <si>
+    <t>INDUSTRIAS REUNIDAS HELIO ARRUDA COELHO / FABRICA COELHO</t>
+  </si>
+  <si>
+    <t>05.270.731/0001-70</t>
+  </si>
+  <si>
+    <t>Ana Flavia</t>
+  </si>
+  <si>
+    <t>Sobral</t>
+  </si>
+  <si>
+    <t>Transportes e Logística Dia &amp; Noite LTDA</t>
+  </si>
+  <si>
+    <t>02.556.936/0001-29</t>
+  </si>
+  <si>
+    <t>Valeria</t>
+  </si>
+  <si>
+    <t>MARCOS FERNANDES (MARCAS)</t>
+  </si>
+  <si>
+    <t>Marcos Fernandes</t>
+  </si>
+  <si>
+    <t>Não informado (pessoa física)</t>
+  </si>
+  <si>
+    <t>LDO TRANSPORTE TURISTICO LTDA</t>
+  </si>
+  <si>
+    <t>73.477.424/0001-15</t>
+  </si>
+  <si>
+    <t>Sr. Anderson</t>
+  </si>
+  <si>
+    <t>responsável administrativo</t>
+  </si>
+  <si>
+    <t>Indaial</t>
+  </si>
+  <si>
+    <t>Igor e João</t>
+  </si>
+  <si>
+    <t>Belfort Seguranca de Bens e Valores Ltda</t>
+  </si>
+  <si>
+    <t>67.848.119/0001-90</t>
+  </si>
+  <si>
+    <t>Sr. Bruno Goob</t>
+  </si>
+  <si>
+    <t>Itabira Agro Industrial (Cimento Nassau)</t>
+  </si>
+  <si>
+    <t>27.175.959/0001-14</t>
+  </si>
+  <si>
+    <t>Delcides</t>
+  </si>
+  <si>
+    <t>resp jurídico</t>
+  </si>
+  <si>
+    <t>CALBRAX CALCARIO AGRICOLA LTDA</t>
+  </si>
+  <si>
+    <t>07.638.538/0001-75</t>
+  </si>
+  <si>
+    <t>Sra. Regiane</t>
+  </si>
+  <si>
+    <t>Guarani de Goiás</t>
+  </si>
+  <si>
+    <t>UNIMED SANTA CATARINA</t>
+  </si>
+  <si>
+    <t>76.590.884/0001-43</t>
+  </si>
+  <si>
+    <t>Leonardo Azevedo e Sra. Elisa Rocha</t>
+  </si>
+  <si>
+    <t>CAIXA ASSISTENCIA</t>
+  </si>
+  <si>
+    <t>39.565.194/0001-08</t>
+  </si>
+  <si>
+    <t>Sra. Angélica</t>
+  </si>
+  <si>
+    <t>gerência de Suprimentos</t>
+  </si>
+  <si>
+    <t>Barueri</t>
+  </si>
+  <si>
+    <t>ROAN ALIMENTOS LTDA</t>
+  </si>
+  <si>
+    <t>01.687.284/0001-07</t>
+  </si>
+  <si>
+    <t>Sra. Juliana</t>
+  </si>
+  <si>
+    <t>Anápolis</t>
+  </si>
+  <si>
+    <t>Willian e Cleber</t>
+  </si>
+  <si>
+    <t>ASSOBRAV GRUPO DISAL</t>
+  </si>
+  <si>
+    <t>43.679.380/0001-45</t>
+  </si>
+  <si>
+    <t>Sr. Luiz Eduardo</t>
+  </si>
+  <si>
+    <t>EMOBREL ENGENHARIA E CONSTRUCOES LTDA</t>
+  </si>
+  <si>
+    <t>71.928.444/0001-30</t>
+  </si>
+  <si>
+    <t>Juliana</t>
+  </si>
+  <si>
+    <t>coordenadora do RH</t>
+  </si>
+  <si>
+    <t>AGRICOLA FAMOSA S.A.</t>
+  </si>
+  <si>
+    <t>00.474.300/0001-02</t>
+  </si>
+  <si>
+    <t>Sra. Nayara Emiliano</t>
+  </si>
+  <si>
+    <t>Aracati</t>
+  </si>
+  <si>
+    <t>REPREMIG REPRESENTACAO E COMERCIO DE MINAS GERAIS LTDA</t>
+  </si>
+  <si>
+    <t>65.149.197/0001-70</t>
+  </si>
+  <si>
+    <t>Sr. Renato</t>
+  </si>
+  <si>
+    <t>Sócio Administrador e chefe do Depto. Administrativo</t>
+  </si>
+  <si>
+    <t>VERSA ENGENHARIA AMBIENTAL LTDA</t>
+  </si>
+  <si>
+    <t>83.073.536/0001-64</t>
+  </si>
+  <si>
+    <t>Srta. Mary Mello</t>
+  </si>
+  <si>
+    <t>Responsável RH</t>
+  </si>
+  <si>
+    <t>Pamela e Andreza</t>
+  </si>
+  <si>
+    <t>TRANSPORTE NORTE SUL</t>
+  </si>
+  <si>
+    <t>04.813.506/0001-70</t>
+  </si>
+  <si>
+    <t>Jhonata</t>
+  </si>
+  <si>
+    <t>resp financeiro</t>
+  </si>
+  <si>
+    <t>Jaboatão dos Guararapes</t>
+  </si>
+  <si>
+    <t>Pamela &amp; Luciana</t>
+  </si>
+  <si>
+    <t>VITALMED - SERVICOS DE EMERGENCIA MEDICA LTDA</t>
+  </si>
+  <si>
+    <t>96.706.718/0001-77</t>
+  </si>
+  <si>
+    <t>Mariana</t>
+  </si>
+  <si>
+    <t>Tayna</t>
+  </si>
+  <si>
+    <t>Empresa Luz e Força Santa Maria SA</t>
+  </si>
+  <si>
+    <t>27.485.069/0001-09</t>
+  </si>
+  <si>
+    <t>Jobs Goncalves</t>
+  </si>
+  <si>
+    <t>Gerente de Compliance</t>
+  </si>
+  <si>
+    <t>Colatina</t>
+  </si>
+  <si>
+    <t>CADMUS CONSULTORIA EM INFORMATICA LTDA</t>
+  </si>
+  <si>
+    <t>00.582.013/0001-16</t>
+  </si>
+  <si>
+    <t>Joelma</t>
+  </si>
+  <si>
+    <t>resp administrativo</t>
+  </si>
+  <si>
+    <t>Paola &amp; João</t>
+  </si>
+  <si>
+    <t>MOVEIS CAFTOR LTDA</t>
+  </si>
+  <si>
+    <t>95.850.806/0001-85</t>
+  </si>
+  <si>
+    <t>Cibele</t>
+  </si>
+  <si>
+    <t>Responsável pelo RH</t>
+  </si>
+  <si>
+    <t>Rio Negrinho</t>
+  </si>
+  <si>
+    <t>Igor e Andreza</t>
+  </si>
+  <si>
+    <t>BATISTA LOGISTICA LTDA</t>
+  </si>
+  <si>
+    <t>Logística</t>
+  </si>
+  <si>
+    <t>22.124.071/0001-39</t>
+  </si>
+  <si>
+    <t>Sra. Rafaela</t>
+  </si>
+  <si>
+    <t>Gerente responsável</t>
+  </si>
+  <si>
+    <t>COOPERATIVA DE LATICINIOS SELITA</t>
+  </si>
+  <si>
+    <t>27.178.359/0001-00</t>
+  </si>
+  <si>
+    <t>Sra. Valéria e Sra. Suelen</t>
+  </si>
+  <si>
+    <t>Depto. Pessoal / Técnica em segurança do trabalho</t>
+  </si>
+  <si>
+    <t>MAURICEA ALIMENTOS DO NORDESTE LTDA</t>
+  </si>
+  <si>
+    <t>12.819.074/0001-33</t>
+  </si>
+  <si>
+    <t>Sr. Flavio</t>
+  </si>
+  <si>
+    <t>responsável financeiro</t>
+  </si>
+  <si>
+    <t>Carpina</t>
+  </si>
+  <si>
+    <t>Pamela Pedro e João Victor Espelho</t>
+  </si>
+  <si>
     <t>Data</t>
   </si>
   <si>
@@ -1255,9 +2029,6 @@
     <t>1155258700 - buscar financeiro  07/07 - resp pelo contabilidade está de ferias e só retorna no inicio do prox mes</t>
   </si>
   <si>
-    <t>PLANATC TECNOLOGIA</t>
-  </si>
-  <si>
     <t>(11) 2141-4891  - somente chamou, buscar financeiro ou rh.  11/06 -  apertei na opção recursos humanos e desligou, retorno 07/07 - fui na opção financ</t>
   </si>
   <si>
@@ -1321,9 +2092,6 @@
     <t>(91) 3222-8368 - Buscar sergio resp financeiro/ recepcionista falou que ele está em reunião para eu ligar mais tarde</t>
   </si>
   <si>
-    <t>BRASIL VIDA TAXI AEREO</t>
-  </si>
-  <si>
     <t>62) 98136-0099 - correio de voz direto /  (62) 3933-9134 - Dr. Humberto não vai para a empresa, somente pelo celular mesmo</t>
   </si>
   <si>
@@ -1351,9 +2119,6 @@
     <t>11) 3315-0052 - Dra Ana Paula   06/07 - Dra. Ana paula está viajando e só retorna em agosto</t>
   </si>
   <si>
-    <t>REAL BRASIL TURISMO</t>
-  </si>
-  <si>
     <t>2124019982  - retomar com a Simone do RH.  06/07 - Simone somente na quarta feira</t>
   </si>
   <si>
@@ -1870,9 +2635,6 @@
     <t>Falei com o Dr. Renato e ele me informou que já possuí assessoria em todas as áreas...  Dr. Renato Junior - Gerente Juridico  (21) 2121-0020</t>
   </si>
   <si>
-    <t>SEQUOIA ALIMENTOS LTDA</t>
-  </si>
-  <si>
     <t>Conversei com o Carlos Gomes do Juridico e o mesmo vai entrar de férias... retomar em agosto.</t>
   </si>
   <si>
@@ -1936,9 +2698,6 @@
     <t>Em contato com Clenilson pediu para falarmos sobre o tema de diagnostico na ultima semana do mês de Junho retornar no dia 29/06</t>
   </si>
   <si>
-    <t>DO MESTRE , FORT SOLUTIONS &amp; BRAVIA</t>
-  </si>
-  <si>
     <t xml:space="preserve">Atendente me informou que a Dra. Jéssica está de home office pq ela vai entrar de licença maternidade... atendente anotou o meu numero e irá retornar </t>
   </si>
   <si>
@@ -2023,9 +2782,6 @@
     <t xml:space="preserve">Ligação   (65) 36424441- falei com a gerente da loja ela disse que a Flavia não estar e pede contato daqui 20 minutos  07/07- (65) 36424441 - Reunião </t>
   </si>
   <si>
-    <t>LDO TRANSPORTE TURISTICO LTDA</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ligação  (47) 3333-0872- retomar o contato com a empresa amanhã as 09:00  07/07- (47) 3333-0872-  falei com a recepcionista ela tentou me trana ferir </t>
   </si>
   <si>
@@ -2047,9 +2803,6 @@
     <t>Ligação  07/07- (21) 3030-9100 -  Falei com a Roberta ela disse que o senhor Gustavo não tem ramal e pediu meu numero e meu e-mail e falou que vai ped</t>
   </si>
   <si>
-    <t>ASSOBRAV GRUPO DISAL</t>
-  </si>
-  <si>
     <t>Ligação  reunião cancelada cliente informou que vai viajar e pediu reagendamento</t>
   </si>
   <si>
@@ -2575,15 +3328,9 @@
     <t>AP</t>
   </si>
   <si>
-    <t>Bancos</t>
-  </si>
-  <si>
     <t>COMPLIANCE CONTROL</t>
   </si>
   <si>
-    <t>Comércio Atacadista</t>
-  </si>
-  <si>
     <t>COMPLIANCE NR1+</t>
   </si>
   <si>
@@ -2593,9 +3340,6 @@
     <t>DIAGNÓSTICO - REFORMA TRIBUTÁRIA</t>
   </si>
   <si>
-    <t>Distribuidor</t>
-  </si>
-  <si>
     <t>DIFAL</t>
   </si>
   <si>
@@ -2635,9 +3379,6 @@
     <t>GESTÃO DO CANAL DE DENÚNCIAS</t>
   </si>
   <si>
-    <t>PA</t>
-  </si>
-  <si>
     <t>Milena Faria</t>
   </si>
   <si>
@@ -2659,9 +3400,6 @@
     <t>Imobiliária</t>
   </si>
   <si>
-    <t>PE</t>
-  </si>
-  <si>
     <t>Importadora e Exportadora</t>
   </si>
   <si>
@@ -2689,9 +3427,6 @@
     <t>RO</t>
   </si>
   <si>
-    <t>Logística</t>
-  </si>
-  <si>
     <t>LEGAL AUDIT</t>
   </si>
   <si>
@@ -2729,9 +3464,6 @@
   </si>
   <si>
     <t>PARCERIA LC E LE</t>
-  </si>
-  <si>
-    <t>Seguradoras</t>
   </si>
   <si>
     <t>PARCERIA VAA</t>
@@ -4447,25 +5179,6 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{51F781DE-E41E-4423-AE2F-E56344F420D0}">
-            <x14:dataBar minLength="0" maxLength="100">
-              <x14:cfvo type="num">
-                <xm:f>0</xm:f>
-              </x14:cfvo>
-              <x14:cfvo type="num">
-                <xm:f>1</xm:f>
-              </x14:cfvo>
-            </x14:dataBar>
-          </x14:cfRule>
-          <xm:sqref>E26:E28</xm:sqref>
-        </x14:conditionalFormatting>
-      </x14:conditionalFormattings>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 
@@ -10092,170 +10805,1765 @@
         <v>201</v>
       </c>
     </row>
-    <row r="52" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52" s="36"/>
-    </row>
-    <row r="53" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53" s="36"/>
-    </row>
-    <row r="54" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54" s="36"/>
-    </row>
-    <row r="55" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55" s="36"/>
-    </row>
-    <row r="56" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56" s="36"/>
-    </row>
-    <row r="57" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57" s="36"/>
-    </row>
-    <row r="58" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58" s="36"/>
-    </row>
-    <row r="59" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59" s="36"/>
-    </row>
-    <row r="60" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60" s="36"/>
-    </row>
-    <row r="61" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61" s="36"/>
-    </row>
-    <row r="62" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62" s="36"/>
-    </row>
-    <row r="63" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63" s="36"/>
-    </row>
-    <row r="64" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64" s="36"/>
-    </row>
-    <row r="65" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" s="36"/>
-    </row>
-    <row r="66" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" s="36"/>
-    </row>
-    <row r="67" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" s="36"/>
-    </row>
-    <row r="68" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" s="36"/>
-    </row>
-    <row r="69" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" s="36"/>
-    </row>
-    <row r="70" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" s="36"/>
-    </row>
-    <row r="71" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71" s="36"/>
-    </row>
-    <row r="72" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72" s="36"/>
-    </row>
-    <row r="73" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73" s="36"/>
-    </row>
-    <row r="74" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74" s="36"/>
-    </row>
-    <row r="75" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75" s="36"/>
-    </row>
-    <row r="76" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76" s="36"/>
-    </row>
-    <row r="77" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77" s="36"/>
-    </row>
-    <row r="78" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78" s="36"/>
-    </row>
-    <row r="79" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79" s="36"/>
-    </row>
-    <row r="80" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" s="36"/>
-    </row>
-    <row r="81" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81" s="36"/>
-    </row>
-    <row r="82" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82" s="36"/>
-    </row>
-    <row r="83" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83" s="36"/>
-    </row>
-    <row r="84" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84" s="36"/>
-    </row>
-    <row r="85" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85" s="36"/>
-    </row>
-    <row r="86" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86" s="36"/>
-    </row>
-    <row r="87" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87" s="36"/>
-    </row>
-    <row r="88" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88" s="36"/>
-    </row>
-    <row r="89" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89" s="36"/>
-    </row>
-    <row r="90" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90" s="36"/>
-    </row>
-    <row r="91" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A91" s="36"/>
-    </row>
-    <row r="92" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92" s="36"/>
-    </row>
-    <row r="93" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A93" s="36"/>
-    </row>
-    <row r="94" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A94" s="36"/>
-    </row>
-    <row r="95" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A95" s="36"/>
-    </row>
-    <row r="96" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A96" s="36"/>
-    </row>
-    <row r="97" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A97" s="36"/>
-    </row>
-    <row r="98" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A98" s="36"/>
-    </row>
-    <row r="99" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A99" s="36"/>
-    </row>
-    <row r="100" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A100" s="36"/>
-    </row>
-    <row r="101" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A101" s="36"/>
-    </row>
-    <row r="102" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A102" s="36"/>
-    </row>
-    <row r="103" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A103" s="36"/>
-    </row>
-    <row r="104" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A104" s="36"/>
-    </row>
-    <row r="105" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A105" s="36"/>
-    </row>
-    <row r="106" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A106" s="36"/>
+    <row r="52" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A52" s="36">
+        <v>46232.5</v>
+      </c>
+      <c r="B52" t="s">
+        <v>383</v>
+      </c>
+      <c r="C52" t="s">
+        <v>384</v>
+      </c>
+      <c r="D52" t="s">
+        <v>385</v>
+      </c>
+      <c r="E52" t="s">
+        <v>386</v>
+      </c>
+      <c r="F52" t="s">
+        <v>206</v>
+      </c>
+      <c r="G52" t="s">
+        <v>146</v>
+      </c>
+      <c r="H52" t="s">
+        <v>146</v>
+      </c>
+      <c r="I52" t="s">
+        <v>50</v>
+      </c>
+      <c r="J52" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" s="36">
+        <v>46219.5</v>
+      </c>
+      <c r="B53" t="s">
+        <v>387</v>
+      </c>
+      <c r="C53" t="s">
+        <v>240</v>
+      </c>
+      <c r="D53" t="s">
+        <v>388</v>
+      </c>
+      <c r="E53" t="s">
+        <v>389</v>
+      </c>
+      <c r="F53" t="s">
+        <v>212</v>
+      </c>
+      <c r="G53" t="s">
+        <v>293</v>
+      </c>
+      <c r="H53" t="s">
+        <v>294</v>
+      </c>
+      <c r="I53" t="s">
+        <v>51</v>
+      </c>
+      <c r="J53" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="54" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" s="36">
+        <v>46226.5</v>
+      </c>
+      <c r="B54" t="s">
+        <v>391</v>
+      </c>
+      <c r="C54" t="s">
+        <v>392</v>
+      </c>
+      <c r="D54" t="s">
+        <v>393</v>
+      </c>
+      <c r="E54" t="s">
+        <v>371</v>
+      </c>
+      <c r="F54" t="s">
+        <v>394</v>
+      </c>
+      <c r="G54" t="s">
+        <v>395</v>
+      </c>
+      <c r="H54" t="s">
+        <v>396</v>
+      </c>
+      <c r="I54" t="s">
+        <v>50</v>
+      </c>
+      <c r="J54" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="55" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" s="36">
+        <v>46239.5</v>
+      </c>
+      <c r="B55" t="s">
+        <v>398</v>
+      </c>
+      <c r="C55" t="s">
+        <v>349</v>
+      </c>
+      <c r="D55" t="s">
+        <v>399</v>
+      </c>
+      <c r="E55" t="s">
+        <v>400</v>
+      </c>
+      <c r="F55" t="s">
+        <v>401</v>
+      </c>
+      <c r="G55" t="s">
+        <v>402</v>
+      </c>
+      <c r="H55" t="s">
+        <v>317</v>
+      </c>
+      <c r="I55" t="s">
+        <v>49</v>
+      </c>
+      <c r="J55" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="56" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" s="36">
+        <v>46247.5</v>
+      </c>
+      <c r="B56" t="s">
+        <v>404</v>
+      </c>
+      <c r="C56" t="s">
+        <v>349</v>
+      </c>
+      <c r="D56" t="s">
+        <v>405</v>
+      </c>
+      <c r="E56" t="s">
+        <v>406</v>
+      </c>
+      <c r="F56" t="s">
+        <v>407</v>
+      </c>
+      <c r="G56" t="s">
+        <v>408</v>
+      </c>
+      <c r="H56" t="s">
+        <v>170</v>
+      </c>
+      <c r="I56" t="s">
+        <v>49</v>
+      </c>
+      <c r="J56" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="57" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" s="36">
+        <v>46251.5</v>
+      </c>
+      <c r="B57" t="s">
+        <v>410</v>
+      </c>
+      <c r="C57" t="s">
+        <v>183</v>
+      </c>
+      <c r="D57" t="s">
+        <v>411</v>
+      </c>
+      <c r="E57" t="s">
+        <v>180</v>
+      </c>
+      <c r="F57" t="s">
+        <v>412</v>
+      </c>
+      <c r="G57" t="s">
+        <v>140</v>
+      </c>
+      <c r="H57" t="s">
+        <v>141</v>
+      </c>
+      <c r="I57" t="s">
+        <v>50</v>
+      </c>
+      <c r="J57" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="58" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" s="36">
+        <v>46247.5</v>
+      </c>
+      <c r="B58" t="s">
+        <v>413</v>
+      </c>
+      <c r="C58" t="s">
+        <v>183</v>
+      </c>
+      <c r="D58" t="s">
+        <v>414</v>
+      </c>
+      <c r="E58" t="s">
+        <v>415</v>
+      </c>
+      <c r="F58" t="s">
+        <v>416</v>
+      </c>
+      <c r="G58" t="s">
+        <v>417</v>
+      </c>
+      <c r="H58" t="s">
+        <v>97</v>
+      </c>
+      <c r="I58" t="s">
+        <v>49</v>
+      </c>
+      <c r="J58" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="59" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A59" s="36">
+        <v>46230.5</v>
+      </c>
+      <c r="B59" t="s">
+        <v>419</v>
+      </c>
+      <c r="C59" t="s">
+        <v>420</v>
+      </c>
+      <c r="D59" t="s">
+        <v>421</v>
+      </c>
+      <c r="E59" t="s">
+        <v>422</v>
+      </c>
+      <c r="F59" t="s">
+        <v>423</v>
+      </c>
+      <c r="G59" t="s">
+        <v>140</v>
+      </c>
+      <c r="H59" t="s">
+        <v>141</v>
+      </c>
+      <c r="I59" t="s">
+        <v>51</v>
+      </c>
+      <c r="J59" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="60" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A60" s="36">
+        <v>46246.5</v>
+      </c>
+      <c r="B60" t="s">
+        <v>425</v>
+      </c>
+      <c r="C60" t="s">
+        <v>183</v>
+      </c>
+      <c r="D60" t="s">
+        <v>426</v>
+      </c>
+      <c r="E60" t="s">
+        <v>427</v>
+      </c>
+      <c r="F60" t="s">
+        <v>428</v>
+      </c>
+      <c r="G60" t="s">
+        <v>429</v>
+      </c>
+      <c r="H60" t="s">
+        <v>157</v>
+      </c>
+      <c r="I60" t="s">
+        <v>50</v>
+      </c>
+      <c r="J60" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="61" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A61" s="36">
+        <v>46247.5</v>
+      </c>
+      <c r="B61" t="s">
+        <v>430</v>
+      </c>
+      <c r="C61" t="s">
+        <v>392</v>
+      </c>
+      <c r="D61" t="s">
+        <v>431</v>
+      </c>
+      <c r="E61" t="s">
+        <v>432</v>
+      </c>
+      <c r="F61" t="s">
+        <v>433</v>
+      </c>
+      <c r="G61" t="s">
+        <v>434</v>
+      </c>
+      <c r="H61" t="s">
+        <v>157</v>
+      </c>
+      <c r="I61" t="s">
+        <v>49</v>
+      </c>
+      <c r="J61" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="62" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A62" s="36">
+        <v>46234.5</v>
+      </c>
+      <c r="B62" t="s">
+        <v>435</v>
+      </c>
+      <c r="C62" t="s">
+        <v>384</v>
+      </c>
+      <c r="D62" t="s">
+        <v>436</v>
+      </c>
+      <c r="E62" t="s">
+        <v>437</v>
+      </c>
+      <c r="F62" t="s">
+        <v>438</v>
+      </c>
+      <c r="G62" t="s">
+        <v>343</v>
+      </c>
+      <c r="H62" t="s">
+        <v>97</v>
+      </c>
+      <c r="I62" t="s">
+        <v>50</v>
+      </c>
+      <c r="J62" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="63" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A63" s="36">
+        <v>46232.5</v>
+      </c>
+      <c r="B63" t="s">
+        <v>440</v>
+      </c>
+      <c r="C63" t="s">
+        <v>173</v>
+      </c>
+      <c r="D63" t="s">
+        <v>441</v>
+      </c>
+      <c r="E63" t="s">
+        <v>442</v>
+      </c>
+      <c r="F63" t="s">
+        <v>443</v>
+      </c>
+      <c r="G63" t="s">
+        <v>140</v>
+      </c>
+      <c r="H63" t="s">
+        <v>141</v>
+      </c>
+      <c r="I63" t="s">
+        <v>49</v>
+      </c>
+      <c r="J63" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="64" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A64" s="36">
+        <v>46225.5</v>
+      </c>
+      <c r="B64" t="s">
+        <v>445</v>
+      </c>
+      <c r="C64" t="s">
+        <v>255</v>
+      </c>
+      <c r="D64" t="s">
+        <v>446</v>
+      </c>
+      <c r="E64" t="s">
+        <v>447</v>
+      </c>
+      <c r="F64" t="s">
+        <v>448</v>
+      </c>
+      <c r="G64" t="s">
+        <v>449</v>
+      </c>
+      <c r="H64" t="s">
+        <v>157</v>
+      </c>
+      <c r="I64" t="s">
+        <v>51</v>
+      </c>
+      <c r="J64" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="65" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A65" s="36">
+        <v>46245.5</v>
+      </c>
+      <c r="B65" t="s">
+        <v>450</v>
+      </c>
+      <c r="C65" t="s">
+        <v>136</v>
+      </c>
+      <c r="D65" t="s">
+        <v>451</v>
+      </c>
+      <c r="E65" t="s">
+        <v>452</v>
+      </c>
+      <c r="F65" t="s">
+        <v>428</v>
+      </c>
+      <c r="G65" t="s">
+        <v>140</v>
+      </c>
+      <c r="H65" t="s">
+        <v>141</v>
+      </c>
+      <c r="I65" t="s">
+        <v>50</v>
+      </c>
+      <c r="J65" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="66" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66" s="36">
+        <v>46248.5</v>
+      </c>
+      <c r="B66" t="s">
+        <v>454</v>
+      </c>
+      <c r="C66" t="s">
+        <v>183</v>
+      </c>
+      <c r="D66" t="s">
+        <v>455</v>
+      </c>
+      <c r="E66" t="s">
+        <v>456</v>
+      </c>
+      <c r="F66" t="s">
+        <v>457</v>
+      </c>
+      <c r="G66" t="s">
+        <v>293</v>
+      </c>
+      <c r="H66" t="s">
+        <v>294</v>
+      </c>
+      <c r="I66" t="s">
+        <v>49</v>
+      </c>
+      <c r="J66" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="67" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A67" s="36">
+        <v>46227.5</v>
+      </c>
+      <c r="B67" t="s">
+        <v>459</v>
+      </c>
+      <c r="C67" t="s">
+        <v>136</v>
+      </c>
+      <c r="D67" t="s">
+        <v>460</v>
+      </c>
+      <c r="E67" t="s">
+        <v>461</v>
+      </c>
+      <c r="F67" t="s">
+        <v>462</v>
+      </c>
+      <c r="G67" t="s">
+        <v>140</v>
+      </c>
+      <c r="H67" t="s">
+        <v>141</v>
+      </c>
+      <c r="I67" t="s">
+        <v>51</v>
+      </c>
+      <c r="J67" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="68" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A68" s="36">
+        <v>46247.5</v>
+      </c>
+      <c r="B68" t="s">
+        <v>464</v>
+      </c>
+      <c r="C68" t="s">
+        <v>183</v>
+      </c>
+      <c r="D68" t="s">
+        <v>465</v>
+      </c>
+      <c r="E68" t="s">
+        <v>466</v>
+      </c>
+      <c r="F68" t="s">
+        <v>467</v>
+      </c>
+      <c r="G68" t="s">
+        <v>468</v>
+      </c>
+      <c r="H68" t="s">
+        <v>157</v>
+      </c>
+      <c r="I68" t="s">
+        <v>49</v>
+      </c>
+      <c r="J68" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="69" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A69" s="36">
+        <v>46244.5</v>
+      </c>
+      <c r="B69" t="s">
+        <v>469</v>
+      </c>
+      <c r="C69" t="s">
+        <v>145</v>
+      </c>
+      <c r="D69" t="s">
+        <v>470</v>
+      </c>
+      <c r="E69" t="s">
+        <v>471</v>
+      </c>
+      <c r="F69" t="s">
+        <v>472</v>
+      </c>
+      <c r="G69" t="s">
+        <v>473</v>
+      </c>
+      <c r="H69" t="s">
+        <v>157</v>
+      </c>
+      <c r="I69" t="s">
+        <v>49</v>
+      </c>
+      <c r="J69" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="70" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A70" s="36">
+        <v>46230.5</v>
+      </c>
+      <c r="B70" t="s">
+        <v>474</v>
+      </c>
+      <c r="C70" t="s">
+        <v>145</v>
+      </c>
+      <c r="D70" t="s">
+        <v>475</v>
+      </c>
+      <c r="E70" t="s">
+        <v>476</v>
+      </c>
+      <c r="F70" t="s">
+        <v>477</v>
+      </c>
+      <c r="G70" t="s">
+        <v>140</v>
+      </c>
+      <c r="H70" t="s">
+        <v>141</v>
+      </c>
+      <c r="I70" t="s">
+        <v>49</v>
+      </c>
+      <c r="J70" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="71" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A71" s="36">
+        <v>46241.5</v>
+      </c>
+      <c r="B71" t="s">
+        <v>479</v>
+      </c>
+      <c r="C71" t="s">
+        <v>255</v>
+      </c>
+      <c r="D71" t="s">
+        <v>480</v>
+      </c>
+      <c r="E71" t="s">
+        <v>481</v>
+      </c>
+      <c r="F71" t="s">
+        <v>482</v>
+      </c>
+      <c r="G71" t="s">
+        <v>483</v>
+      </c>
+      <c r="H71" t="s">
+        <v>364</v>
+      </c>
+      <c r="I71" t="s">
+        <v>50</v>
+      </c>
+      <c r="J71" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="72" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A72" s="36">
+        <v>46252.5</v>
+      </c>
+      <c r="B72" t="s">
+        <v>485</v>
+      </c>
+      <c r="C72" t="s">
+        <v>384</v>
+      </c>
+      <c r="D72" t="s">
+        <v>486</v>
+      </c>
+      <c r="E72" t="s">
+        <v>288</v>
+      </c>
+      <c r="F72" t="s">
+        <v>487</v>
+      </c>
+      <c r="G72" t="s">
+        <v>488</v>
+      </c>
+      <c r="H72" t="s">
+        <v>489</v>
+      </c>
+      <c r="I72" t="s">
+        <v>51</v>
+      </c>
+      <c r="J72" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="73" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A73" s="36">
+        <v>46239.5</v>
+      </c>
+      <c r="B73" t="s">
+        <v>491</v>
+      </c>
+      <c r="C73" t="s">
+        <v>165</v>
+      </c>
+      <c r="D73" t="s">
+        <v>492</v>
+      </c>
+      <c r="E73" t="s">
+        <v>493</v>
+      </c>
+      <c r="F73" t="s">
+        <v>494</v>
+      </c>
+      <c r="G73" t="s">
+        <v>169</v>
+      </c>
+      <c r="H73" t="s">
+        <v>170</v>
+      </c>
+      <c r="I73" t="s">
+        <v>50</v>
+      </c>
+      <c r="J73" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="74" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A74" s="36">
+        <v>46247.5</v>
+      </c>
+      <c r="B74" t="s">
+        <v>495</v>
+      </c>
+      <c r="C74" t="s">
+        <v>183</v>
+      </c>
+      <c r="D74" t="s">
+        <v>496</v>
+      </c>
+      <c r="E74" t="s">
+        <v>497</v>
+      </c>
+      <c r="F74" t="s">
+        <v>472</v>
+      </c>
+      <c r="G74" t="s">
+        <v>498</v>
+      </c>
+      <c r="H74" t="s">
+        <v>149</v>
+      </c>
+      <c r="I74" t="s">
+        <v>49</v>
+      </c>
+      <c r="J74" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="75" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A75" s="36">
+        <v>46234.5</v>
+      </c>
+      <c r="B75" t="s">
+        <v>324</v>
+      </c>
+      <c r="C75" t="s">
+        <v>146</v>
+      </c>
+      <c r="D75" t="s">
+        <v>325</v>
+      </c>
+      <c r="E75" t="s">
+        <v>499</v>
+      </c>
+      <c r="F75" t="s">
+        <v>500</v>
+      </c>
+      <c r="G75" t="s">
+        <v>146</v>
+      </c>
+      <c r="H75" t="s">
+        <v>146</v>
+      </c>
+      <c r="I75" t="s">
+        <v>50</v>
+      </c>
+      <c r="J75" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="76" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A76" s="36">
+        <v>46245.5</v>
+      </c>
+      <c r="B76" t="s">
+        <v>501</v>
+      </c>
+      <c r="C76" t="s">
+        <v>502</v>
+      </c>
+      <c r="D76" t="s">
+        <v>503</v>
+      </c>
+      <c r="E76" t="s">
+        <v>504</v>
+      </c>
+      <c r="F76" t="s">
+        <v>505</v>
+      </c>
+      <c r="G76" t="s">
+        <v>293</v>
+      </c>
+      <c r="H76" t="s">
+        <v>294</v>
+      </c>
+      <c r="I76" t="s">
+        <v>50</v>
+      </c>
+      <c r="J76" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="77" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A77" s="36">
+        <v>46245.5</v>
+      </c>
+      <c r="B77" t="s">
+        <v>507</v>
+      </c>
+      <c r="C77" t="s">
+        <v>165</v>
+      </c>
+      <c r="D77" t="s">
+        <v>508</v>
+      </c>
+      <c r="E77" t="s">
+        <v>509</v>
+      </c>
+      <c r="F77" t="s">
+        <v>428</v>
+      </c>
+      <c r="G77" t="s">
+        <v>347</v>
+      </c>
+      <c r="H77" t="s">
+        <v>317</v>
+      </c>
+      <c r="I77" t="s">
+        <v>50</v>
+      </c>
+      <c r="J77" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="78" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A78" s="36">
+        <v>46231.5</v>
+      </c>
+      <c r="B78" t="s">
+        <v>510</v>
+      </c>
+      <c r="C78" t="s">
+        <v>349</v>
+      </c>
+      <c r="D78" t="s">
+        <v>511</v>
+      </c>
+      <c r="E78" t="s">
+        <v>512</v>
+      </c>
+      <c r="F78" t="s">
+        <v>513</v>
+      </c>
+      <c r="G78" t="s">
+        <v>347</v>
+      </c>
+      <c r="H78" t="s">
+        <v>317</v>
+      </c>
+      <c r="I78" t="s">
+        <v>51</v>
+      </c>
+      <c r="J78" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="79" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A79" s="36">
+        <v>46252.5</v>
+      </c>
+      <c r="B79" t="s">
+        <v>515</v>
+      </c>
+      <c r="C79" t="s">
+        <v>183</v>
+      </c>
+      <c r="D79" t="s">
+        <v>516</v>
+      </c>
+      <c r="E79" t="s">
+        <v>517</v>
+      </c>
+      <c r="F79" t="s">
+        <v>518</v>
+      </c>
+      <c r="G79" t="s">
+        <v>519</v>
+      </c>
+      <c r="H79" t="s">
+        <v>141</v>
+      </c>
+      <c r="I79" t="s">
+        <v>49</v>
+      </c>
+      <c r="J79" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="80" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A80" s="36">
+        <v>46248.5</v>
+      </c>
+      <c r="B80" t="s">
+        <v>520</v>
+      </c>
+      <c r="C80" t="s">
+        <v>240</v>
+      </c>
+      <c r="D80" t="s">
+        <v>521</v>
+      </c>
+      <c r="E80" t="s">
+        <v>522</v>
+      </c>
+      <c r="F80" t="s">
+        <v>523</v>
+      </c>
+      <c r="G80" t="s">
+        <v>343</v>
+      </c>
+      <c r="H80" t="s">
+        <v>97</v>
+      </c>
+      <c r="I80" t="s">
+        <v>49</v>
+      </c>
+      <c r="J80" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="81" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A81" s="36">
+        <v>46244.5</v>
+      </c>
+      <c r="B81" t="s">
+        <v>525</v>
+      </c>
+      <c r="C81" t="s">
+        <v>183</v>
+      </c>
+      <c r="D81" t="s">
+        <v>526</v>
+      </c>
+      <c r="E81" t="s">
+        <v>527</v>
+      </c>
+      <c r="F81" t="s">
+        <v>528</v>
+      </c>
+      <c r="G81" t="s">
+        <v>529</v>
+      </c>
+      <c r="H81" t="s">
+        <v>489</v>
+      </c>
+      <c r="I81" t="s">
+        <v>49</v>
+      </c>
+      <c r="J81" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="82" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A82" s="36">
+        <v>46246.5</v>
+      </c>
+      <c r="B82" t="s">
+        <v>531</v>
+      </c>
+      <c r="C82" t="s">
+        <v>392</v>
+      </c>
+      <c r="D82" t="s">
+        <v>532</v>
+      </c>
+      <c r="E82" t="s">
+        <v>533</v>
+      </c>
+      <c r="F82" t="s">
+        <v>206</v>
+      </c>
+      <c r="G82" t="s">
+        <v>140</v>
+      </c>
+      <c r="H82" t="s">
+        <v>141</v>
+      </c>
+      <c r="I82" t="s">
+        <v>50</v>
+      </c>
+      <c r="J82" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="83" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A83" s="36">
+        <v>46251.5</v>
+      </c>
+      <c r="B83" t="s">
+        <v>535</v>
+      </c>
+      <c r="C83" t="s">
+        <v>255</v>
+      </c>
+      <c r="D83" t="s">
+        <v>536</v>
+      </c>
+      <c r="E83" t="s">
+        <v>537</v>
+      </c>
+      <c r="F83" t="s">
+        <v>538</v>
+      </c>
+      <c r="G83" t="s">
+        <v>539</v>
+      </c>
+      <c r="H83" t="s">
+        <v>252</v>
+      </c>
+      <c r="I83" t="s">
+        <v>50</v>
+      </c>
+      <c r="J83" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="84" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A84" s="36">
+        <v>46245.5</v>
+      </c>
+      <c r="B84" t="s">
+        <v>540</v>
+      </c>
+      <c r="C84" t="s">
+        <v>146</v>
+      </c>
+      <c r="D84" t="s">
+        <v>541</v>
+      </c>
+      <c r="E84" t="s">
+        <v>542</v>
+      </c>
+      <c r="F84" t="s">
+        <v>472</v>
+      </c>
+      <c r="G84" t="s">
+        <v>543</v>
+      </c>
+      <c r="H84" t="s">
+        <v>303</v>
+      </c>
+      <c r="I84" t="s">
+        <v>49</v>
+      </c>
+      <c r="J84" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="85" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A85" s="36">
+        <v>46246.5</v>
+      </c>
+      <c r="B85" t="s">
+        <v>544</v>
+      </c>
+      <c r="C85" t="s">
+        <v>146</v>
+      </c>
+      <c r="D85" t="s">
+        <v>545</v>
+      </c>
+      <c r="E85" t="s">
+        <v>546</v>
+      </c>
+      <c r="F85" t="s">
+        <v>428</v>
+      </c>
+      <c r="G85" t="s">
+        <v>200</v>
+      </c>
+      <c r="H85" t="s">
+        <v>141</v>
+      </c>
+      <c r="I85" t="s">
+        <v>50</v>
+      </c>
+      <c r="J85" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="86" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A86" s="36">
+        <v>46237.5</v>
+      </c>
+      <c r="B86" t="s">
+        <v>547</v>
+      </c>
+      <c r="C86" t="s">
+        <v>146</v>
+      </c>
+      <c r="D86" t="s">
+        <v>146</v>
+      </c>
+      <c r="E86" t="s">
+        <v>548</v>
+      </c>
+      <c r="F86" t="s">
+        <v>549</v>
+      </c>
+      <c r="G86" t="s">
+        <v>146</v>
+      </c>
+      <c r="H86" t="s">
+        <v>146</v>
+      </c>
+      <c r="I86" t="s">
+        <v>51</v>
+      </c>
+      <c r="J86" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="87" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A87" s="36">
+        <v>46226.5</v>
+      </c>
+      <c r="B87" t="s">
+        <v>550</v>
+      </c>
+      <c r="C87" t="s">
+        <v>165</v>
+      </c>
+      <c r="D87" t="s">
+        <v>551</v>
+      </c>
+      <c r="E87" t="s">
+        <v>552</v>
+      </c>
+      <c r="F87" t="s">
+        <v>553</v>
+      </c>
+      <c r="G87" t="s">
+        <v>554</v>
+      </c>
+      <c r="H87" t="s">
+        <v>157</v>
+      </c>
+      <c r="I87" t="s">
+        <v>49</v>
+      </c>
+      <c r="J87" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="88" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A88" s="36">
+        <v>46248.5</v>
+      </c>
+      <c r="B88" t="s">
+        <v>556</v>
+      </c>
+      <c r="C88" t="s">
+        <v>145</v>
+      </c>
+      <c r="D88" t="s">
+        <v>557</v>
+      </c>
+      <c r="E88" t="s">
+        <v>558</v>
+      </c>
+      <c r="F88" t="s">
+        <v>206</v>
+      </c>
+      <c r="G88" t="s">
+        <v>140</v>
+      </c>
+      <c r="H88" t="s">
+        <v>141</v>
+      </c>
+      <c r="I88" t="s">
+        <v>49</v>
+      </c>
+      <c r="J88" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="89" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A89" s="36">
+        <v>46240.5</v>
+      </c>
+      <c r="B89" t="s">
+        <v>559</v>
+      </c>
+      <c r="C89" t="s">
+        <v>233</v>
+      </c>
+      <c r="D89" t="s">
+        <v>560</v>
+      </c>
+      <c r="E89" t="s">
+        <v>561</v>
+      </c>
+      <c r="F89" t="s">
+        <v>562</v>
+      </c>
+      <c r="G89" t="s">
+        <v>372</v>
+      </c>
+      <c r="H89" t="s">
+        <v>271</v>
+      </c>
+      <c r="I89" t="s">
+        <v>50</v>
+      </c>
+      <c r="J89" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="90" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A90" s="36">
+        <v>46217.5</v>
+      </c>
+      <c r="B90" t="s">
+        <v>563</v>
+      </c>
+      <c r="C90" t="s">
+        <v>183</v>
+      </c>
+      <c r="D90" t="s">
+        <v>564</v>
+      </c>
+      <c r="E90" t="s">
+        <v>565</v>
+      </c>
+      <c r="F90" t="s">
+        <v>407</v>
+      </c>
+      <c r="G90" t="s">
+        <v>566</v>
+      </c>
+      <c r="H90" t="s">
+        <v>170</v>
+      </c>
+      <c r="I90" t="s">
+        <v>49</v>
+      </c>
+      <c r="J90" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="91" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A91" s="36">
+        <v>46218.5</v>
+      </c>
+      <c r="B91" t="s">
+        <v>567</v>
+      </c>
+      <c r="C91" t="s">
+        <v>240</v>
+      </c>
+      <c r="D91" t="s">
+        <v>568</v>
+      </c>
+      <c r="E91" t="s">
+        <v>569</v>
+      </c>
+      <c r="F91" t="s">
+        <v>206</v>
+      </c>
+      <c r="G91" t="s">
+        <v>473</v>
+      </c>
+      <c r="H91" t="s">
+        <v>157</v>
+      </c>
+      <c r="I91" t="s">
+        <v>49</v>
+      </c>
+      <c r="J91" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="92" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A92" s="36">
+        <v>46218.5</v>
+      </c>
+      <c r="B92" t="s">
+        <v>570</v>
+      </c>
+      <c r="C92" t="s">
+        <v>420</v>
+      </c>
+      <c r="D92" t="s">
+        <v>571</v>
+      </c>
+      <c r="E92" t="s">
+        <v>572</v>
+      </c>
+      <c r="F92" t="s">
+        <v>573</v>
+      </c>
+      <c r="G92" t="s">
+        <v>574</v>
+      </c>
+      <c r="H92" t="s">
+        <v>141</v>
+      </c>
+      <c r="I92" t="s">
+        <v>49</v>
+      </c>
+      <c r="J92" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="93" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A93" s="36">
+        <v>46219.5</v>
+      </c>
+      <c r="B93" t="s">
+        <v>575</v>
+      </c>
+      <c r="C93" t="s">
+        <v>349</v>
+      </c>
+      <c r="D93" t="s">
+        <v>576</v>
+      </c>
+      <c r="E93" t="s">
+        <v>577</v>
+      </c>
+      <c r="F93" t="s">
+        <v>487</v>
+      </c>
+      <c r="G93" t="s">
+        <v>578</v>
+      </c>
+      <c r="H93" t="s">
+        <v>170</v>
+      </c>
+      <c r="I93" t="s">
+        <v>49</v>
+      </c>
+      <c r="J93" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="94" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A94" s="36">
+        <v>46225.5</v>
+      </c>
+      <c r="B94" t="s">
+        <v>580</v>
+      </c>
+      <c r="C94" t="s">
+        <v>183</v>
+      </c>
+      <c r="D94" t="s">
+        <v>581</v>
+      </c>
+      <c r="E94" t="s">
+        <v>582</v>
+      </c>
+      <c r="F94" t="s">
+        <v>472</v>
+      </c>
+      <c r="G94" t="s">
+        <v>140</v>
+      </c>
+      <c r="H94" t="s">
+        <v>141</v>
+      </c>
+      <c r="I94" t="s">
+        <v>49</v>
+      </c>
+      <c r="J94" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="95" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A95" s="36">
+        <v>46226.5</v>
+      </c>
+      <c r="B95" t="s">
+        <v>583</v>
+      </c>
+      <c r="C95" t="s">
+        <v>136</v>
+      </c>
+      <c r="D95" t="s">
+        <v>584</v>
+      </c>
+      <c r="E95" t="s">
+        <v>585</v>
+      </c>
+      <c r="F95" t="s">
+        <v>586</v>
+      </c>
+      <c r="G95" t="s">
+        <v>140</v>
+      </c>
+      <c r="H95" t="s">
+        <v>141</v>
+      </c>
+      <c r="I95" t="s">
+        <v>197</v>
+      </c>
+      <c r="J95" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="96" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A96" s="36">
+        <v>46227.5</v>
+      </c>
+      <c r="B96" t="s">
+        <v>587</v>
+      </c>
+      <c r="C96" t="s">
+        <v>255</v>
+      </c>
+      <c r="D96" t="s">
+        <v>588</v>
+      </c>
+      <c r="E96" t="s">
+        <v>589</v>
+      </c>
+      <c r="F96" t="s">
+        <v>407</v>
+      </c>
+      <c r="G96" t="s">
+        <v>590</v>
+      </c>
+      <c r="H96" t="s">
+        <v>303</v>
+      </c>
+      <c r="I96" t="s">
+        <v>49</v>
+      </c>
+      <c r="J96" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="97" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A97" s="36">
+        <v>46213.5</v>
+      </c>
+      <c r="B97" t="s">
+        <v>591</v>
+      </c>
+      <c r="C97" t="s">
+        <v>384</v>
+      </c>
+      <c r="D97" t="s">
+        <v>592</v>
+      </c>
+      <c r="E97" t="s">
+        <v>593</v>
+      </c>
+      <c r="F97" t="s">
+        <v>594</v>
+      </c>
+      <c r="G97" t="s">
+        <v>343</v>
+      </c>
+      <c r="H97" t="s">
+        <v>97</v>
+      </c>
+      <c r="I97" t="s">
+        <v>49</v>
+      </c>
+      <c r="J97" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="98" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A98" s="36">
+        <v>46248.5</v>
+      </c>
+      <c r="B98" t="s">
+        <v>595</v>
+      </c>
+      <c r="C98" t="s">
+        <v>255</v>
+      </c>
+      <c r="D98" t="s">
+        <v>596</v>
+      </c>
+      <c r="E98" t="s">
+        <v>597</v>
+      </c>
+      <c r="F98" t="s">
+        <v>598</v>
+      </c>
+      <c r="G98" t="s">
+        <v>473</v>
+      </c>
+      <c r="H98" t="s">
+        <v>157</v>
+      </c>
+      <c r="I98" t="s">
+        <v>49</v>
+      </c>
+      <c r="J98" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="99" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A99" s="36">
+        <v>46251.5</v>
+      </c>
+      <c r="B99" t="s">
+        <v>600</v>
+      </c>
+      <c r="C99" t="s">
+        <v>165</v>
+      </c>
+      <c r="D99" t="s">
+        <v>601</v>
+      </c>
+      <c r="E99" t="s">
+        <v>602</v>
+      </c>
+      <c r="F99" t="s">
+        <v>603</v>
+      </c>
+      <c r="G99" t="s">
+        <v>604</v>
+      </c>
+      <c r="H99" t="s">
+        <v>396</v>
+      </c>
+      <c r="I99" t="s">
+        <v>50</v>
+      </c>
+      <c r="J99" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="100" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A100" s="36">
+        <v>46233.5</v>
+      </c>
+      <c r="B100" t="s">
+        <v>606</v>
+      </c>
+      <c r="C100" t="s">
+        <v>240</v>
+      </c>
+      <c r="D100" t="s">
+        <v>607</v>
+      </c>
+      <c r="E100" t="s">
+        <v>608</v>
+      </c>
+      <c r="F100" t="s">
+        <v>505</v>
+      </c>
+      <c r="G100" t="s">
+        <v>244</v>
+      </c>
+      <c r="H100" t="s">
+        <v>149</v>
+      </c>
+      <c r="I100" t="s">
+        <v>50</v>
+      </c>
+      <c r="J100" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="101" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A101" s="36">
+        <v>46239.5</v>
+      </c>
+      <c r="B101" t="s">
+        <v>610</v>
+      </c>
+      <c r="C101" t="s">
+        <v>183</v>
+      </c>
+      <c r="D101" t="s">
+        <v>611</v>
+      </c>
+      <c r="E101" t="s">
+        <v>612</v>
+      </c>
+      <c r="F101" t="s">
+        <v>613</v>
+      </c>
+      <c r="G101" t="s">
+        <v>614</v>
+      </c>
+      <c r="H101" t="s">
+        <v>271</v>
+      </c>
+      <c r="I101" t="s">
+        <v>51</v>
+      </c>
+      <c r="J101" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="102" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A102" s="36">
+        <v>46246.5</v>
+      </c>
+      <c r="B102" t="s">
+        <v>615</v>
+      </c>
+      <c r="C102" t="s">
+        <v>146</v>
+      </c>
+      <c r="D102" t="s">
+        <v>616</v>
+      </c>
+      <c r="E102" t="s">
+        <v>617</v>
+      </c>
+      <c r="F102" t="s">
+        <v>618</v>
+      </c>
+      <c r="G102" t="s">
+        <v>146</v>
+      </c>
+      <c r="H102" t="s">
+        <v>146</v>
+      </c>
+      <c r="I102" t="s">
+        <v>50</v>
+      </c>
+      <c r="J102" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="103" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A103" s="36">
+        <v>46248.5</v>
+      </c>
+      <c r="B103" t="s">
+        <v>620</v>
+      </c>
+      <c r="C103" t="s">
+        <v>286</v>
+      </c>
+      <c r="D103" t="s">
+        <v>621</v>
+      </c>
+      <c r="E103" t="s">
+        <v>622</v>
+      </c>
+      <c r="F103" t="s">
+        <v>623</v>
+      </c>
+      <c r="G103" t="s">
+        <v>624</v>
+      </c>
+      <c r="H103" t="s">
+        <v>157</v>
+      </c>
+      <c r="I103" t="s">
+        <v>49</v>
+      </c>
+      <c r="J103" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="104" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A104" s="36">
+        <v>46248.5</v>
+      </c>
+      <c r="B104" t="s">
+        <v>626</v>
+      </c>
+      <c r="C104" t="s">
+        <v>627</v>
+      </c>
+      <c r="D104" t="s">
+        <v>628</v>
+      </c>
+      <c r="E104" t="s">
+        <v>629</v>
+      </c>
+      <c r="F104" t="s">
+        <v>630</v>
+      </c>
+      <c r="G104" t="s">
+        <v>270</v>
+      </c>
+      <c r="H104" t="s">
+        <v>271</v>
+      </c>
+      <c r="I104" t="s">
+        <v>49</v>
+      </c>
+      <c r="J104" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="105" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A105" s="36">
+        <v>46238.5</v>
+      </c>
+      <c r="B105" t="s">
+        <v>631</v>
+      </c>
+      <c r="C105" t="s">
+        <v>349</v>
+      </c>
+      <c r="D105" t="s">
+        <v>632</v>
+      </c>
+      <c r="E105" t="s">
+        <v>633</v>
+      </c>
+      <c r="F105" t="s">
+        <v>634</v>
+      </c>
+      <c r="G105" t="s">
+        <v>372</v>
+      </c>
+      <c r="H105" t="s">
+        <v>271</v>
+      </c>
+      <c r="I105" t="s">
+        <v>49</v>
+      </c>
+      <c r="J105" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="106" ht="15" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A106" s="36">
+        <v>46239.5</v>
+      </c>
+      <c r="B106" t="s">
+        <v>635</v>
+      </c>
+      <c r="C106" t="s">
+        <v>349</v>
+      </c>
+      <c r="D106" t="s">
+        <v>636</v>
+      </c>
+      <c r="E106" t="s">
+        <v>637</v>
+      </c>
+      <c r="F106" t="s">
+        <v>638</v>
+      </c>
+      <c r="G106" t="s">
+        <v>639</v>
+      </c>
+      <c r="H106" t="s">
+        <v>396</v>
+      </c>
+      <c r="I106" t="s">
+        <v>51</v>
+      </c>
+      <c r="J106" t="s">
+        <v>640</v>
+      </c>
     </row>
     <row r="107" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" s="36"/>
@@ -10924,7 +13232,7 @@
   <sheetData>
     <row r="1" ht="21.75" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
-        <v>383</v>
+        <v>641</v>
       </c>
       <c r="B1" s="13" t="s">
         <v>36</v>
@@ -10936,10 +13244,10 @@
         <v>89</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>384</v>
+        <v>642</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>385</v>
+        <v>643</v>
       </c>
     </row>
     <row r="2" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10950,16 +13258,16 @@
         <v>50</v>
       </c>
       <c r="C2" t="s">
-        <v>386</v>
+        <v>644</v>
       </c>
       <c r="D2" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E2" t="s">
         <v>61</v>
       </c>
       <c r="F2" t="s">
-        <v>388</v>
+        <v>646</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10970,16 +13278,16 @@
         <v>50</v>
       </c>
       <c r="C3" t="s">
-        <v>389</v>
+        <v>647</v>
       </c>
       <c r="D3" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E3" t="s">
         <v>60</v>
       </c>
       <c r="F3" t="s">
-        <v>390</v>
+        <v>648</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10990,16 +13298,16 @@
         <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>391</v>
+        <v>649</v>
       </c>
       <c r="D4" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E4" t="s">
         <v>60</v>
       </c>
       <c r="F4" t="s">
-        <v>392</v>
+        <v>650</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11010,16 +13318,16 @@
         <v>50</v>
       </c>
       <c r="C5" t="s">
-        <v>393</v>
+        <v>651</v>
       </c>
       <c r="D5" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E5" t="s">
         <v>64</v>
       </c>
       <c r="F5" t="s">
-        <v>394</v>
+        <v>652</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11030,16 +13338,16 @@
         <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>395</v>
+        <v>653</v>
       </c>
       <c r="D6" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E6" t="s">
         <v>62</v>
       </c>
       <c r="F6" t="s">
-        <v>396</v>
+        <v>654</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11053,13 +13361,13 @@
         <v>267</v>
       </c>
       <c r="D7" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E7" t="s">
         <v>66</v>
       </c>
       <c r="F7" t="s">
-        <v>397</v>
+        <v>655</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11070,16 +13378,16 @@
         <v>50</v>
       </c>
       <c r="C8" t="s">
-        <v>398</v>
+        <v>656</v>
       </c>
       <c r="D8" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E8" t="s">
         <v>61</v>
       </c>
       <c r="F8" t="s">
-        <v>399</v>
+        <v>657</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11090,16 +13398,16 @@
         <v>50</v>
       </c>
       <c r="C9" t="s">
-        <v>400</v>
+        <v>658</v>
       </c>
       <c r="D9" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E9" t="s">
         <v>61</v>
       </c>
       <c r="F9" t="s">
-        <v>401</v>
+        <v>659</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11110,16 +13418,16 @@
         <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>402</v>
+        <v>660</v>
       </c>
       <c r="D10" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E10" t="s">
         <v>60</v>
       </c>
       <c r="F10" t="s">
-        <v>403</v>
+        <v>661</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11130,16 +13438,16 @@
         <v>50</v>
       </c>
       <c r="C11" t="s">
-        <v>402</v>
+        <v>660</v>
       </c>
       <c r="D11" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E11" t="s">
         <v>61</v>
       </c>
       <c r="F11" t="s">
-        <v>404</v>
+        <v>662</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11150,16 +13458,16 @@
         <v>50</v>
       </c>
       <c r="C12" t="s">
-        <v>405</v>
+        <v>663</v>
       </c>
       <c r="D12" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E12" t="s">
         <v>63</v>
       </c>
       <c r="F12" t="s">
-        <v>406</v>
+        <v>664</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11170,16 +13478,16 @@
         <v>50</v>
       </c>
       <c r="C13" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D13" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E13" t="s">
         <v>61</v>
       </c>
       <c r="F13" t="s">
-        <v>408</v>
+        <v>665</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11190,16 +13498,16 @@
         <v>50</v>
       </c>
       <c r="C14" t="s">
-        <v>409</v>
+        <v>666</v>
       </c>
       <c r="D14" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E14" t="s">
         <v>61</v>
       </c>
       <c r="F14" t="s">
-        <v>410</v>
+        <v>667</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11210,16 +13518,16 @@
         <v>50</v>
       </c>
       <c r="C15" t="s">
-        <v>411</v>
+        <v>668</v>
       </c>
       <c r="D15" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E15" t="s">
         <v>61</v>
       </c>
       <c r="F15" t="s">
-        <v>412</v>
+        <v>669</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11230,16 +13538,16 @@
         <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>413</v>
+        <v>670</v>
       </c>
       <c r="D16" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E16" t="s">
         <v>61</v>
       </c>
       <c r="F16" t="s">
-        <v>414</v>
+        <v>671</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11250,16 +13558,16 @@
         <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>415</v>
+        <v>672</v>
       </c>
       <c r="D17" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E17" t="s">
         <v>61</v>
       </c>
       <c r="F17" t="s">
-        <v>416</v>
+        <v>673</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11270,16 +13578,16 @@
         <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>417</v>
+        <v>674</v>
       </c>
       <c r="D18" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E18" t="s">
         <v>61</v>
       </c>
       <c r="F18" t="s">
-        <v>418</v>
+        <v>675</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11290,16 +13598,16 @@
         <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>419</v>
+        <v>676</v>
       </c>
       <c r="D19" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E19" t="s">
         <v>60</v>
       </c>
       <c r="F19" t="s">
-        <v>420</v>
+        <v>677</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11310,16 +13618,16 @@
         <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>421</v>
+        <v>678</v>
       </c>
       <c r="D20" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E20" t="s">
         <v>64</v>
       </c>
       <c r="F20" t="s">
-        <v>422</v>
+        <v>679</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11333,13 +13641,13 @@
         <v>254</v>
       </c>
       <c r="D21" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E21" t="s">
         <v>66</v>
       </c>
       <c r="F21" t="s">
-        <v>423</v>
+        <v>680</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11350,16 +13658,16 @@
         <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>402</v>
+        <v>660</v>
       </c>
       <c r="D22" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E22" t="s">
         <v>60</v>
       </c>
       <c r="F22" t="s">
-        <v>424</v>
+        <v>681</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11373,13 +13681,13 @@
         <v>254</v>
       </c>
       <c r="D23" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E23" t="s">
         <v>61</v>
       </c>
       <c r="F23" t="s">
-        <v>425</v>
+        <v>682</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11390,16 +13698,16 @@
         <v>50</v>
       </c>
       <c r="C24" t="s">
-        <v>426</v>
+        <v>683</v>
       </c>
       <c r="D24" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E24" t="s">
         <v>62</v>
       </c>
       <c r="F24" t="s">
-        <v>427</v>
+        <v>684</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11410,16 +13718,16 @@
         <v>50</v>
       </c>
       <c r="C25" t="s">
-        <v>389</v>
+        <v>647</v>
       </c>
       <c r="D25" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E25" t="s">
         <v>61</v>
       </c>
       <c r="F25" t="s">
-        <v>428</v>
+        <v>685</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11430,16 +13738,16 @@
         <v>50</v>
       </c>
       <c r="C26" t="s">
-        <v>429</v>
+        <v>491</v>
       </c>
       <c r="D26" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E26" t="s">
         <v>60</v>
       </c>
       <c r="F26" t="s">
-        <v>430</v>
+        <v>686</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11450,16 +13758,16 @@
         <v>50</v>
       </c>
       <c r="C27" t="s">
-        <v>431</v>
+        <v>687</v>
       </c>
       <c r="D27" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E27" t="s">
         <v>64</v>
       </c>
       <c r="F27" t="s">
-        <v>432</v>
+        <v>688</v>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11473,13 +13781,13 @@
         <v>239</v>
       </c>
       <c r="D28" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E28" t="s">
         <v>60</v>
       </c>
       <c r="F28" t="s">
-        <v>433</v>
+        <v>689</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11490,16 +13798,16 @@
         <v>50</v>
       </c>
       <c r="C29" t="s">
-        <v>434</v>
+        <v>690</v>
       </c>
       <c r="D29" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E29" t="s">
         <v>60</v>
       </c>
       <c r="F29" t="s">
-        <v>435</v>
+        <v>691</v>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11510,16 +13818,16 @@
         <v>50</v>
       </c>
       <c r="C30" t="s">
-        <v>434</v>
+        <v>690</v>
       </c>
       <c r="D30" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E30" t="s">
         <v>60</v>
       </c>
       <c r="F30" t="s">
-        <v>436</v>
+        <v>692</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11530,16 +13838,16 @@
         <v>50</v>
       </c>
       <c r="C31" t="s">
-        <v>437</v>
+        <v>693</v>
       </c>
       <c r="D31" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E31" t="s">
         <v>60</v>
       </c>
       <c r="F31" t="s">
-        <v>438</v>
+        <v>694</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11550,16 +13858,16 @@
         <v>50</v>
       </c>
       <c r="C32" t="s">
-        <v>439</v>
+        <v>507</v>
       </c>
       <c r="D32" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E32" t="s">
         <v>60</v>
       </c>
       <c r="F32" t="s">
-        <v>440</v>
+        <v>695</v>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11573,13 +13881,13 @@
         <v>232</v>
       </c>
       <c r="D33" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E33" t="s">
         <v>61</v>
       </c>
       <c r="F33" t="s">
-        <v>441</v>
+        <v>696</v>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11590,16 +13898,16 @@
         <v>50</v>
       </c>
       <c r="C34" t="s">
-        <v>442</v>
+        <v>697</v>
       </c>
       <c r="D34" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E34" t="s">
         <v>60</v>
       </c>
       <c r="F34" t="s">
-        <v>443</v>
+        <v>698</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11610,16 +13918,16 @@
         <v>50</v>
       </c>
       <c r="C35" t="s">
-        <v>442</v>
+        <v>697</v>
       </c>
       <c r="D35" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E35" t="s">
         <v>61</v>
       </c>
       <c r="F35" t="s">
-        <v>444</v>
+        <v>699</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11630,16 +13938,16 @@
         <v>50</v>
       </c>
       <c r="C36" t="s">
-        <v>445</v>
+        <v>700</v>
       </c>
       <c r="D36" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E36" t="s">
         <v>61</v>
       </c>
       <c r="F36" t="s">
-        <v>446</v>
+        <v>701</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11650,16 +13958,16 @@
         <v>50</v>
       </c>
       <c r="C37" t="s">
-        <v>445</v>
+        <v>700</v>
       </c>
       <c r="D37" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E37" t="s">
         <v>63</v>
       </c>
       <c r="F37" t="s">
-        <v>447</v>
+        <v>702</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11670,16 +13978,16 @@
         <v>50</v>
       </c>
       <c r="C38" t="s">
-        <v>448</v>
+        <v>703</v>
       </c>
       <c r="D38" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E38" t="s">
         <v>61</v>
       </c>
       <c r="F38" t="s">
-        <v>449</v>
+        <v>704</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11690,16 +13998,16 @@
         <v>50</v>
       </c>
       <c r="C39" t="s">
-        <v>450</v>
+        <v>705</v>
       </c>
       <c r="D39" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E39" t="s">
         <v>60</v>
       </c>
       <c r="F39" t="s">
-        <v>451</v>
+        <v>706</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11710,16 +14018,16 @@
         <v>50</v>
       </c>
       <c r="C40" t="s">
-        <v>452</v>
+        <v>707</v>
       </c>
       <c r="D40" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E40" t="s">
         <v>60</v>
       </c>
       <c r="F40" t="s">
-        <v>453</v>
+        <v>708</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11730,16 +14038,16 @@
         <v>50</v>
       </c>
       <c r="C41" t="s">
-        <v>454</v>
+        <v>709</v>
       </c>
       <c r="D41" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E41" t="s">
         <v>61</v>
       </c>
       <c r="F41" t="s">
-        <v>455</v>
+        <v>710</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11750,16 +14058,16 @@
         <v>50</v>
       </c>
       <c r="C42" t="s">
-        <v>456</v>
+        <v>711</v>
       </c>
       <c r="D42" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E42" t="s">
         <v>63</v>
       </c>
       <c r="F42" t="s">
-        <v>457</v>
+        <v>712</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11770,16 +14078,16 @@
         <v>50</v>
       </c>
       <c r="C43" t="s">
-        <v>456</v>
+        <v>711</v>
       </c>
       <c r="D43" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E43" t="s">
         <v>60</v>
       </c>
       <c r="F43" t="s">
-        <v>458</v>
+        <v>713</v>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11790,16 +14098,16 @@
         <v>50</v>
       </c>
       <c r="C44" t="s">
-        <v>459</v>
+        <v>714</v>
       </c>
       <c r="D44" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E44" t="s">
         <v>60</v>
       </c>
       <c r="F44" t="s">
-        <v>460</v>
+        <v>715</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11810,16 +14118,16 @@
         <v>50</v>
       </c>
       <c r="C45" t="s">
-        <v>448</v>
+        <v>703</v>
       </c>
       <c r="D45" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E45" t="s">
         <v>61</v>
       </c>
       <c r="F45" t="s">
-        <v>461</v>
+        <v>716</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11830,16 +14138,16 @@
         <v>50</v>
       </c>
       <c r="C46" t="s">
-        <v>452</v>
+        <v>707</v>
       </c>
       <c r="D46" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E46" t="s">
         <v>60</v>
       </c>
       <c r="F46" t="s">
-        <v>462</v>
+        <v>717</v>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11850,16 +14158,16 @@
         <v>50</v>
       </c>
       <c r="C47" t="s">
-        <v>463</v>
+        <v>718</v>
       </c>
       <c r="D47" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E47" t="s">
         <v>60</v>
       </c>
       <c r="F47" t="s">
-        <v>464</v>
+        <v>719</v>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11870,16 +14178,16 @@
         <v>50</v>
       </c>
       <c r="C48" t="s">
-        <v>465</v>
+        <v>720</v>
       </c>
       <c r="D48" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E48" t="s">
         <v>64</v>
       </c>
       <c r="F48" t="s">
-        <v>466</v>
+        <v>721</v>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11890,16 +14198,16 @@
         <v>50</v>
       </c>
       <c r="C49" t="s">
-        <v>467</v>
+        <v>722</v>
       </c>
       <c r="D49" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E49" t="s">
         <v>61</v>
       </c>
       <c r="F49" t="s">
-        <v>468</v>
+        <v>723</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11910,16 +14218,16 @@
         <v>50</v>
       </c>
       <c r="C50" t="s">
-        <v>469</v>
+        <v>724</v>
       </c>
       <c r="D50" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E50" t="s">
         <v>64</v>
       </c>
       <c r="F50" t="s">
-        <v>470</v>
+        <v>725</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11930,16 +14238,16 @@
         <v>50</v>
       </c>
       <c r="C51" t="s">
-        <v>471</v>
+        <v>726</v>
       </c>
       <c r="D51" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E51" t="s">
         <v>65</v>
       </c>
       <c r="F51" t="s">
-        <v>472</v>
+        <v>727</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11950,16 +14258,16 @@
         <v>50</v>
       </c>
       <c r="C52" t="s">
-        <v>473</v>
+        <v>728</v>
       </c>
       <c r="D52" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E52" t="s">
         <v>61</v>
       </c>
       <c r="F52" t="s">
-        <v>474</v>
+        <v>729</v>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11970,16 +14278,16 @@
         <v>50</v>
       </c>
       <c r="C53" t="s">
-        <v>475</v>
+        <v>730</v>
       </c>
       <c r="D53" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E53" t="s">
         <v>61</v>
       </c>
       <c r="F53" t="s">
-        <v>476</v>
+        <v>731</v>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -11990,16 +14298,16 @@
         <v>50</v>
       </c>
       <c r="C54" t="s">
-        <v>477</v>
+        <v>732</v>
       </c>
       <c r="D54" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E54" t="s">
         <v>61</v>
       </c>
       <c r="F54" t="s">
-        <v>478</v>
+        <v>733</v>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12010,16 +14318,16 @@
         <v>50</v>
       </c>
       <c r="C55" t="s">
-        <v>479</v>
+        <v>734</v>
       </c>
       <c r="D55" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E55" t="s">
         <v>60</v>
       </c>
       <c r="F55" t="s">
-        <v>480</v>
+        <v>735</v>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12030,16 +14338,16 @@
         <v>50</v>
       </c>
       <c r="C56" t="s">
-        <v>481</v>
+        <v>736</v>
       </c>
       <c r="D56" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E56" t="s">
         <v>64</v>
       </c>
       <c r="F56" t="s">
-        <v>482</v>
+        <v>737</v>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12050,16 +14358,16 @@
         <v>50</v>
       </c>
       <c r="C57" t="s">
-        <v>456</v>
+        <v>711</v>
       </c>
       <c r="D57" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E57" t="s">
         <v>61</v>
       </c>
       <c r="F57" t="s">
-        <v>483</v>
+        <v>738</v>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12070,16 +14378,16 @@
         <v>50</v>
       </c>
       <c r="C58" t="s">
-        <v>448</v>
+        <v>703</v>
       </c>
       <c r="D58" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E58" t="s">
         <v>61</v>
       </c>
       <c r="F58" t="s">
-        <v>484</v>
+        <v>739</v>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12090,16 +14398,16 @@
         <v>50</v>
       </c>
       <c r="C59" t="s">
-        <v>485</v>
+        <v>740</v>
       </c>
       <c r="D59" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E59" t="s">
         <v>61</v>
       </c>
       <c r="F59" t="s">
-        <v>486</v>
+        <v>741</v>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12110,16 +14418,16 @@
         <v>50</v>
       </c>
       <c r="C60" t="s">
-        <v>487</v>
+        <v>742</v>
       </c>
       <c r="D60" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E60" t="s">
         <v>61</v>
       </c>
       <c r="F60" t="s">
-        <v>488</v>
+        <v>743</v>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12130,16 +14438,16 @@
         <v>50</v>
       </c>
       <c r="C61" t="s">
-        <v>489</v>
+        <v>744</v>
       </c>
       <c r="D61" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E61" t="s">
         <v>60</v>
       </c>
       <c r="F61" t="s">
-        <v>490</v>
+        <v>745</v>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12150,16 +14458,16 @@
         <v>50</v>
       </c>
       <c r="C62" t="s">
-        <v>491</v>
+        <v>746</v>
       </c>
       <c r="D62" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E62" t="s">
         <v>61</v>
       </c>
       <c r="F62" t="s">
-        <v>492</v>
+        <v>747</v>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12170,16 +14478,16 @@
         <v>50</v>
       </c>
       <c r="C63" t="s">
-        <v>493</v>
+        <v>748</v>
       </c>
       <c r="D63" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E63" t="s">
         <v>61</v>
       </c>
       <c r="F63" t="s">
-        <v>494</v>
+        <v>749</v>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12190,16 +14498,16 @@
         <v>50</v>
       </c>
       <c r="C64" t="s">
-        <v>495</v>
+        <v>750</v>
       </c>
       <c r="D64" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E64" t="s">
         <v>61</v>
       </c>
       <c r="F64" t="s">
-        <v>496</v>
+        <v>751</v>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12210,16 +14518,16 @@
         <v>50</v>
       </c>
       <c r="C65" t="s">
-        <v>497</v>
+        <v>752</v>
       </c>
       <c r="D65" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E65" t="s">
         <v>61</v>
       </c>
       <c r="F65" t="s">
-        <v>498</v>
+        <v>753</v>
       </c>
     </row>
     <row r="66" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12233,13 +14541,13 @@
         <v>279</v>
       </c>
       <c r="D66" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E66" t="s">
         <v>60</v>
       </c>
       <c r="F66" t="s">
-        <v>499</v>
+        <v>754</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12250,16 +14558,16 @@
         <v>50</v>
       </c>
       <c r="C67" t="s">
-        <v>500</v>
+        <v>755</v>
       </c>
       <c r="D67" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E67" t="s">
         <v>61</v>
       </c>
       <c r="F67" t="s">
-        <v>501</v>
+        <v>756</v>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12270,16 +14578,16 @@
         <v>50</v>
       </c>
       <c r="C68" t="s">
-        <v>502</v>
+        <v>757</v>
       </c>
       <c r="D68" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E68" t="s">
         <v>61</v>
       </c>
       <c r="F68" t="s">
-        <v>503</v>
+        <v>758</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12293,13 +14601,13 @@
         <v>279</v>
       </c>
       <c r="D69" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E69" t="s">
         <v>60</v>
       </c>
       <c r="F69" t="s">
-        <v>504</v>
+        <v>759</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12310,16 +14618,16 @@
         <v>50</v>
       </c>
       <c r="C70" t="s">
-        <v>505</v>
+        <v>760</v>
       </c>
       <c r="D70" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E70" t="s">
         <v>61</v>
       </c>
       <c r="F70" t="s">
-        <v>506</v>
+        <v>761</v>
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12330,16 +14638,16 @@
         <v>50</v>
       </c>
       <c r="C71" t="s">
-        <v>507</v>
+        <v>762</v>
       </c>
       <c r="D71" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E71" t="s">
         <v>61</v>
       </c>
       <c r="F71" t="s">
-        <v>508</v>
+        <v>763</v>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12350,16 +14658,16 @@
         <v>50</v>
       </c>
       <c r="C72" t="s">
-        <v>509</v>
+        <v>764</v>
       </c>
       <c r="D72" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E72" t="s">
         <v>61</v>
       </c>
       <c r="F72" t="s">
-        <v>510</v>
+        <v>765</v>
       </c>
     </row>
     <row r="73" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12370,16 +14678,16 @@
         <v>50</v>
       </c>
       <c r="C73" t="s">
-        <v>511</v>
+        <v>766</v>
       </c>
       <c r="D73" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E73" t="s">
         <v>60</v>
       </c>
       <c r="F73" t="s">
-        <v>512</v>
+        <v>767</v>
       </c>
     </row>
     <row r="74" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12390,16 +14698,16 @@
         <v>50</v>
       </c>
       <c r="C74" t="s">
-        <v>513</v>
+        <v>768</v>
       </c>
       <c r="D74" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E74" t="s">
         <v>61</v>
       </c>
       <c r="F74" t="s">
-        <v>514</v>
+        <v>769</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12410,16 +14718,16 @@
         <v>50</v>
       </c>
       <c r="C75" t="s">
-        <v>515</v>
+        <v>770</v>
       </c>
       <c r="D75" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E75" t="s">
         <v>61</v>
       </c>
       <c r="F75" t="s">
-        <v>516</v>
+        <v>771</v>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12430,16 +14738,16 @@
         <v>50</v>
       </c>
       <c r="C76" t="s">
-        <v>517</v>
+        <v>772</v>
       </c>
       <c r="D76" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E76" t="s">
         <v>61</v>
       </c>
       <c r="F76" t="s">
-        <v>518</v>
+        <v>773</v>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12450,16 +14758,16 @@
         <v>50</v>
       </c>
       <c r="C77" t="s">
-        <v>519</v>
+        <v>774</v>
       </c>
       <c r="D77" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E77" t="s">
         <v>61</v>
       </c>
       <c r="F77" t="s">
-        <v>520</v>
+        <v>775</v>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12470,16 +14778,16 @@
         <v>50</v>
       </c>
       <c r="C78" t="s">
-        <v>463</v>
+        <v>718</v>
       </c>
       <c r="D78" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E78" t="s">
         <v>61</v>
       </c>
       <c r="F78" t="s">
-        <v>521</v>
+        <v>776</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12490,16 +14798,16 @@
         <v>50</v>
       </c>
       <c r="C79" t="s">
-        <v>522</v>
+        <v>777</v>
       </c>
       <c r="D79" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E79" t="s">
         <v>61</v>
       </c>
       <c r="F79" t="s">
-        <v>523</v>
+        <v>778</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12510,16 +14818,16 @@
         <v>50</v>
       </c>
       <c r="C80" t="s">
-        <v>452</v>
+        <v>707</v>
       </c>
       <c r="D80" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E80" t="s">
         <v>60</v>
       </c>
       <c r="F80" t="s">
-        <v>524</v>
+        <v>779</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12530,16 +14838,16 @@
         <v>50</v>
       </c>
       <c r="C81" t="s">
-        <v>525</v>
+        <v>780</v>
       </c>
       <c r="D81" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E81" t="s">
         <v>60</v>
       </c>
       <c r="F81" t="s">
-        <v>526</v>
+        <v>781</v>
       </c>
     </row>
     <row r="82" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12550,16 +14858,16 @@
         <v>50</v>
       </c>
       <c r="C82" t="s">
-        <v>527</v>
+        <v>782</v>
       </c>
       <c r="D82" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E82" t="s">
         <v>60</v>
       </c>
       <c r="F82" t="s">
-        <v>528</v>
+        <v>783</v>
       </c>
     </row>
     <row r="83" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12570,16 +14878,16 @@
         <v>50</v>
       </c>
       <c r="C83" t="s">
-        <v>529</v>
+        <v>784</v>
       </c>
       <c r="D83" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E83" t="s">
         <v>60</v>
       </c>
       <c r="F83" t="s">
-        <v>530</v>
+        <v>785</v>
       </c>
     </row>
     <row r="84" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12590,16 +14898,16 @@
         <v>50</v>
       </c>
       <c r="C84" t="s">
-        <v>531</v>
+        <v>786</v>
       </c>
       <c r="D84" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E84" t="s">
         <v>60</v>
       </c>
       <c r="F84" t="s">
-        <v>532</v>
+        <v>787</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12610,16 +14918,16 @@
         <v>50</v>
       </c>
       <c r="C85" t="s">
-        <v>533</v>
+        <v>788</v>
       </c>
       <c r="D85" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E85" t="s">
         <v>60</v>
       </c>
       <c r="F85" t="s">
-        <v>534</v>
+        <v>789</v>
       </c>
     </row>
     <row r="86" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12630,16 +14938,16 @@
         <v>50</v>
       </c>
       <c r="C86" t="s">
-        <v>386</v>
+        <v>644</v>
       </c>
       <c r="D86" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E86" t="s">
         <v>61</v>
       </c>
       <c r="F86" t="s">
-        <v>535</v>
+        <v>790</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12650,16 +14958,16 @@
         <v>50</v>
       </c>
       <c r="C87" t="s">
-        <v>536</v>
+        <v>791</v>
       </c>
       <c r="D87" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E87" t="s">
         <v>61</v>
       </c>
       <c r="F87" t="s">
-        <v>537</v>
+        <v>792</v>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12670,16 +14978,16 @@
         <v>50</v>
       </c>
       <c r="C88" t="s">
-        <v>465</v>
+        <v>720</v>
       </c>
       <c r="D88" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E88" t="s">
         <v>61</v>
       </c>
       <c r="F88" t="s">
-        <v>538</v>
+        <v>793</v>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12690,16 +14998,16 @@
         <v>50</v>
       </c>
       <c r="C89" t="s">
-        <v>539</v>
+        <v>794</v>
       </c>
       <c r="D89" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E89" t="s">
         <v>63</v>
       </c>
       <c r="F89" t="s">
-        <v>540</v>
+        <v>795</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12710,16 +15018,16 @@
         <v>50</v>
       </c>
       <c r="C90" t="s">
-        <v>541</v>
+        <v>796</v>
       </c>
       <c r="D90" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E90" t="s">
         <v>60</v>
       </c>
       <c r="F90" t="s">
-        <v>542</v>
+        <v>797</v>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12730,16 +15038,16 @@
         <v>50</v>
       </c>
       <c r="C91" t="s">
-        <v>543</v>
+        <v>798</v>
       </c>
       <c r="D91" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E91" t="s">
         <v>60</v>
       </c>
       <c r="F91" t="s">
-        <v>544</v>
+        <v>799</v>
       </c>
     </row>
     <row r="92" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12750,16 +15058,16 @@
         <v>50</v>
       </c>
       <c r="C92" t="s">
-        <v>545</v>
+        <v>800</v>
       </c>
       <c r="D92" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E92" t="s">
         <v>61</v>
       </c>
       <c r="F92" t="s">
-        <v>546</v>
+        <v>801</v>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12770,16 +15078,16 @@
         <v>50</v>
       </c>
       <c r="C93" t="s">
-        <v>547</v>
+        <v>802</v>
       </c>
       <c r="D93" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E93" t="s">
         <v>61</v>
       </c>
       <c r="F93" t="s">
-        <v>548</v>
+        <v>803</v>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12790,16 +15098,16 @@
         <v>50</v>
       </c>
       <c r="C94" t="s">
-        <v>549</v>
+        <v>804</v>
       </c>
       <c r="D94" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E94" t="s">
         <v>60</v>
       </c>
       <c r="F94" t="s">
-        <v>550</v>
+        <v>805</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12810,16 +15118,16 @@
         <v>50</v>
       </c>
       <c r="C95" t="s">
-        <v>551</v>
+        <v>806</v>
       </c>
       <c r="D95" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E95" t="s">
         <v>60</v>
       </c>
       <c r="F95" t="s">
-        <v>552</v>
+        <v>807</v>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12830,16 +15138,16 @@
         <v>50</v>
       </c>
       <c r="C96" t="s">
-        <v>553</v>
+        <v>808</v>
       </c>
       <c r="D96" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E96" t="s">
         <v>64</v>
       </c>
       <c r="F96" t="s">
-        <v>554</v>
+        <v>809</v>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12850,16 +15158,16 @@
         <v>50</v>
       </c>
       <c r="C97" t="s">
-        <v>531</v>
+        <v>786</v>
       </c>
       <c r="D97" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E97" t="s">
         <v>61</v>
       </c>
       <c r="F97" t="s">
-        <v>555</v>
+        <v>810</v>
       </c>
     </row>
     <row r="98" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12870,16 +15178,16 @@
         <v>50</v>
       </c>
       <c r="C98" t="s">
-        <v>556</v>
+        <v>811</v>
       </c>
       <c r="D98" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E98" t="s">
         <v>60</v>
       </c>
       <c r="F98" t="s">
-        <v>557</v>
+        <v>812</v>
       </c>
     </row>
     <row r="99" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12890,16 +15198,16 @@
         <v>50</v>
       </c>
       <c r="C99" t="s">
-        <v>558</v>
+        <v>813</v>
       </c>
       <c r="D99" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E99" t="s">
         <v>65</v>
       </c>
       <c r="F99" t="s">
-        <v>559</v>
+        <v>814</v>
       </c>
     </row>
     <row r="100" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12910,16 +15218,16 @@
         <v>50</v>
       </c>
       <c r="C100" t="s">
-        <v>560</v>
+        <v>815</v>
       </c>
       <c r="D100" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E100" t="s">
         <v>64</v>
       </c>
       <c r="F100" t="s">
-        <v>561</v>
+        <v>816</v>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12930,16 +15238,16 @@
         <v>50</v>
       </c>
       <c r="C101" t="s">
-        <v>562</v>
+        <v>817</v>
       </c>
       <c r="D101" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E101" t="s">
         <v>61</v>
       </c>
       <c r="F101" t="s">
-        <v>563</v>
+        <v>818</v>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12950,16 +15258,16 @@
         <v>50</v>
       </c>
       <c r="C102" t="s">
-        <v>564</v>
+        <v>819</v>
       </c>
       <c r="D102" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E102" t="s">
         <v>61</v>
       </c>
       <c r="F102" t="s">
-        <v>565</v>
+        <v>820</v>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12970,16 +15278,16 @@
         <v>50</v>
       </c>
       <c r="C103" t="s">
-        <v>566</v>
+        <v>821</v>
       </c>
       <c r="D103" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E103" t="s">
         <v>62</v>
       </c>
       <c r="F103" t="s">
-        <v>567</v>
+        <v>822</v>
       </c>
     </row>
     <row r="104" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -12990,16 +15298,16 @@
         <v>50</v>
       </c>
       <c r="C104" t="s">
-        <v>568</v>
+        <v>823</v>
       </c>
       <c r="D104" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E104" t="s">
         <v>60</v>
       </c>
       <c r="F104" t="s">
-        <v>569</v>
+        <v>824</v>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13010,16 +15318,16 @@
         <v>50</v>
       </c>
       <c r="C105" t="s">
-        <v>570</v>
+        <v>825</v>
       </c>
       <c r="D105" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E105" t="s">
         <v>60</v>
       </c>
       <c r="F105" t="s">
-        <v>571</v>
+        <v>826</v>
       </c>
     </row>
     <row r="106" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13030,16 +15338,16 @@
         <v>50</v>
       </c>
       <c r="C106" t="s">
-        <v>572</v>
+        <v>827</v>
       </c>
       <c r="D106" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E106" t="s">
         <v>63</v>
       </c>
       <c r="F106" t="s">
-        <v>573</v>
+        <v>828</v>
       </c>
     </row>
     <row r="107" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13050,16 +15358,16 @@
         <v>50</v>
       </c>
       <c r="C107" t="s">
-        <v>574</v>
+        <v>829</v>
       </c>
       <c r="D107" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E107" t="s">
         <v>61</v>
       </c>
       <c r="F107" t="s">
-        <v>575</v>
+        <v>830</v>
       </c>
     </row>
     <row r="108" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13070,16 +15378,16 @@
         <v>50</v>
       </c>
       <c r="C108" t="s">
-        <v>576</v>
+        <v>831</v>
       </c>
       <c r="D108" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E108" t="s">
         <v>60</v>
       </c>
       <c r="F108" t="s">
-        <v>577</v>
+        <v>832</v>
       </c>
     </row>
     <row r="109" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13090,16 +15398,16 @@
         <v>50</v>
       </c>
       <c r="C109" t="s">
-        <v>578</v>
+        <v>833</v>
       </c>
       <c r="D109" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E109" t="s">
         <v>60</v>
       </c>
       <c r="F109" t="s">
-        <v>579</v>
+        <v>834</v>
       </c>
     </row>
     <row r="110" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13113,13 +15421,13 @@
         <v>373</v>
       </c>
       <c r="D110" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E110" t="s">
         <v>61</v>
       </c>
       <c r="F110" t="s">
-        <v>580</v>
+        <v>835</v>
       </c>
     </row>
     <row r="111" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13130,16 +15438,16 @@
         <v>50</v>
       </c>
       <c r="C111" t="s">
-        <v>581</v>
+        <v>836</v>
       </c>
       <c r="D111" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E111" t="s">
         <v>60</v>
       </c>
       <c r="F111" t="s">
-        <v>582</v>
+        <v>837</v>
       </c>
     </row>
     <row r="112" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13150,16 +15458,16 @@
         <v>50</v>
       </c>
       <c r="C112" t="s">
-        <v>583</v>
+        <v>838</v>
       </c>
       <c r="D112" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E112" t="s">
         <v>60</v>
       </c>
       <c r="F112" t="s">
-        <v>584</v>
+        <v>839</v>
       </c>
     </row>
     <row r="113" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13170,16 +15478,16 @@
         <v>51</v>
       </c>
       <c r="C113" t="s">
-        <v>585</v>
+        <v>840</v>
       </c>
       <c r="D113" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E113" t="s">
         <v>60</v>
       </c>
       <c r="F113" t="s">
-        <v>586</v>
+        <v>841</v>
       </c>
     </row>
     <row r="114" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13190,16 +15498,16 @@
         <v>51</v>
       </c>
       <c r="C114" t="s">
-        <v>585</v>
+        <v>840</v>
       </c>
       <c r="D114" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E114" t="s">
         <v>60</v>
       </c>
       <c r="F114" t="s">
-        <v>587</v>
+        <v>842</v>
       </c>
     </row>
     <row r="115" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13210,16 +15518,16 @@
         <v>51</v>
       </c>
       <c r="C115" t="s">
-        <v>588</v>
+        <v>843</v>
       </c>
       <c r="D115" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E115" t="s">
         <v>60</v>
       </c>
       <c r="F115" t="s">
-        <v>589</v>
+        <v>844</v>
       </c>
     </row>
     <row r="116" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13230,16 +15538,16 @@
         <v>51</v>
       </c>
       <c r="C116" t="s">
-        <v>590</v>
+        <v>845</v>
       </c>
       <c r="D116" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E116" t="s">
         <v>60</v>
       </c>
       <c r="F116" t="s">
-        <v>591</v>
+        <v>846</v>
       </c>
     </row>
     <row r="117" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13253,13 +15561,13 @@
         <v>159</v>
       </c>
       <c r="D117" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E117" t="s">
         <v>60</v>
       </c>
       <c r="F117" t="s">
-        <v>592</v>
+        <v>847</v>
       </c>
     </row>
     <row r="118" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13270,16 +15578,16 @@
         <v>51</v>
       </c>
       <c r="C118" t="s">
-        <v>593</v>
+        <v>848</v>
       </c>
       <c r="D118" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E118" t="s">
         <v>60</v>
       </c>
       <c r="F118" t="s">
-        <v>594</v>
+        <v>849</v>
       </c>
     </row>
     <row r="119" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13290,16 +15598,16 @@
         <v>51</v>
       </c>
       <c r="C119" t="s">
-        <v>595</v>
+        <v>850</v>
       </c>
       <c r="D119" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E119" t="s">
         <v>63</v>
       </c>
       <c r="F119" t="s">
-        <v>596</v>
+        <v>851</v>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13310,16 +15618,16 @@
         <v>51</v>
       </c>
       <c r="C120" t="s">
-        <v>597</v>
+        <v>852</v>
       </c>
       <c r="D120" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E120" t="s">
         <v>63</v>
       </c>
       <c r="F120" t="s">
-        <v>598</v>
+        <v>853</v>
       </c>
     </row>
     <row r="121" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13330,16 +15638,16 @@
         <v>51</v>
       </c>
       <c r="C121" t="s">
-        <v>597</v>
+        <v>852</v>
       </c>
       <c r="D121" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E121" t="s">
         <v>61</v>
       </c>
       <c r="F121" t="s">
-        <v>599</v>
+        <v>854</v>
       </c>
     </row>
     <row r="122" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13350,16 +15658,16 @@
         <v>51</v>
       </c>
       <c r="C122" t="s">
-        <v>600</v>
+        <v>855</v>
       </c>
       <c r="D122" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E122" t="s">
         <v>60</v>
       </c>
       <c r="F122" t="s">
-        <v>601</v>
+        <v>856</v>
       </c>
     </row>
     <row r="123" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13370,16 +15678,16 @@
         <v>51</v>
       </c>
       <c r="C123" t="s">
-        <v>602</v>
+        <v>857</v>
       </c>
       <c r="D123" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E123" t="s">
         <v>60</v>
       </c>
       <c r="F123" t="s">
-        <v>603</v>
+        <v>858</v>
       </c>
     </row>
     <row r="124" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13390,16 +15698,16 @@
         <v>51</v>
       </c>
       <c r="C124" t="s">
-        <v>604</v>
+        <v>859</v>
       </c>
       <c r="D124" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E124" t="s">
         <v>65</v>
       </c>
       <c r="F124" t="s">
-        <v>605</v>
+        <v>860</v>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13413,13 +15721,13 @@
         <v>232</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E125" t="s">
         <v>64</v>
       </c>
       <c r="F125" t="s">
-        <v>606</v>
+        <v>861</v>
       </c>
     </row>
     <row r="126" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13430,16 +15738,16 @@
         <v>51</v>
       </c>
       <c r="C126" t="s">
-        <v>607</v>
+        <v>862</v>
       </c>
       <c r="D126" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E126" t="s">
         <v>60</v>
       </c>
       <c r="F126" t="s">
-        <v>608</v>
+        <v>863</v>
       </c>
     </row>
     <row r="127" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13450,16 +15758,16 @@
         <v>51</v>
       </c>
       <c r="C127" t="s">
-        <v>609</v>
+        <v>864</v>
       </c>
       <c r="D127" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E127" t="s">
         <v>60</v>
       </c>
       <c r="F127" t="s">
-        <v>610</v>
+        <v>865</v>
       </c>
     </row>
     <row r="128" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13470,16 +15778,16 @@
         <v>51</v>
       </c>
       <c r="C128" t="s">
-        <v>609</v>
+        <v>864</v>
       </c>
       <c r="D128" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E128" t="s">
         <v>64</v>
       </c>
       <c r="F128" t="s">
-        <v>611</v>
+        <v>866</v>
       </c>
     </row>
     <row r="129" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13490,16 +15798,16 @@
         <v>51</v>
       </c>
       <c r="C129" t="s">
-        <v>612</v>
+        <v>398</v>
       </c>
       <c r="D129" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E129" t="s">
         <v>63</v>
       </c>
       <c r="F129" t="s">
-        <v>613</v>
+        <v>867</v>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13510,16 +15818,16 @@
         <v>51</v>
       </c>
       <c r="C130" t="s">
-        <v>614</v>
+        <v>868</v>
       </c>
       <c r="D130" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E130" t="s">
         <v>63</v>
       </c>
       <c r="F130" t="s">
-        <v>615</v>
+        <v>869</v>
       </c>
     </row>
     <row r="131" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13530,16 +15838,16 @@
         <v>51</v>
       </c>
       <c r="C131" t="s">
-        <v>616</v>
+        <v>870</v>
       </c>
       <c r="D131" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E131" t="s">
         <v>60</v>
       </c>
       <c r="F131" t="s">
-        <v>617</v>
+        <v>871</v>
       </c>
     </row>
     <row r="132" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13550,16 +15858,16 @@
         <v>51</v>
       </c>
       <c r="C132" t="s">
-        <v>618</v>
+        <v>872</v>
       </c>
       <c r="D132" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E132" t="s">
         <v>60</v>
       </c>
       <c r="F132" t="s">
-        <v>619</v>
+        <v>873</v>
       </c>
     </row>
     <row r="133" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13570,16 +15878,16 @@
         <v>51</v>
       </c>
       <c r="C133" t="s">
-        <v>620</v>
+        <v>874</v>
       </c>
       <c r="D133" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E133" t="s">
         <v>60</v>
       </c>
       <c r="F133" t="s">
-        <v>621</v>
+        <v>875</v>
       </c>
     </row>
     <row r="134" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13590,16 +15898,16 @@
         <v>51</v>
       </c>
       <c r="C134" t="s">
-        <v>622</v>
+        <v>876</v>
       </c>
       <c r="D134" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E134" t="s">
         <v>62</v>
       </c>
       <c r="F134" t="s">
-        <v>623</v>
+        <v>877</v>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13613,13 +15921,13 @@
         <v>159</v>
       </c>
       <c r="D135" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E135" t="s">
         <v>60</v>
       </c>
       <c r="F135" t="s">
-        <v>624</v>
+        <v>878</v>
       </c>
     </row>
     <row r="136" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13630,16 +15938,16 @@
         <v>51</v>
       </c>
       <c r="C136" t="s">
-        <v>625</v>
+        <v>879</v>
       </c>
       <c r="D136" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E136" t="s">
         <v>60</v>
       </c>
       <c r="F136" t="s">
-        <v>626</v>
+        <v>880</v>
       </c>
     </row>
     <row r="137" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13650,16 +15958,16 @@
         <v>51</v>
       </c>
       <c r="C137" t="s">
-        <v>625</v>
+        <v>879</v>
       </c>
       <c r="D137" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E137" t="s">
         <v>60</v>
       </c>
       <c r="F137" t="s">
-        <v>627</v>
+        <v>881</v>
       </c>
     </row>
     <row r="138" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13670,16 +15978,16 @@
         <v>51</v>
       </c>
       <c r="C138" t="s">
-        <v>628</v>
+        <v>882</v>
       </c>
       <c r="D138" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E138" t="s">
         <v>60</v>
       </c>
       <c r="F138" t="s">
-        <v>629</v>
+        <v>883</v>
       </c>
     </row>
     <row r="139" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13690,16 +15998,16 @@
         <v>51</v>
       </c>
       <c r="C139" t="s">
-        <v>630</v>
+        <v>884</v>
       </c>
       <c r="D139" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E139" t="s">
         <v>60</v>
       </c>
       <c r="F139" t="s">
-        <v>631</v>
+        <v>885</v>
       </c>
     </row>
     <row r="140" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13710,16 +16018,16 @@
         <v>51</v>
       </c>
       <c r="C140" t="s">
-        <v>630</v>
+        <v>884</v>
       </c>
       <c r="D140" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E140" t="s">
         <v>60</v>
       </c>
       <c r="F140" t="s">
-        <v>632</v>
+        <v>886</v>
       </c>
     </row>
     <row r="141" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13730,16 +16038,16 @@
         <v>51</v>
       </c>
       <c r="C141" t="s">
-        <v>630</v>
+        <v>884</v>
       </c>
       <c r="D141" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E141" t="s">
         <v>60</v>
       </c>
       <c r="F141" t="s">
-        <v>633</v>
+        <v>887</v>
       </c>
     </row>
     <row r="142" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13750,16 +16058,16 @@
         <v>51</v>
       </c>
       <c r="C142" t="s">
-        <v>634</v>
+        <v>391</v>
       </c>
       <c r="D142" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E142" t="s">
         <v>60</v>
       </c>
       <c r="F142" t="s">
-        <v>635</v>
+        <v>888</v>
       </c>
     </row>
     <row r="143" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13770,16 +16078,16 @@
         <v>51</v>
       </c>
       <c r="C143" t="s">
-        <v>636</v>
+        <v>889</v>
       </c>
       <c r="D143" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E143" t="s">
         <v>60</v>
       </c>
       <c r="F143" t="s">
-        <v>637</v>
+        <v>890</v>
       </c>
     </row>
     <row r="144" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13790,16 +16098,16 @@
         <v>51</v>
       </c>
       <c r="C144" t="s">
-        <v>638</v>
+        <v>891</v>
       </c>
       <c r="D144" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E144" t="s">
         <v>65</v>
       </c>
       <c r="F144" t="s">
-        <v>639</v>
+        <v>892</v>
       </c>
     </row>
     <row r="145" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13810,16 +16118,16 @@
         <v>51</v>
       </c>
       <c r="C145" t="s">
-        <v>588</v>
+        <v>843</v>
       </c>
       <c r="D145" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E145" t="s">
         <v>60</v>
       </c>
       <c r="F145" t="s">
-        <v>640</v>
+        <v>893</v>
       </c>
     </row>
     <row r="146" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13830,16 +16138,16 @@
         <v>51</v>
       </c>
       <c r="C146" t="s">
-        <v>588</v>
+        <v>843</v>
       </c>
       <c r="D146" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E146" t="s">
         <v>60</v>
       </c>
       <c r="F146" t="s">
-        <v>641</v>
+        <v>894</v>
       </c>
     </row>
     <row r="147" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13850,16 +16158,16 @@
         <v>49</v>
       </c>
       <c r="C147" t="s">
-        <v>642</v>
+        <v>895</v>
       </c>
       <c r="D147" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E147" t="s">
         <v>60</v>
       </c>
       <c r="F147" t="s">
-        <v>643</v>
+        <v>896</v>
       </c>
     </row>
     <row r="148" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13873,13 +16181,13 @@
         <v>182</v>
       </c>
       <c r="D148" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E148" t="s">
         <v>60</v>
       </c>
       <c r="F148" t="s">
-        <v>644</v>
+        <v>897</v>
       </c>
     </row>
     <row r="149" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13890,16 +16198,16 @@
         <v>49</v>
       </c>
       <c r="C149" t="s">
-        <v>645</v>
+        <v>898</v>
       </c>
       <c r="D149" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E149" t="s">
         <v>60</v>
       </c>
       <c r="F149" t="s">
-        <v>646</v>
+        <v>899</v>
       </c>
     </row>
     <row r="150" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13910,16 +16218,16 @@
         <v>49</v>
       </c>
       <c r="C150" t="s">
-        <v>647</v>
+        <v>900</v>
       </c>
       <c r="D150" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E150" t="s">
         <v>60</v>
       </c>
       <c r="F150" t="s">
-        <v>648</v>
+        <v>901</v>
       </c>
     </row>
     <row r="151" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13930,16 +16238,16 @@
         <v>49</v>
       </c>
       <c r="C151" t="s">
-        <v>649</v>
+        <v>902</v>
       </c>
       <c r="D151" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E151" t="s">
         <v>60</v>
       </c>
       <c r="F151" t="s">
-        <v>650</v>
+        <v>903</v>
       </c>
     </row>
     <row r="152" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13950,16 +16258,16 @@
         <v>49</v>
       </c>
       <c r="C152" t="s">
-        <v>651</v>
+        <v>904</v>
       </c>
       <c r="D152" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E152" t="s">
         <v>61</v>
       </c>
       <c r="F152" t="s">
-        <v>652</v>
+        <v>905</v>
       </c>
     </row>
     <row r="153" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13970,16 +16278,16 @@
         <v>49</v>
       </c>
       <c r="C153" t="s">
-        <v>653</v>
+        <v>906</v>
       </c>
       <c r="D153" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E153" t="s">
         <v>60</v>
       </c>
       <c r="F153" t="s">
-        <v>654</v>
+        <v>907</v>
       </c>
     </row>
     <row r="154" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -13990,16 +16298,16 @@
         <v>49</v>
       </c>
       <c r="C154" t="s">
-        <v>655</v>
+        <v>908</v>
       </c>
       <c r="D154" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E154" t="s">
         <v>60</v>
       </c>
       <c r="F154" t="s">
-        <v>656</v>
+        <v>909</v>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14010,16 +16318,16 @@
         <v>49</v>
       </c>
       <c r="C155" t="s">
-        <v>655</v>
+        <v>908</v>
       </c>
       <c r="D155" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E155" t="s">
         <v>60</v>
       </c>
       <c r="F155" t="s">
-        <v>657</v>
+        <v>910</v>
       </c>
     </row>
     <row r="156" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14030,16 +16338,16 @@
         <v>49</v>
       </c>
       <c r="C156" t="s">
-        <v>658</v>
+        <v>911</v>
       </c>
       <c r="D156" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E156" t="s">
         <v>63</v>
       </c>
       <c r="F156" t="s">
-        <v>659</v>
+        <v>912</v>
       </c>
     </row>
     <row r="157" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14050,16 +16358,16 @@
         <v>49</v>
       </c>
       <c r="C157" t="s">
-        <v>660</v>
+        <v>913</v>
       </c>
       <c r="D157" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E157" t="s">
         <v>60</v>
       </c>
       <c r="F157" t="s">
-        <v>661</v>
+        <v>914</v>
       </c>
     </row>
     <row r="158" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14073,13 +16381,13 @@
         <v>247</v>
       </c>
       <c r="D158" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E158" t="s">
         <v>60</v>
       </c>
       <c r="F158" t="s">
-        <v>662</v>
+        <v>915</v>
       </c>
     </row>
     <row r="159" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14090,16 +16398,16 @@
         <v>49</v>
       </c>
       <c r="C159" t="s">
-        <v>663</v>
+        <v>550</v>
       </c>
       <c r="D159" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E159" t="s">
         <v>61</v>
       </c>
       <c r="F159" t="s">
-        <v>664</v>
+        <v>916</v>
       </c>
     </row>
     <row r="160" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14110,16 +16418,16 @@
         <v>49</v>
       </c>
       <c r="C160" t="s">
-        <v>665</v>
+        <v>917</v>
       </c>
       <c r="D160" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E160" t="s">
         <v>61</v>
       </c>
       <c r="F160" t="s">
-        <v>666</v>
+        <v>918</v>
       </c>
     </row>
     <row r="161" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14130,16 +16438,16 @@
         <v>49</v>
       </c>
       <c r="C161" t="s">
-        <v>667</v>
+        <v>919</v>
       </c>
       <c r="D161" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E161" t="s">
         <v>64</v>
       </c>
       <c r="F161" t="s">
-        <v>668</v>
+        <v>920</v>
       </c>
     </row>
     <row r="162" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14150,16 +16458,16 @@
         <v>49</v>
       </c>
       <c r="C162" t="s">
-        <v>669</v>
+        <v>921</v>
       </c>
       <c r="D162" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E162" t="s">
         <v>60</v>
       </c>
       <c r="F162" t="s">
-        <v>670</v>
+        <v>922</v>
       </c>
     </row>
     <row r="163" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14170,16 +16478,16 @@
         <v>49</v>
       </c>
       <c r="C163" t="s">
-        <v>671</v>
+        <v>580</v>
       </c>
       <c r="D163" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E163" t="s">
         <v>60</v>
       </c>
       <c r="F163" t="s">
-        <v>672</v>
+        <v>923</v>
       </c>
     </row>
     <row r="164" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14190,16 +16498,16 @@
         <v>49</v>
       </c>
       <c r="C164" t="s">
-        <v>667</v>
+        <v>919</v>
       </c>
       <c r="D164" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E164" t="s">
         <v>60</v>
       </c>
       <c r="F164" t="s">
-        <v>673</v>
+        <v>924</v>
       </c>
     </row>
     <row r="165" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14210,16 +16518,16 @@
         <v>49</v>
       </c>
       <c r="C165" t="s">
-        <v>674</v>
+        <v>925</v>
       </c>
       <c r="D165" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E165" t="s">
         <v>60</v>
       </c>
       <c r="F165" t="s">
-        <v>675</v>
+        <v>926</v>
       </c>
     </row>
     <row r="166" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14233,13 +16541,13 @@
         <v>226</v>
       </c>
       <c r="D166" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E166" t="s">
         <v>60</v>
       </c>
       <c r="F166" t="s">
-        <v>676</v>
+        <v>927</v>
       </c>
     </row>
     <row r="167" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14250,16 +16558,16 @@
         <v>49</v>
       </c>
       <c r="C167" t="s">
-        <v>607</v>
+        <v>862</v>
       </c>
       <c r="D167" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E167" t="s">
         <v>60</v>
       </c>
       <c r="F167" t="s">
-        <v>677</v>
+        <v>928</v>
       </c>
     </row>
     <row r="168" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14270,16 +16578,16 @@
         <v>49</v>
       </c>
       <c r="C168" t="s">
-        <v>607</v>
+        <v>862</v>
       </c>
       <c r="D168" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E168" t="s">
         <v>61</v>
       </c>
       <c r="F168" t="s">
-        <v>678</v>
+        <v>929</v>
       </c>
     </row>
     <row r="169" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14293,13 +16601,13 @@
         <v>247</v>
       </c>
       <c r="D169" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E169" t="s">
         <v>60</v>
       </c>
       <c r="F169" t="s">
-        <v>679</v>
+        <v>930</v>
       </c>
     </row>
     <row r="170" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14310,16 +16618,16 @@
         <v>49</v>
       </c>
       <c r="C170" t="s">
-        <v>680</v>
+        <v>931</v>
       </c>
       <c r="D170" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E170" t="s">
         <v>60</v>
       </c>
       <c r="F170" t="s">
-        <v>681</v>
+        <v>932</v>
       </c>
     </row>
     <row r="171" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14330,16 +16638,16 @@
         <v>49</v>
       </c>
       <c r="C171" t="s">
-        <v>682</v>
+        <v>933</v>
       </c>
       <c r="D171" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E171" t="s">
         <v>60</v>
       </c>
       <c r="F171" t="s">
-        <v>683</v>
+        <v>934</v>
       </c>
     </row>
     <row r="172" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14353,13 +16661,13 @@
         <v>226</v>
       </c>
       <c r="D172" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E172" t="s">
         <v>61</v>
       </c>
       <c r="F172" t="s">
-        <v>684</v>
+        <v>935</v>
       </c>
     </row>
     <row r="173" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14370,16 +16678,16 @@
         <v>49</v>
       </c>
       <c r="C173" t="s">
-        <v>663</v>
+        <v>550</v>
       </c>
       <c r="D173" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E173" t="s">
         <v>60</v>
       </c>
       <c r="F173" t="s">
-        <v>685</v>
+        <v>936</v>
       </c>
     </row>
     <row r="174" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14393,13 +16701,13 @@
         <v>329</v>
       </c>
       <c r="D174" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E174" t="s">
         <v>60</v>
       </c>
       <c r="F174" t="s">
-        <v>686</v>
+        <v>937</v>
       </c>
     </row>
     <row r="175" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14410,16 +16718,16 @@
         <v>49</v>
       </c>
       <c r="C175" t="s">
-        <v>687</v>
+        <v>938</v>
       </c>
       <c r="D175" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E175" t="s">
         <v>60</v>
       </c>
       <c r="F175" t="s">
-        <v>688</v>
+        <v>939</v>
       </c>
     </row>
     <row r="176" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14430,16 +16738,16 @@
         <v>49</v>
       </c>
       <c r="C176" t="s">
-        <v>689</v>
+        <v>940</v>
       </c>
       <c r="D176" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E176" t="s">
         <v>60</v>
       </c>
       <c r="F176" t="s">
-        <v>690</v>
+        <v>941</v>
       </c>
     </row>
     <row r="177" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14450,16 +16758,16 @@
         <v>49</v>
       </c>
       <c r="C177" t="s">
-        <v>691</v>
+        <v>942</v>
       </c>
       <c r="D177" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E177" t="s">
         <v>61</v>
       </c>
       <c r="F177" t="s">
-        <v>692</v>
+        <v>943</v>
       </c>
     </row>
     <row r="178" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14470,16 +16778,16 @@
         <v>49</v>
       </c>
       <c r="C178" t="s">
-        <v>693</v>
+        <v>944</v>
       </c>
       <c r="D178" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E178" t="s">
         <v>60</v>
       </c>
       <c r="F178" t="s">
-        <v>694</v>
+        <v>945</v>
       </c>
     </row>
     <row r="179" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14490,16 +16798,16 @@
         <v>49</v>
       </c>
       <c r="C179" t="s">
-        <v>695</v>
+        <v>946</v>
       </c>
       <c r="D179" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E179" t="s">
         <v>61</v>
       </c>
       <c r="F179" t="s">
-        <v>696</v>
+        <v>947</v>
       </c>
     </row>
     <row r="180" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14510,16 +16818,16 @@
         <v>49</v>
       </c>
       <c r="C180" t="s">
-        <v>697</v>
+        <v>948</v>
       </c>
       <c r="D180" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E180" t="s">
         <v>61</v>
       </c>
       <c r="F180" t="s">
-        <v>698</v>
+        <v>949</v>
       </c>
     </row>
     <row r="181" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14533,13 +16841,13 @@
         <v>209</v>
       </c>
       <c r="D181" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E181" t="s">
         <v>60</v>
       </c>
       <c r="F181" t="s">
-        <v>699</v>
+        <v>950</v>
       </c>
     </row>
     <row r="182" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14550,16 +16858,16 @@
         <v>49</v>
       </c>
       <c r="C182" t="s">
-        <v>700</v>
+        <v>951</v>
       </c>
       <c r="D182" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E182" t="s">
         <v>60</v>
       </c>
       <c r="F182" t="s">
-        <v>701</v>
+        <v>952</v>
       </c>
     </row>
     <row r="183" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14570,16 +16878,16 @@
         <v>49</v>
       </c>
       <c r="C183" t="s">
-        <v>702</v>
+        <v>953</v>
       </c>
       <c r="D183" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E183" t="s">
         <v>60</v>
       </c>
       <c r="F183" t="s">
-        <v>703</v>
+        <v>954</v>
       </c>
     </row>
     <row r="184" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14590,16 +16898,16 @@
         <v>49</v>
       </c>
       <c r="C184" t="s">
-        <v>704</v>
+        <v>955</v>
       </c>
       <c r="D184" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E184" t="s">
         <v>60</v>
       </c>
       <c r="F184" t="s">
-        <v>705</v>
+        <v>956</v>
       </c>
     </row>
     <row r="185" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14610,16 +16918,16 @@
         <v>49</v>
       </c>
       <c r="C185" t="s">
-        <v>704</v>
+        <v>955</v>
       </c>
       <c r="D185" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E185" t="s">
         <v>60</v>
       </c>
       <c r="F185" t="s">
-        <v>706</v>
+        <v>957</v>
       </c>
     </row>
     <row r="186" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14633,13 +16941,13 @@
         <v>209</v>
       </c>
       <c r="D186" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E186" t="s">
         <v>60</v>
       </c>
       <c r="F186" t="s">
-        <v>707</v>
+        <v>958</v>
       </c>
     </row>
     <row r="187" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14650,16 +16958,16 @@
         <v>49</v>
       </c>
       <c r="C187" t="s">
-        <v>708</v>
+        <v>959</v>
       </c>
       <c r="D187" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E187" t="s">
         <v>60</v>
       </c>
       <c r="F187" t="s">
-        <v>709</v>
+        <v>960</v>
       </c>
     </row>
     <row r="188" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14670,16 +16978,16 @@
         <v>49</v>
       </c>
       <c r="C188" t="s">
-        <v>710</v>
+        <v>961</v>
       </c>
       <c r="D188" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E188" t="s">
         <v>60</v>
       </c>
       <c r="F188" t="s">
-        <v>711</v>
+        <v>962</v>
       </c>
     </row>
     <row r="189" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14690,16 +16998,16 @@
         <v>49</v>
       </c>
       <c r="C189" t="s">
-        <v>700</v>
+        <v>951</v>
       </c>
       <c r="D189" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E189" t="s">
         <v>60</v>
       </c>
       <c r="F189" t="s">
-        <v>712</v>
+        <v>963</v>
       </c>
     </row>
     <row r="190" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14710,16 +17018,16 @@
         <v>49</v>
       </c>
       <c r="C190" t="s">
-        <v>713</v>
+        <v>964</v>
       </c>
       <c r="D190" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E190" t="s">
         <v>60</v>
       </c>
       <c r="F190" t="s">
-        <v>714</v>
+        <v>965</v>
       </c>
     </row>
     <row r="191" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14730,16 +17038,16 @@
         <v>49</v>
       </c>
       <c r="C191" t="s">
-        <v>715</v>
+        <v>966</v>
       </c>
       <c r="D191" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E191" t="s">
         <v>60</v>
       </c>
       <c r="F191" t="s">
-        <v>716</v>
+        <v>967</v>
       </c>
     </row>
     <row r="192" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14750,16 +17058,16 @@
         <v>49</v>
       </c>
       <c r="C192" t="s">
-        <v>715</v>
+        <v>966</v>
       </c>
       <c r="D192" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E192" t="s">
         <v>60</v>
       </c>
       <c r="F192" t="s">
-        <v>717</v>
+        <v>968</v>
       </c>
     </row>
     <row r="193" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14770,16 +17078,16 @@
         <v>49</v>
       </c>
       <c r="C193" t="s">
-        <v>718</v>
+        <v>969</v>
       </c>
       <c r="D193" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E193" t="s">
         <v>60</v>
       </c>
       <c r="F193" t="s">
-        <v>719</v>
+        <v>970</v>
       </c>
     </row>
     <row r="194" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14790,16 +17098,16 @@
         <v>49</v>
       </c>
       <c r="C194" t="s">
-        <v>720</v>
+        <v>971</v>
       </c>
       <c r="D194" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E194" t="s">
         <v>60</v>
       </c>
       <c r="F194" t="s">
-        <v>721</v>
+        <v>972</v>
       </c>
     </row>
     <row r="195" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14810,16 +17118,16 @@
         <v>49</v>
       </c>
       <c r="C195" t="s">
-        <v>722</v>
+        <v>973</v>
       </c>
       <c r="D195" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E195" t="s">
         <v>60</v>
       </c>
       <c r="F195" t="s">
-        <v>723</v>
+        <v>974</v>
       </c>
     </row>
     <row r="196" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14830,16 +17138,16 @@
         <v>49</v>
       </c>
       <c r="C196" t="s">
-        <v>655</v>
+        <v>908</v>
       </c>
       <c r="D196" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E196" t="s">
         <v>60</v>
       </c>
       <c r="F196" t="s">
-        <v>724</v>
+        <v>975</v>
       </c>
     </row>
     <row r="197" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14850,16 +17158,16 @@
         <v>49</v>
       </c>
       <c r="C197" t="s">
-        <v>725</v>
+        <v>976</v>
       </c>
       <c r="D197" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E197" t="s">
         <v>60</v>
       </c>
       <c r="F197" t="s">
-        <v>726</v>
+        <v>977</v>
       </c>
     </row>
     <row r="198" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14870,16 +17178,16 @@
         <v>49</v>
       </c>
       <c r="C198" t="s">
-        <v>727</v>
+        <v>978</v>
       </c>
       <c r="D198" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E198" t="s">
         <v>60</v>
       </c>
       <c r="F198" t="s">
-        <v>728</v>
+        <v>979</v>
       </c>
     </row>
     <row r="199" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14890,16 +17198,16 @@
         <v>49</v>
       </c>
       <c r="C199" t="s">
-        <v>729</v>
+        <v>980</v>
       </c>
       <c r="D199" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E199" t="s">
         <v>60</v>
       </c>
       <c r="F199" t="s">
-        <v>730</v>
+        <v>981</v>
       </c>
     </row>
     <row r="200" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14910,16 +17218,16 @@
         <v>49</v>
       </c>
       <c r="C200" t="s">
-        <v>731</v>
+        <v>982</v>
       </c>
       <c r="D200" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E200" t="s">
         <v>64</v>
       </c>
       <c r="F200" t="s">
-        <v>732</v>
+        <v>983</v>
       </c>
     </row>
     <row r="201" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14930,16 +17238,16 @@
         <v>49</v>
       </c>
       <c r="C201" t="s">
-        <v>720</v>
+        <v>971</v>
       </c>
       <c r="D201" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E201" t="s">
         <v>60</v>
       </c>
       <c r="F201" t="s">
-        <v>733</v>
+        <v>984</v>
       </c>
     </row>
     <row r="202" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14950,16 +17258,16 @@
         <v>49</v>
       </c>
       <c r="C202" t="s">
-        <v>734</v>
+        <v>985</v>
       </c>
       <c r="D202" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E202" t="s">
         <v>60</v>
       </c>
       <c r="F202" t="s">
-        <v>735</v>
+        <v>986</v>
       </c>
     </row>
     <row r="203" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14970,16 +17278,16 @@
         <v>49</v>
       </c>
       <c r="C203" t="s">
-        <v>736</v>
+        <v>987</v>
       </c>
       <c r="D203" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E203" t="s">
         <v>60</v>
       </c>
       <c r="F203" t="s">
-        <v>737</v>
+        <v>988</v>
       </c>
     </row>
     <row r="204" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -14993,13 +17301,13 @@
         <v>182</v>
       </c>
       <c r="D204" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E204" t="s">
         <v>60</v>
       </c>
       <c r="F204" t="s">
-        <v>738</v>
+        <v>989</v>
       </c>
     </row>
     <row r="205" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15010,16 +17318,16 @@
         <v>49</v>
       </c>
       <c r="C205" t="s">
-        <v>739</v>
+        <v>990</v>
       </c>
       <c r="D205" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E205" t="s">
         <v>61</v>
       </c>
       <c r="F205" t="s">
-        <v>740</v>
+        <v>991</v>
       </c>
     </row>
     <row r="206" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15030,16 +17338,16 @@
         <v>49</v>
       </c>
       <c r="C206" t="s">
-        <v>655</v>
+        <v>908</v>
       </c>
       <c r="D206" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E206" t="s">
         <v>61</v>
       </c>
       <c r="F206" t="s">
-        <v>741</v>
+        <v>992</v>
       </c>
     </row>
     <row r="207" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15053,13 +17361,13 @@
         <v>178</v>
       </c>
       <c r="D207" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E207" t="s">
         <v>60</v>
       </c>
       <c r="F207" t="s">
-        <v>742</v>
+        <v>993</v>
       </c>
     </row>
     <row r="208" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15070,16 +17378,16 @@
         <v>49</v>
       </c>
       <c r="C208" t="s">
-        <v>743</v>
+        <v>994</v>
       </c>
       <c r="D208" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E208" t="s">
         <v>60</v>
       </c>
       <c r="F208" t="s">
-        <v>744</v>
+        <v>995</v>
       </c>
     </row>
     <row r="209" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15093,13 +17401,13 @@
         <v>172</v>
       </c>
       <c r="D209" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E209" t="s">
         <v>60</v>
       </c>
       <c r="F209" t="s">
-        <v>745</v>
+        <v>996</v>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15110,16 +17418,16 @@
         <v>49</v>
       </c>
       <c r="C210" t="s">
-        <v>746</v>
+        <v>997</v>
       </c>
       <c r="D210" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E210" t="s">
         <v>64</v>
       </c>
       <c r="F210" t="s">
-        <v>747</v>
+        <v>998</v>
       </c>
     </row>
     <row r="211" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15130,16 +17438,16 @@
         <v>49</v>
       </c>
       <c r="C211" t="s">
-        <v>748</v>
+        <v>999</v>
       </c>
       <c r="D211" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E211" t="s">
         <v>64</v>
       </c>
       <c r="F211" t="s">
-        <v>749</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="212" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15150,16 +17458,16 @@
         <v>49</v>
       </c>
       <c r="C212" t="s">
-        <v>750</v>
+        <v>1001</v>
       </c>
       <c r="D212" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E212" t="s">
         <v>60</v>
       </c>
       <c r="F212" t="s">
-        <v>751</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="213" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15170,16 +17478,16 @@
         <v>49</v>
       </c>
       <c r="C213" t="s">
-        <v>752</v>
+        <v>1003</v>
       </c>
       <c r="D213" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E213" t="s">
         <v>60</v>
       </c>
       <c r="F213" t="s">
-        <v>753</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="214" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15190,16 +17498,16 @@
         <v>49</v>
       </c>
       <c r="C214" t="s">
-        <v>754</v>
+        <v>1005</v>
       </c>
       <c r="D214" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E214" t="s">
         <v>64</v>
       </c>
       <c r="F214" t="s">
-        <v>755</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="215" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15213,13 +17521,13 @@
         <v>182</v>
       </c>
       <c r="D215" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E215" t="s">
         <v>60</v>
       </c>
       <c r="F215" t="s">
-        <v>756</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="216" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15230,16 +17538,16 @@
         <v>49</v>
       </c>
       <c r="C216" t="s">
-        <v>757</v>
+        <v>1008</v>
       </c>
       <c r="D216" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E216" t="s">
         <v>60</v>
       </c>
       <c r="F216" t="s">
-        <v>758</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="217" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15250,16 +17558,16 @@
         <v>49</v>
       </c>
       <c r="C217" t="s">
-        <v>759</v>
+        <v>1010</v>
       </c>
       <c r="D217" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E217" t="s">
         <v>60</v>
       </c>
       <c r="F217" t="s">
-        <v>760</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="218" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15270,16 +17578,16 @@
         <v>49</v>
       </c>
       <c r="C218" t="s">
-        <v>759</v>
+        <v>1010</v>
       </c>
       <c r="D218" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E218" t="s">
         <v>61</v>
       </c>
       <c r="F218" t="s">
-        <v>761</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="219" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15293,13 +17601,13 @@
         <v>164</v>
       </c>
       <c r="D219" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E219" t="s">
         <v>60</v>
       </c>
       <c r="F219" t="s">
-        <v>762</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="220" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15310,16 +17618,16 @@
         <v>49</v>
       </c>
       <c r="C220" t="s">
-        <v>763</v>
+        <v>1014</v>
       </c>
       <c r="D220" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E220" t="s">
         <v>60</v>
       </c>
       <c r="F220" t="s">
-        <v>764</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="221" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15330,16 +17638,16 @@
         <v>49</v>
       </c>
       <c r="C221" t="s">
-        <v>765</v>
+        <v>1016</v>
       </c>
       <c r="D221" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E221" t="s">
         <v>60</v>
       </c>
       <c r="F221" t="s">
-        <v>766</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="222" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15350,16 +17658,16 @@
         <v>49</v>
       </c>
       <c r="C222" t="s">
-        <v>767</v>
+        <v>1018</v>
       </c>
       <c r="D222" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E222" t="s">
         <v>64</v>
       </c>
       <c r="F222" t="s">
-        <v>768</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="223" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15370,16 +17678,16 @@
         <v>49</v>
       </c>
       <c r="C223" t="s">
-        <v>769</v>
+        <v>1020</v>
       </c>
       <c r="D223" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E223" t="s">
         <v>64</v>
       </c>
       <c r="F223" t="s">
-        <v>770</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="224" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15390,16 +17698,16 @@
         <v>49</v>
       </c>
       <c r="C224" t="s">
-        <v>771</v>
+        <v>1022</v>
       </c>
       <c r="D224" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E224" t="s">
         <v>60</v>
       </c>
       <c r="F224" t="s">
-        <v>772</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="225" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15410,16 +17718,16 @@
         <v>49</v>
       </c>
       <c r="C225" t="s">
-        <v>773</v>
+        <v>1024</v>
       </c>
       <c r="D225" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E225" t="s">
         <v>60</v>
       </c>
       <c r="F225" t="s">
-        <v>774</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="226" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15430,16 +17738,16 @@
         <v>49</v>
       </c>
       <c r="C226" t="s">
-        <v>775</v>
+        <v>1026</v>
       </c>
       <c r="D226" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E226" t="s">
         <v>60</v>
       </c>
       <c r="F226" t="s">
-        <v>776</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="227" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15450,16 +17758,16 @@
         <v>49</v>
       </c>
       <c r="C227" t="s">
-        <v>777</v>
+        <v>1028</v>
       </c>
       <c r="D227" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E227" t="s">
         <v>63</v>
       </c>
       <c r="F227" t="s">
-        <v>778</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="228" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15470,16 +17778,16 @@
         <v>49</v>
       </c>
       <c r="C228" t="s">
-        <v>779</v>
+        <v>1030</v>
       </c>
       <c r="D228" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E228" t="s">
         <v>61</v>
       </c>
       <c r="F228" t="s">
-        <v>780</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="229" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15490,16 +17798,16 @@
         <v>49</v>
       </c>
       <c r="C229" t="s">
-        <v>781</v>
+        <v>1032</v>
       </c>
       <c r="D229" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E229" t="s">
         <v>60</v>
       </c>
       <c r="F229" t="s">
-        <v>782</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="230" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15510,16 +17818,16 @@
         <v>49</v>
       </c>
       <c r="C230" t="s">
-        <v>783</v>
+        <v>1034</v>
       </c>
       <c r="D230" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E230" t="s">
         <v>64</v>
       </c>
       <c r="F230" t="s">
-        <v>784</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="231" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15530,16 +17838,16 @@
         <v>49</v>
       </c>
       <c r="C231" t="s">
-        <v>785</v>
+        <v>1036</v>
       </c>
       <c r="D231" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E231" t="s">
         <v>60</v>
       </c>
       <c r="F231" t="s">
-        <v>786</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="232" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15553,13 +17861,13 @@
         <v>144</v>
       </c>
       <c r="D232" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E232" t="s">
         <v>60</v>
       </c>
       <c r="F232" t="s">
-        <v>787</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="233" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15570,16 +17878,16 @@
         <v>49</v>
       </c>
       <c r="C233" t="s">
-        <v>691</v>
+        <v>942</v>
       </c>
       <c r="D233" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E233" t="s">
         <v>60</v>
       </c>
       <c r="F233" t="s">
-        <v>788</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="234" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15590,16 +17898,16 @@
         <v>49</v>
       </c>
       <c r="C234" t="s">
-        <v>789</v>
+        <v>1040</v>
       </c>
       <c r="D234" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E234" t="s">
         <v>60</v>
       </c>
       <c r="F234" t="s">
-        <v>790</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="235" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15610,16 +17918,16 @@
         <v>49</v>
       </c>
       <c r="C235" t="s">
-        <v>791</v>
+        <v>1042</v>
       </c>
       <c r="D235" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E235" t="s">
         <v>60</v>
       </c>
       <c r="F235" t="s">
-        <v>792</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="236" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15630,16 +17938,16 @@
         <v>49</v>
       </c>
       <c r="C236" t="s">
-        <v>793</v>
+        <v>1044</v>
       </c>
       <c r="D236" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E236" t="s">
         <v>60</v>
       </c>
       <c r="F236" t="s">
-        <v>794</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="237" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15650,16 +17958,16 @@
         <v>49</v>
       </c>
       <c r="C237" t="s">
-        <v>795</v>
+        <v>1046</v>
       </c>
       <c r="D237" s="37" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E237" t="s">
         <v>60</v>
       </c>
       <c r="F237" t="s">
-        <v>796</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="238" ht="15" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -15673,13 +17981,13 @@
         <v>135</v>
       </c>
       <c r="D238" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="E238" t="s">
         <v>60</v>
       </c>
       <c r="F238" t="s">
-        <v>797</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="239" ht="15" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -16232,7 +18540,7 @@
     </row>
     <row r="2" ht="19.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>798</v>
+        <v>1049</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -16243,19 +18551,19 @@
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>799</v>
+        <v>1050</v>
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="9" t="s">
-        <v>800</v>
+        <v>1051</v>
       </c>
       <c r="D4" s="9"/>
       <c r="E4" s="9" t="s">
-        <v>801</v>
+        <v>1052</v>
       </c>
       <c r="F4" s="9"/>
       <c r="G4" s="9" t="s">
-        <v>802</v>
+        <v>1053</v>
       </c>
       <c r="H4" s="9"/>
     </row>
@@ -16283,7 +18591,7 @@
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>803</v>
+        <v>1054</v>
       </c>
       <c r="B7" s="9"/>
     </row>
@@ -16296,7 +18604,7 @@
     </row>
     <row r="11" ht="21.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>804</v>
+        <v>1055</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>125</v>
@@ -16308,16 +18616,16 @@
         <v>133</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>805</v>
+        <v>1056</v>
       </c>
       <c r="F11" s="13" t="s">
         <v>89</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>806</v>
+        <v>1057</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>385</v>
+        <v>643</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -16325,19 +18633,19 @@
         <v>46210</v>
       </c>
       <c r="B12" t="s">
-        <v>807</v>
+        <v>1058</v>
       </c>
       <c r="C12" t="s">
         <v>51</v>
       </c>
       <c r="D12" t="s">
-        <v>808</v>
+        <v>1059</v>
       </c>
       <c r="E12" s="39">
         <v>10000</v>
       </c>
       <c r="F12" t="s">
-        <v>809</v>
+        <v>1060</v>
       </c>
       <c r="G12" s="36"/>
     </row>
@@ -16346,19 +18654,19 @@
         <v>46210</v>
       </c>
       <c r="B13" t="s">
-        <v>810</v>
+        <v>1061</v>
       </c>
       <c r="C13" t="s">
         <v>51</v>
       </c>
       <c r="D13" t="s">
-        <v>811</v>
+        <v>1062</v>
       </c>
       <c r="E13" s="39">
         <v>1500</v>
       </c>
       <c r="F13" t="s">
-        <v>812</v>
+        <v>1063</v>
       </c>
       <c r="G13" s="36">
         <v>46210</v>
@@ -16375,13 +18683,13 @@
         <v>51</v>
       </c>
       <c r="D14" t="s">
-        <v>813</v>
+        <v>1064</v>
       </c>
       <c r="E14" s="39">
         <v>3500</v>
       </c>
       <c r="F14" t="s">
-        <v>814</v>
+        <v>1065</v>
       </c>
       <c r="G14" s="36"/>
     </row>
@@ -16390,19 +18698,19 @@
         <v>46204</v>
       </c>
       <c r="B15" t="s">
-        <v>815</v>
+        <v>1066</v>
       </c>
       <c r="C15" t="s">
         <v>51</v>
       </c>
       <c r="D15" t="s">
-        <v>816</v>
+        <v>1067</v>
       </c>
       <c r="E15" s="39">
         <v>590</v>
       </c>
       <c r="F15" t="s">
-        <v>812</v>
+        <v>1063</v>
       </c>
       <c r="G15" s="36">
         <v>46210</v>
@@ -16419,13 +18727,13 @@
         <v>51</v>
       </c>
       <c r="D16" t="s">
-        <v>817</v>
+        <v>1068</v>
       </c>
       <c r="E16" s="39">
         <v>14000</v>
       </c>
       <c r="F16" t="s">
-        <v>809</v>
+        <v>1060</v>
       </c>
       <c r="G16" s="36"/>
     </row>
@@ -16434,25 +18742,25 @@
         <v>46205</v>
       </c>
       <c r="B17" t="s">
-        <v>818</v>
+        <v>1069</v>
       </c>
       <c r="C17" t="s">
         <v>51</v>
       </c>
       <c r="D17" t="s">
-        <v>819</v>
+        <v>1070</v>
       </c>
       <c r="E17" s="39">
         <v>4200</v>
       </c>
       <c r="F17" t="s">
-        <v>820</v>
+        <v>1071</v>
       </c>
       <c r="G17" s="36">
         <v>46210</v>
       </c>
       <c r="H17" t="s">
-        <v>821</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -16460,25 +18768,25 @@
         <v>46205</v>
       </c>
       <c r="B18" t="s">
-        <v>818</v>
+        <v>1069</v>
       </c>
       <c r="C18" t="s">
         <v>51</v>
       </c>
       <c r="D18" t="s">
-        <v>819</v>
+        <v>1070</v>
       </c>
       <c r="E18" s="39">
         <v>4200</v>
       </c>
       <c r="F18" t="s">
-        <v>820</v>
+        <v>1071</v>
       </c>
       <c r="G18" s="36">
         <v>46210</v>
       </c>
       <c r="H18" t="s">
-        <v>822</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -16486,17 +18794,17 @@
         <v>46205</v>
       </c>
       <c r="B19" t="s">
-        <v>823</v>
+        <v>1074</v>
       </c>
       <c r="C19" t="s">
         <v>50</v>
       </c>
       <c r="D19" t="s">
-        <v>824</v>
+        <v>1075</v>
       </c>
       <c r="E19" s="39"/>
       <c r="F19" t="s">
-        <v>814</v>
+        <v>1065</v>
       </c>
       <c r="G19" s="36"/>
     </row>
@@ -16511,13 +18819,13 @@
         <v>51</v>
       </c>
       <c r="D20" t="s">
-        <v>813</v>
+        <v>1064</v>
       </c>
       <c r="E20" s="39">
         <v>5500</v>
       </c>
       <c r="F20" t="s">
-        <v>814</v>
+        <v>1065</v>
       </c>
       <c r="G20" s="36"/>
     </row>
@@ -16532,13 +18840,13 @@
         <v>49</v>
       </c>
       <c r="D21" t="s">
-        <v>825</v>
+        <v>1076</v>
       </c>
       <c r="E21" s="39">
         <v>850</v>
       </c>
       <c r="F21" t="s">
-        <v>814</v>
+        <v>1065</v>
       </c>
       <c r="G21" s="36"/>
     </row>
@@ -16547,19 +18855,19 @@
         <v>46209</v>
       </c>
       <c r="B22" t="s">
-        <v>795</v>
+        <v>1046</v>
       </c>
       <c r="C22" t="s">
         <v>49</v>
       </c>
       <c r="D22" t="s">
-        <v>825</v>
+        <v>1076</v>
       </c>
       <c r="E22" s="39">
         <v>2700</v>
       </c>
       <c r="F22" t="s">
-        <v>814</v>
+        <v>1065</v>
       </c>
       <c r="G22" s="36"/>
     </row>
@@ -17585,7 +19893,7 @@
         <v>46054</v>
       </c>
       <c r="C2" t="s">
-        <v>826</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -17618,7 +19926,7 @@
         <v>45931</v>
       </c>
       <c r="C5" t="s">
-        <v>826</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -17689,7 +19997,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>827</v>
+        <v>1078</v>
       </c>
       <c r="B12" s="41"/>
       <c r="C12" t="s">
@@ -17698,7 +20006,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>828</v>
+        <v>1079</v>
       </c>
       <c r="B13" s="41"/>
       <c r="C13" t="s">
@@ -17707,7 +20015,7 @@
     </row>
     <row r="15" ht="32.85" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="35" t="s">
-        <v>829</v>
+        <v>1080</v>
       </c>
       <c r="B15" s="35"/>
       <c r="C15" s="35"/>
@@ -17744,25 +20052,25 @@
         <v>89</v>
       </c>
       <c r="E1" t="s">
-        <v>830</v>
+        <v>1081</v>
       </c>
       <c r="G1" t="s">
-        <v>831</v>
+        <v>1082</v>
       </c>
       <c r="I1" t="s">
-        <v>832</v>
+        <v>1083</v>
       </c>
       <c r="K1" t="s">
-        <v>833</v>
+        <v>1084</v>
       </c>
       <c r="M1" t="s">
-        <v>834</v>
+        <v>1085</v>
       </c>
       <c r="O1" t="s">
-        <v>835</v>
+        <v>1086</v>
       </c>
       <c r="Q1" t="s">
-        <v>836</v>
+        <v>1087</v>
       </c>
       <c r="S1" t="s">
         <v>83</v>
@@ -17779,25 +20087,25 @@
         <v>152</v>
       </c>
       <c r="G2" t="s">
-        <v>814</v>
+        <v>1065</v>
       </c>
       <c r="I2" t="s">
-        <v>837</v>
+        <v>1088</v>
       </c>
       <c r="K2" t="s">
         <v>255</v>
       </c>
       <c r="M2" t="s">
-        <v>819</v>
+        <v>1070</v>
       </c>
       <c r="O2" t="s">
-        <v>387</v>
+        <v>645</v>
       </c>
       <c r="Q2" t="s">
         <v>60</v>
       </c>
       <c r="S2" t="s">
-        <v>838</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -17811,25 +20119,25 @@
         <v>278</v>
       </c>
       <c r="G3" t="s">
-        <v>809</v>
+        <v>1060</v>
       </c>
       <c r="I3" t="s">
-        <v>839</v>
+        <v>1090</v>
       </c>
       <c r="K3" t="s">
         <v>349</v>
       </c>
       <c r="M3" t="s">
-        <v>840</v>
+        <v>1091</v>
       </c>
       <c r="O3" t="s">
-        <v>841</v>
+        <v>1092</v>
       </c>
       <c r="Q3" t="s">
         <v>61</v>
       </c>
       <c r="S3" t="s">
-        <v>842</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -17837,25 +20145,25 @@
         <v>46</v>
       </c>
       <c r="C4" t="s">
-        <v>843</v>
+        <v>1094</v>
       </c>
       <c r="G4" t="s">
-        <v>812</v>
+        <v>1063</v>
       </c>
       <c r="I4" t="s">
         <v>3</v>
       </c>
       <c r="K4" t="s">
-        <v>844</v>
+        <v>1095</v>
       </c>
       <c r="M4" t="s">
-        <v>845</v>
+        <v>1096</v>
       </c>
       <c r="Q4" t="s">
         <v>62</v>
       </c>
       <c r="S4" t="s">
-        <v>846</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -17866,13 +20174,13 @@
         <v>198</v>
       </c>
       <c r="G5" t="s">
-        <v>820</v>
+        <v>1071</v>
       </c>
       <c r="K5" t="s">
-        <v>847</v>
+        <v>420</v>
       </c>
       <c r="M5" t="s">
-        <v>848</v>
+        <v>1098</v>
       </c>
       <c r="Q5" t="s">
         <v>63</v>
@@ -17886,10 +20194,10 @@
         <v>48</v>
       </c>
       <c r="K6" t="s">
-        <v>849</v>
+        <v>384</v>
       </c>
       <c r="M6" t="s">
-        <v>850</v>
+        <v>1099</v>
       </c>
       <c r="Q6" t="s">
         <v>64</v>
@@ -17906,7 +20214,7 @@
         <v>286</v>
       </c>
       <c r="M7" t="s">
-        <v>851</v>
+        <v>1100</v>
       </c>
       <c r="Q7" t="s">
         <v>65</v>
@@ -17923,7 +20231,7 @@
         <v>136</v>
       </c>
       <c r="M8" t="s">
-        <v>852</v>
+        <v>1101</v>
       </c>
       <c r="Q8" t="s">
         <v>66</v>
@@ -17937,10 +20245,10 @@
         <v>51</v>
       </c>
       <c r="K9" t="s">
-        <v>853</v>
+        <v>392</v>
       </c>
       <c r="M9" t="s">
-        <v>854</v>
+        <v>1102</v>
       </c>
       <c r="Q9" t="s">
         <v>67</v>
@@ -17957,7 +20265,7 @@
         <v>203</v>
       </c>
       <c r="M10" t="s">
-        <v>855</v>
+        <v>1103</v>
       </c>
       <c r="S10" t="s">
         <v>170</v>
@@ -17971,10 +20279,10 @@
         <v>222</v>
       </c>
       <c r="M11" t="s">
-        <v>856</v>
+        <v>1104</v>
       </c>
       <c r="S11" t="s">
-        <v>857</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -17982,10 +20290,10 @@
         <v>54</v>
       </c>
       <c r="K12" t="s">
-        <v>858</v>
+        <v>1106</v>
       </c>
       <c r="M12" t="s">
-        <v>811</v>
+        <v>1062</v>
       </c>
       <c r="S12" t="s">
         <v>252</v>
@@ -17996,10 +20304,10 @@
         <v>55</v>
       </c>
       <c r="K13" t="s">
-        <v>859</v>
+        <v>1107</v>
       </c>
       <c r="M13" t="s">
-        <v>860</v>
+        <v>1108</v>
       </c>
       <c r="S13" t="s">
         <v>266</v>
@@ -18007,13 +20315,13 @@
     </row>
     <row r="14" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>861</v>
+        <v>1109</v>
       </c>
       <c r="K14" t="s">
-        <v>862</v>
+        <v>1110</v>
       </c>
       <c r="M14" t="s">
-        <v>863</v>
+        <v>1111</v>
       </c>
       <c r="S14" t="s">
         <v>97</v>
@@ -18021,27 +20329,27 @@
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>864</v>
+        <v>1112</v>
       </c>
       <c r="K15" t="s">
-        <v>865</v>
+        <v>1113</v>
       </c>
       <c r="M15" t="s">
-        <v>866</v>
+        <v>1114</v>
       </c>
       <c r="S15" t="s">
-        <v>867</v>
+        <v>489</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>868</v>
+        <v>1115</v>
       </c>
       <c r="K16" t="s">
-        <v>869</v>
+        <v>1116</v>
       </c>
       <c r="M16" t="s">
-        <v>870</v>
+        <v>1117</v>
       </c>
       <c r="S16" t="s">
         <v>364</v>
@@ -18049,13 +20357,13 @@
     </row>
     <row r="17" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>871</v>
+        <v>1118</v>
       </c>
       <c r="K17" t="s">
-        <v>872</v>
+        <v>1119</v>
       </c>
       <c r="M17" t="s">
-        <v>825</v>
+        <v>1076</v>
       </c>
       <c r="S17" t="s">
         <v>92</v>
@@ -18063,27 +20371,27 @@
     </row>
     <row r="18" ht="15" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>873</v>
+        <v>1120</v>
       </c>
       <c r="K18" t="s">
-        <v>874</v>
+        <v>1121</v>
       </c>
       <c r="M18" t="s">
-        <v>816</v>
+        <v>1067</v>
       </c>
       <c r="S18" t="s">
-        <v>875</v>
+        <v>396</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
       <c r="K19" t="s">
-        <v>876</v>
+        <v>1122</v>
       </c>
       <c r="M19" t="s">
-        <v>877</v>
+        <v>1123</v>
       </c>
       <c r="S19" t="s">
-        <v>878</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
@@ -18091,7 +20399,7 @@
         <v>233</v>
       </c>
       <c r="M20" t="s">
-        <v>879</v>
+        <v>1125</v>
       </c>
       <c r="S20" t="s">
         <v>317</v>
@@ -18102,7 +20410,7 @@
         <v>183</v>
       </c>
       <c r="M21" t="s">
-        <v>880</v>
+        <v>1126</v>
       </c>
       <c r="S21" t="s">
         <v>237</v>
@@ -18110,10 +20418,10 @@
     </row>
     <row r="22" ht="15" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
       <c r="K22" t="s">
-        <v>881</v>
+        <v>1127</v>
       </c>
       <c r="M22" t="s">
-        <v>882</v>
+        <v>1128</v>
       </c>
       <c r="S22" t="s">
         <v>99</v>
@@ -18124,29 +20432,29 @@
         <v>173</v>
       </c>
       <c r="M23" t="s">
-        <v>883</v>
+        <v>1129</v>
       </c>
       <c r="S23" t="s">
-        <v>884</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
       <c r="K24" t="s">
-        <v>885</v>
+        <v>627</v>
       </c>
       <c r="M24" t="s">
-        <v>886</v>
+        <v>1131</v>
       </c>
       <c r="S24" t="s">
-        <v>887</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
       <c r="K25" t="s">
-        <v>888</v>
+        <v>1133</v>
       </c>
       <c r="M25" t="s">
-        <v>889</v>
+        <v>1134</v>
       </c>
       <c r="S25" t="s">
         <v>157</v>
@@ -18154,10 +20462,10 @@
     </row>
     <row r="26" ht="15" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
       <c r="K26" t="s">
-        <v>890</v>
+        <v>1135</v>
       </c>
       <c r="M26" t="s">
-        <v>891</v>
+        <v>1136</v>
       </c>
       <c r="S26" t="s">
         <v>141</v>
@@ -18165,24 +20473,24 @@
     </row>
     <row r="27" ht="15" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
       <c r="K27" t="s">
-        <v>892</v>
+        <v>1137</v>
       </c>
       <c r="M27" t="s">
-        <v>893</v>
+        <v>1138</v>
       </c>
       <c r="S27" t="s">
-        <v>894</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" spans="11:19" x14ac:dyDescent="0.25">
       <c r="K28" t="s">
-        <v>895</v>
+        <v>1140</v>
       </c>
       <c r="M28" t="s">
-        <v>896</v>
+        <v>1141</v>
       </c>
       <c r="S28" t="s">
-        <v>897</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" spans="11:13" x14ac:dyDescent="0.25">
@@ -18190,15 +20498,15 @@
         <v>240</v>
       </c>
       <c r="M29" t="s">
-        <v>898</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" spans="11:13" x14ac:dyDescent="0.25">
       <c r="K30" t="s">
-        <v>899</v>
+        <v>502</v>
       </c>
       <c r="M30" t="s">
-        <v>900</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" spans="11:13" x14ac:dyDescent="0.25">
@@ -18206,7 +20514,7 @@
         <v>280</v>
       </c>
       <c r="M31" t="s">
-        <v>901</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" spans="11:13" x14ac:dyDescent="0.25">
@@ -18214,15 +20522,15 @@
         <v>335</v>
       </c>
       <c r="M32" t="s">
-        <v>902</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" spans="11:13" x14ac:dyDescent="0.25">
       <c r="K33" t="s">
-        <v>903</v>
+        <v>1147</v>
       </c>
       <c r="M33" t="s">
-        <v>904</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" spans="11:13" x14ac:dyDescent="0.25">
@@ -18230,160 +20538,160 @@
         <v>165</v>
       </c>
       <c r="M34" t="s">
-        <v>905</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" spans="11:13" x14ac:dyDescent="0.25">
       <c r="K35" t="s">
-        <v>906</v>
+        <v>1150</v>
       </c>
       <c r="M35" t="s">
-        <v>813</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M36" t="s">
-        <v>907</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M37" t="s">
-        <v>908</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M38" t="s">
-        <v>909</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M39" t="s">
-        <v>910</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M40" t="s">
-        <v>911</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M41" t="s">
-        <v>912</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M42" t="s">
-        <v>913</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M43" t="s">
-        <v>914</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M44" t="s">
-        <v>824</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M45" t="s">
-        <v>808</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M46" t="s">
-        <v>915</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M47" t="s">
-        <v>916</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M48" t="s">
-        <v>917</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M49" t="s">
-        <v>918</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M50" t="s">
-        <v>919</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M51" t="s">
-        <v>920</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M52" t="s">
-        <v>817</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M53" t="s">
-        <v>921</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M54" t="s">
-        <v>922</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M55" t="s">
-        <v>923</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M56" t="s">
-        <v>924</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M57" t="s">
-        <v>925</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M58" t="s">
-        <v>926</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M59" t="s">
-        <v>927</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M60" t="s">
-        <v>928</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="61" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M61" t="s">
-        <v>929</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M62" t="s">
-        <v>930</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M63" t="s">
-        <v>931</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M64" t="s">
-        <v>932</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
@@ -18393,22 +20701,22 @@
     </row>
     <row r="66" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M66" t="s">
-        <v>933</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="67" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M67" t="s">
-        <v>934</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="68" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M68" t="s">
-        <v>935</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" spans="13:13" x14ac:dyDescent="0.25">
       <c r="M69" t="s">
-        <v>936</v>
+        <v>1180</v>
       </c>
     </row>
   </sheetData>
